--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="489">
   <si>
     <t>IDSocio</t>
   </si>
@@ -103,241 +103,409 @@
     <t>Rutina</t>
   </si>
   <si>
+    <t>338748</t>
+  </si>
+  <si>
     <t>98101</t>
   </si>
   <si>
+    <t>330960</t>
+  </si>
+  <si>
+    <t>84873</t>
+  </si>
+  <si>
     <t>338906</t>
   </si>
   <si>
+    <t>339855</t>
+  </si>
+  <si>
+    <t>340357</t>
+  </si>
+  <si>
+    <t>340395</t>
+  </si>
+  <si>
+    <t>341050</t>
+  </si>
+  <si>
+    <t>338861</t>
+  </si>
+  <si>
     <t>338858</t>
   </si>
   <si>
-    <t>339855</t>
-  </si>
-  <si>
-    <t>338861</t>
-  </si>
-  <si>
-    <t>340357</t>
-  </si>
-  <si>
-    <t>340395</t>
+    <t>340980</t>
   </si>
   <si>
     <t>340164</t>
   </si>
   <si>
-    <t>340980</t>
+    <t>341657</t>
+  </si>
+  <si>
+    <t>341829</t>
+  </si>
+  <si>
+    <t>340619</t>
   </si>
   <si>
     <t>340598</t>
   </si>
   <si>
-    <t>341050</t>
-  </si>
-  <si>
-    <t>340619</t>
-  </si>
-  <si>
-    <t>341657</t>
-  </si>
-  <si>
-    <t>341829</t>
+    <t>342326</t>
+  </si>
+  <si>
+    <t>343533</t>
+  </si>
+  <si>
+    <t>343614</t>
+  </si>
+  <si>
+    <t>344617</t>
+  </si>
+  <si>
+    <t>343909</t>
+  </si>
+  <si>
+    <t>344104</t>
+  </si>
+  <si>
+    <t>343906</t>
   </si>
   <si>
     <t>341744</t>
   </si>
   <si>
-    <t>342326</t>
+    <t>343865</t>
+  </si>
+  <si>
+    <t>344702</t>
+  </si>
+  <si>
+    <t>344139</t>
+  </si>
+  <si>
+    <t>344328</t>
+  </si>
+  <si>
+    <t>343530</t>
+  </si>
+  <si>
+    <t>343922</t>
   </si>
   <si>
     <t>342397</t>
   </si>
   <si>
+    <t>343908</t>
+  </si>
+  <si>
     <t>342743</t>
   </si>
   <si>
-    <t>343533</t>
-  </si>
-  <si>
-    <t>343865</t>
-  </si>
-  <si>
-    <t>343530</t>
+    <t>344705</t>
+  </si>
+  <si>
+    <t>16566</t>
   </si>
   <si>
     <t>95858</t>
   </si>
   <si>
+    <t>16014</t>
+  </si>
+  <si>
+    <t>82656</t>
+  </si>
+  <si>
     <t>16724</t>
   </si>
   <si>
+    <t>17673</t>
+  </si>
+  <si>
+    <t>18175</t>
+  </si>
+  <si>
+    <t>18213</t>
+  </si>
+  <si>
+    <t>18868</t>
+  </si>
+  <si>
+    <t>16679</t>
+  </si>
+  <si>
     <t>16676</t>
   </si>
   <si>
-    <t>17673</t>
-  </si>
-  <si>
-    <t>16679</t>
-  </si>
-  <si>
-    <t>18175</t>
-  </si>
-  <si>
-    <t>18213</t>
+    <t>18798</t>
   </si>
   <si>
     <t>17982</t>
   </si>
   <si>
-    <t>18798</t>
+    <t>19475</t>
+  </si>
+  <si>
+    <t>19647</t>
+  </si>
+  <si>
+    <t>18437</t>
   </si>
   <si>
     <t>18416</t>
   </si>
   <si>
-    <t>18868</t>
-  </si>
-  <si>
-    <t>18437</t>
-  </si>
-  <si>
-    <t>19475</t>
-  </si>
-  <si>
-    <t>19647</t>
+    <t>20144</t>
+  </si>
+  <si>
+    <t>21350</t>
+  </si>
+  <si>
+    <t>21431</t>
+  </si>
+  <si>
+    <t>22434</t>
+  </si>
+  <si>
+    <t>21726</t>
+  </si>
+  <si>
+    <t>21921</t>
+  </si>
+  <si>
+    <t>21723</t>
   </si>
   <si>
     <t>19562</t>
   </si>
   <si>
-    <t>20144</t>
+    <t>21682</t>
+  </si>
+  <si>
+    <t>22519</t>
+  </si>
+  <si>
+    <t>21956</t>
+  </si>
+  <si>
+    <t>22145</t>
+  </si>
+  <si>
+    <t>21347</t>
+  </si>
+  <si>
+    <t>21739</t>
   </si>
   <si>
     <t>20215</t>
   </si>
   <si>
+    <t>21725</t>
+  </si>
+  <si>
     <t>20560</t>
   </si>
   <si>
-    <t>21350</t>
-  </si>
-  <si>
-    <t>21682</t>
-  </si>
-  <si>
-    <t>21347</t>
+    <t>22522</t>
   </si>
   <si>
     <t>AZAHARES CUL</t>
   </si>
   <si>
+    <t xml:space="preserve">ITZEL VALERIA </t>
+  </si>
+  <si>
     <t>DANIEL ALBERTO</t>
   </si>
   <si>
+    <t>KARLA JANETH</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALMA LETICIA </t>
   </si>
   <si>
+    <t xml:space="preserve">JUAN PABLO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARAHI DE MARIA </t>
+  </si>
+  <si>
+    <t>SARAH FABIOLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESUS IVAN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALERIA </t>
+  </si>
+  <si>
     <t xml:space="preserve">MANUEL FERNANDO </t>
   </si>
   <si>
-    <t xml:space="preserve">JUAN PABLO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALERIA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARAHI DE MARIA </t>
-  </si>
-  <si>
-    <t>SARAH FABIOLA</t>
+    <t>JUAN JOSE</t>
   </si>
   <si>
     <t xml:space="preserve">DYLAN ARTURO </t>
   </si>
   <si>
-    <t>JUAN JOSE</t>
+    <t xml:space="preserve">KEVIN RICARDO </t>
+  </si>
+  <si>
+    <t>EDGAR FRANCISCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE RAUL </t>
   </si>
   <si>
     <t xml:space="preserve">LAURA LILIA </t>
   </si>
   <si>
-    <t xml:space="preserve">JESUS IVAN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOSE RAUL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEVIN RICARDO </t>
-  </si>
-  <si>
-    <t>EDGAR FRANCISCO</t>
+    <t xml:space="preserve">MARIAN </t>
+  </si>
+  <si>
+    <t>JOSE GUADALLUPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUAN FRANCISCO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALBERTO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLORIA GUADALUPE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA FERNANDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADRIANA REBECA </t>
   </si>
   <si>
     <t xml:space="preserve">PEDRO </t>
   </si>
   <si>
-    <t xml:space="preserve">MARIAN </t>
+    <t xml:space="preserve">VLADIMIR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARLETH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KATHERINE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ALONSO </t>
+  </si>
+  <si>
+    <t>MAURO EMMANUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRENE </t>
   </si>
   <si>
     <t>GUSTAVO</t>
   </si>
   <si>
+    <t>LUIS JESUS</t>
+  </si>
+  <si>
     <t xml:space="preserve">OCTAVIANO </t>
   </si>
   <si>
-    <t>JOSE GUADALLUPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VLADIMIR </t>
-  </si>
-  <si>
-    <t>MAURO EMMANUEL</t>
+    <t xml:space="preserve">DIANA LAURA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEREZ </t>
   </si>
   <si>
     <t xml:space="preserve">VIZCARRA </t>
   </si>
   <si>
+    <t xml:space="preserve">PEÑUELAS </t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>CHAIRES</t>
   </si>
   <si>
+    <t xml:space="preserve">PADILLA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUIAR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BORRAZ </t>
+  </si>
+  <si>
+    <t>REATIGA</t>
+  </si>
+  <si>
     <t xml:space="preserve">LAMAS </t>
   </si>
   <si>
-    <t xml:space="preserve">PADILLA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGUIAR </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BORRAZ </t>
+    <t xml:space="preserve">PONCE </t>
   </si>
   <si>
     <t xml:space="preserve">RUBIO </t>
   </si>
   <si>
-    <t xml:space="preserve">PONCE </t>
+    <t xml:space="preserve">RAMIREZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANZANO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORENO </t>
   </si>
   <si>
     <t xml:space="preserve">ONTIVEROS </t>
   </si>
   <si>
-    <t>REATIGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORENO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMIREZ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANZANO </t>
+    <t>MONTES</t>
+  </si>
+  <si>
+    <t>RENTERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROJO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARRA </t>
+  </si>
+  <si>
+    <t>AMEZQUITA</t>
   </si>
   <si>
     <t xml:space="preserve">CAMACHO </t>
   </si>
   <si>
-    <t>MONTES</t>
+    <t xml:space="preserve">RENTERIA </t>
+  </si>
+  <si>
+    <t>OROPEZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HERNANDEZ </t>
+  </si>
+  <si>
+    <t>MEZA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAVARRO </t>
   </si>
   <si>
     <t xml:space="preserve">LEYVA </t>
@@ -346,373 +514,589 @@
     <t xml:space="preserve">LOPEZ </t>
   </si>
   <si>
-    <t>RENTERIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RENTERIA </t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>SILVA</t>
+  </si>
+  <si>
+    <t>MENDIVIL</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t xml:space="preserve">PERALES </t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
+    <t xml:space="preserve">SALAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZAZUETA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEDINA </t>
+  </si>
+  <si>
+    <t>ARCE</t>
+  </si>
+  <si>
     <t xml:space="preserve">GALINDO </t>
   </si>
   <si>
-    <t xml:space="preserve">SALAS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZAZUETA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEDINA </t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALENZUELA </t>
   </si>
   <si>
     <t xml:space="preserve">DUARTE </t>
   </si>
   <si>
-    <t>ARCE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALENZUELA </t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t xml:space="preserve">CAMPOS </t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GARCIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANCHEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACHADO </t>
   </si>
   <si>
     <t xml:space="preserve">HARO </t>
   </si>
   <si>
-    <t xml:space="preserve">CAMPOS </t>
+    <t xml:space="preserve">DOMINGUEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COTA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAZQUEZ </t>
   </si>
   <si>
     <t>BELTRAN</t>
   </si>
   <si>
+    <t xml:space="preserve">ANGULO </t>
+  </si>
+  <si>
     <t xml:space="preserve">SAUCEDA </t>
   </si>
   <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HERNANDEZ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAZQUEZ </t>
+    <t>ROMAN</t>
   </si>
   <si>
     <t>52</t>
   </si>
   <si>
+    <t>6673260503</t>
+  </si>
+  <si>
     <t>6675383330</t>
   </si>
   <si>
+    <t>6671284496</t>
+  </si>
+  <si>
+    <t>6671055229</t>
+  </si>
+  <si>
     <t>6672011841</t>
   </si>
   <si>
+    <t>6681452661</t>
+  </si>
+  <si>
+    <t>6674761021</t>
+  </si>
+  <si>
+    <t>6674779002</t>
+  </si>
+  <si>
+    <t>6675777773</t>
+  </si>
+  <si>
+    <t>6671901936</t>
+  </si>
+  <si>
     <t>6674956589</t>
   </si>
   <si>
-    <t>6681452661</t>
-  </si>
-  <si>
-    <t>6671901936</t>
-  </si>
-  <si>
-    <t>6674761021</t>
-  </si>
-  <si>
-    <t>6674779002</t>
+    <t>6673450501</t>
   </si>
   <si>
     <t>6674732132</t>
   </si>
   <si>
-    <t>6673450501</t>
+    <t>3224537874</t>
+  </si>
+  <si>
+    <t>6676987648</t>
+  </si>
+  <si>
+    <t>6672537304</t>
   </si>
   <si>
     <t>6673537007</t>
   </si>
   <si>
-    <t>6675777773</t>
-  </si>
-  <si>
-    <t>6672537304</t>
-  </si>
-  <si>
-    <t>3224537874</t>
-  </si>
-  <si>
-    <t>6676987648</t>
+    <t>6675145803</t>
+  </si>
+  <si>
+    <t>6673961529</t>
+  </si>
+  <si>
+    <t>6671911835</t>
+  </si>
+  <si>
+    <t>6671751779</t>
+  </si>
+  <si>
+    <t>6672155907</t>
+  </si>
+  <si>
+    <t>6862342452</t>
+  </si>
+  <si>
+    <t>6674722142</t>
   </si>
   <si>
     <t>3221713510</t>
   </si>
   <si>
-    <t>6675145803</t>
+    <t>6872535687</t>
+  </si>
+  <si>
+    <t>6671444793</t>
+  </si>
+  <si>
+    <t>6671456800</t>
+  </si>
+  <si>
+    <t>6721229789</t>
+  </si>
+  <si>
+    <t>6674640838</t>
+  </si>
+  <si>
+    <t>6674077607</t>
   </si>
   <si>
     <t>6674049839</t>
   </si>
   <si>
+    <t>6672551941</t>
+  </si>
+  <si>
     <t>6731436529</t>
   </si>
   <si>
-    <t>6673961529</t>
-  </si>
-  <si>
-    <t>6872535687</t>
-  </si>
-  <si>
-    <t>6674640838</t>
+    <t>6673290828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANUBIO </t>
   </si>
   <si>
     <t>C. GABRIELA MISTRAL 3445</t>
   </si>
   <si>
+    <t>ESTANCIA</t>
+  </si>
+  <si>
+    <t>C. TENOTITLAN 4418</t>
+  </si>
+  <si>
     <t xml:space="preserve">BACHIGULATO </t>
   </si>
   <si>
-    <t xml:space="preserve">TORRES </t>
-  </si>
-  <si>
     <t xml:space="preserve">BUGAMBILIAS </t>
   </si>
   <si>
+    <t xml:space="preserve">LA ESTANCIA </t>
+  </si>
+  <si>
+    <t>BLVD FLOR DE LIZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">BACHIGUALTO </t>
   </si>
   <si>
-    <t xml:space="preserve">LA ESTANCIA </t>
-  </si>
-  <si>
-    <t>BLVD FLOR DE LIZ</t>
-  </si>
-  <si>
     <t xml:space="preserve">VILLAS DEL RIO </t>
   </si>
   <si>
+    <t xml:space="preserve">ARGENTINA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTA ROCIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILLAS DE MANANTIAL </t>
+  </si>
+  <si>
+    <t>CAMPO BELLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CULIACANCITO </t>
+  </si>
+  <si>
     <t xml:space="preserve">TRRANOVA </t>
   </si>
   <si>
-    <t xml:space="preserve">ARGENTINA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CULIACANCITO </t>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>Femenino</t>
   </si>
   <si>
     <t>Masculino</t>
   </si>
   <si>
-    <t>Femenino</t>
+    <t>18-12-2008</t>
   </si>
   <si>
     <t>17-05-1998</t>
   </si>
   <si>
+    <t>23-10-1995</t>
+  </si>
+  <si>
+    <t>30-11-1979</t>
+  </si>
+  <si>
     <t>04-03-1983</t>
   </si>
   <si>
+    <t>06-12-1998</t>
+  </si>
+  <si>
+    <t>22-12-2001</t>
+  </si>
+  <si>
+    <t>05-10-2004</t>
+  </si>
+  <si>
+    <t>23-03-2011</t>
+  </si>
+  <si>
+    <t>12-06-2001</t>
+  </si>
+  <si>
     <t>22-06-2005</t>
   </si>
   <si>
-    <t>06-12-1998</t>
-  </si>
-  <si>
-    <t>12-06-2001</t>
-  </si>
-  <si>
-    <t>22-12-2001</t>
-  </si>
-  <si>
-    <t>05-10-2004</t>
+    <t>08-10-2007</t>
   </si>
   <si>
     <t>25-09-2010</t>
   </si>
   <si>
-    <t>08-10-2007</t>
+    <t>05-08-1995</t>
+  </si>
+  <si>
+    <t>15-06-1994</t>
+  </si>
+  <si>
+    <t>01-09-1999</t>
   </si>
   <si>
     <t>17-02-2009</t>
   </si>
   <si>
-    <t>23-03-2011</t>
-  </si>
-  <si>
-    <t>01-09-1999</t>
-  </si>
-  <si>
-    <t>05-08-1995</t>
-  </si>
-  <si>
-    <t>15-06-1994</t>
+    <t>21-12-1999</t>
+  </si>
+  <si>
+    <t>06-09-2006</t>
+  </si>
+  <si>
+    <t>17-03-2007</t>
+  </si>
+  <si>
+    <t>21-02-2000</t>
+  </si>
+  <si>
+    <t>26-10-1982</t>
+  </si>
+  <si>
+    <t>27-01-1995</t>
+  </si>
+  <si>
+    <t>25-11-2005</t>
   </si>
   <si>
     <t>12-12-1974</t>
   </si>
   <si>
-    <t>21-12-1999</t>
+    <t>23-01-2009</t>
+  </si>
+  <si>
+    <t>27-05-2005</t>
+  </si>
+  <si>
+    <t>05-01-2008</t>
+  </si>
+  <si>
+    <t>08-11-1995</t>
+  </si>
+  <si>
+    <t>04-04-2005</t>
+  </si>
+  <si>
+    <t>19-10-1976</t>
   </si>
   <si>
     <t>15-10-1992</t>
   </si>
   <si>
+    <t>20-01-2010</t>
+  </si>
+  <si>
     <t>20-11-2000</t>
   </si>
   <si>
-    <t>06-09-2006</t>
-  </si>
-  <si>
-    <t>23-01-2009</t>
-  </si>
-  <si>
-    <t>04-04-2005</t>
+    <t>16-03-2004</t>
+  </si>
+  <si>
+    <t>ITZELPEREZ1812@GMAIL.COM</t>
   </si>
   <si>
     <t>DANIELVIZCARRA@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>KARLAPERALES23@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALBERTOTOMARQUEZ79@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
   </si>
   <si>
+    <t>JUAN18752@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SARAHIAGUIAR001@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SARAHABORRAZ05@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JESUSIVANREATIGA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VLAMASGALINDO@GMIAL.COM</t>
+  </si>
+  <si>
     <t>MANUELLAMASGALINDO@GMAIL.COM</t>
   </si>
   <si>
-    <t>JUAN18752@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>VLAMASGALINDO@GMIAL.COM</t>
-  </si>
-  <si>
-    <t>SARAHIAGUIAR001@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>SARAHABORRAZ05@GMAIL.COM</t>
+    <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
   </si>
   <si>
     <t>DYLANRUBIO2509@GMAIL.COM</t>
   </si>
   <si>
-    <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
+    <t>DISTRITOTRECEE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>EDGAR.VLA@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>JRAULMV1@GMAIL.COM</t>
   </si>
   <si>
     <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
   </si>
   <si>
-    <t>JESUSIVANREATIGA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JRAULMV1@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DISTRITOTRECEE@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>EDGAR.VLA@HOTMAIL.COM</t>
+    <t>MARIANONTES125@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JFX4318@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALBERTOROJO21@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>PARRAGLORIA321@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
+  </si>
+  <si>
+    <t>ADRIANAPARRA2500@GMAIL.COM</t>
   </si>
   <si>
     <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>MARIANONTES125@GMAIL.COM</t>
+    <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MARLETH5002@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>KAT0508SAN@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CARLOSMEZA0811@OUTLOOK.COM</t>
+  </si>
+  <si>
+    <t>MAUROEMMANUEL0404@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
   </si>
   <si>
     <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
   </si>
   <si>
+    <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
+  </si>
+  <si>
     <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
   </si>
   <si>
-    <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>MAUROEMMANUEL0404@GMAIL.COM</t>
+    <t>DIANA_SR16@OUTLOOK.COM</t>
+  </si>
+  <si>
+    <t>28-01-2026 14:48:02</t>
   </si>
   <si>
     <t>06-06-2022 19:25:07</t>
   </si>
   <si>
+    <t>29-12-2025 18:55:46</t>
+  </si>
+  <si>
+    <t>12-04-2022 08:01:19</t>
+  </si>
+  <si>
     <t>28-01-2026 19:52:18</t>
   </si>
   <si>
+    <t>02-02-2026 05:48:09</t>
+  </si>
+  <si>
+    <t>02-02-2026 18:57:00</t>
+  </si>
+  <si>
+    <t>02-02-2026 20:56:33</t>
+  </si>
+  <si>
+    <t>04-02-2026 15:49:35</t>
+  </si>
+  <si>
+    <t>28-01-2026 18:02:40</t>
+  </si>
+  <si>
     <t>28-01-2026 17:57:35</t>
   </si>
   <si>
-    <t>02-02-2026 05:48:09</t>
-  </si>
-  <si>
-    <t>28-01-2026 18:02:40</t>
-  </si>
-  <si>
-    <t>02-02-2026 18:57:00</t>
-  </si>
-  <si>
-    <t>02-02-2026 20:56:33</t>
+    <t>04-02-2026 13:04:54</t>
   </si>
   <si>
     <t>02-02-2026 14:14:23</t>
   </si>
   <si>
-    <t>04-02-2026 13:04:54</t>
+    <t>06-02-2026 18:05:27</t>
+  </si>
+  <si>
+    <t>07-02-2026 13:08:56</t>
+  </si>
+  <si>
+    <t>03-02-2026 15:16:06</t>
   </si>
   <si>
     <t>03-02-2026 14:38:21</t>
   </si>
   <si>
-    <t>04-02-2026 15:49:35</t>
-  </si>
-  <si>
-    <t>03-02-2026 15:16:06</t>
-  </si>
-  <si>
-    <t>06-02-2026 18:05:27</t>
-  </si>
-  <si>
-    <t>07-02-2026 13:08:56</t>
+    <t>09-02-2026 17:29:11</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:37:04</t>
+  </si>
+  <si>
+    <t>13-02-2026 20:07:29</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:34:00</t>
+  </si>
+  <si>
+    <t>16-02-2026 04:41:54</t>
+  </si>
+  <si>
+    <t>16-02-2026 14:49:21</t>
+  </si>
+  <si>
+    <t>16-02-2026 04:24:57</t>
   </si>
   <si>
     <t>07-02-2026 07:59:31</t>
   </si>
   <si>
-    <t>09-02-2026 17:29:11</t>
+    <t>15-02-2026 14:10:10</t>
+  </si>
+  <si>
+    <t>17-02-2026 20:20:03</t>
+  </si>
+  <si>
+    <t>16-02-2026 15:58:58</t>
+  </si>
+  <si>
+    <t>16-02-2026 19:03:39</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:28:11</t>
+  </si>
+  <si>
+    <t>16-02-2026 06:00:38</t>
   </si>
   <si>
     <t>09-02-2026 18:34:08</t>
   </si>
   <si>
+    <t>16-02-2026 04:37:58</t>
+  </si>
+  <si>
     <t>10-02-2026 17:15:49</t>
   </si>
   <si>
-    <t>13-02-2026 16:37:04</t>
-  </si>
-  <si>
-    <t>15-02-2026 14:10:10</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:28:11</t>
+    <t>17-02-2026 20:25:26</t>
   </si>
   <si>
     <t>Culiacan pago</t>
   </si>
   <si>
+    <t>inscripcion promo 199</t>
+  </si>
+  <si>
+    <t>Forzoso</t>
+  </si>
+  <si>
     <t>Sin contrato</t>
   </si>
   <si>
-    <t>Forzoso</t>
+    <t>No Forzoso</t>
+  </si>
+  <si>
+    <t>PLAN FAMILIA / AMIGOS X $499</t>
   </si>
   <si>
     <t>1 MES $899</t>
@@ -721,241 +1105,364 @@
     <t>PROMO FEBRERO 12 MESES</t>
   </si>
   <si>
-    <t>PLAN FAMILIA / AMIGOS X $499</t>
-  </si>
-  <si>
     <t>3 MESES $1,899</t>
   </si>
   <si>
     <t>CONVENIOS $549</t>
   </si>
   <si>
+    <t>RECURRENTE $649 LE</t>
+  </si>
+  <si>
+    <t>TRIMESTRE ESTUDIANTE</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
     <t>899</t>
   </si>
   <si>
-    <t>499</t>
-  </si>
-  <si>
     <t>633</t>
   </si>
   <si>
     <t>549</t>
   </si>
   <si>
+    <t>649</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:40:35</t>
+  </si>
+  <si>
     <t>02-02-2026 17:55:17</t>
   </si>
   <si>
+    <t>17-02-2026 18:46:14</t>
+  </si>
+  <si>
+    <t>16-02-2026 04:14:14</t>
+  </si>
+  <si>
     <t>09-02-2026 18:05:21</t>
   </si>
   <si>
+    <t>02-02-2026 05:49:53</t>
+  </si>
+  <si>
+    <t>02-02-2026 18:58:53</t>
+  </si>
+  <si>
+    <t>05-02-2026 20:14:53</t>
+  </si>
+  <si>
+    <t>04-02-2026 15:52:13</t>
+  </si>
+  <si>
+    <t>03-02-2026 18:13:35</t>
+  </si>
+  <si>
     <t>03-02-2026 18:15:55</t>
   </si>
   <si>
-    <t>02-02-2026 05:49:53</t>
-  </si>
-  <si>
-    <t>03-02-2026 18:13:35</t>
-  </si>
-  <si>
-    <t>02-02-2026 18:58:53</t>
-  </si>
-  <si>
-    <t>05-02-2026 20:14:53</t>
+    <t>04-02-2026 13:06:15</t>
   </si>
   <si>
     <t>02-02-2026 14:15:24</t>
   </si>
   <si>
-    <t>04-02-2026 13:06:15</t>
+    <t>06-02-2026 18:09:06</t>
+  </si>
+  <si>
+    <t>07-02-2026 13:12:58</t>
+  </si>
+  <si>
+    <t>03-02-2026 15:23:17</t>
   </si>
   <si>
     <t>03-02-2026 14:39:22</t>
   </si>
   <si>
-    <t>04-02-2026 15:52:13</t>
-  </si>
-  <si>
-    <t>03-02-2026 15:23:17</t>
-  </si>
-  <si>
-    <t>06-02-2026 18:09:06</t>
-  </si>
-  <si>
-    <t>07-02-2026 13:12:58</t>
+    <t>09-02-2026 17:30:56</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:39:33</t>
+  </si>
+  <si>
+    <t>16-02-2026 19:40:20</t>
+  </si>
+  <si>
+    <t>17-02-2026 17:35:27</t>
+  </si>
+  <si>
+    <t>16-02-2026 04:45:09</t>
+  </si>
+  <si>
+    <t>16-02-2026 14:53:31</t>
+  </si>
+  <si>
+    <t>16-02-2026 04:34:04</t>
   </si>
   <si>
     <t>07-02-2026 08:01:13</t>
   </si>
   <si>
-    <t>09-02-2026 17:30:56</t>
+    <t>15-02-2026 14:11:41</t>
+  </si>
+  <si>
+    <t>17-02-2026 20:22:39</t>
+  </si>
+  <si>
+    <t>16-02-2026 16:00:45</t>
+  </si>
+  <si>
+    <t>16-02-2026 19:05:32</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:30:21</t>
+  </si>
+  <si>
+    <t>16-02-2026 06:02:04</t>
   </si>
   <si>
     <t>11-02-2026 18:23:52</t>
   </si>
   <si>
+    <t>16-02-2026 04:39:44</t>
+  </si>
+  <si>
     <t>10-02-2026 17:22:40</t>
   </si>
   <si>
-    <t>13-02-2026 16:39:33</t>
-  </si>
-  <si>
-    <t>15-02-2026 14:11:41</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:30:21</t>
+    <t>17-02-2026 20:27:25</t>
+  </si>
+  <si>
+    <t>16-03-2026 23:59:59</t>
   </si>
   <si>
     <t>02-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>17-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>16-05-2026 23:59:59</t>
+  </si>
+  <si>
     <t>09-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>02-05-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>05-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>04-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>03-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>02-05-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>05-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>04-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>06-03-2026 23:59:59</t>
   </si>
   <si>
     <t>07-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>13-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>15-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>11-03-2026 23:59:59</t>
   </si>
   <si>
     <t>10-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>13-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>15-03-2026 23:59:59</t>
+    <t>16-02-2026 13:40:08</t>
+  </si>
+  <si>
+    <t>17-02-2026 18:45:49</t>
   </si>
   <si>
     <t>09-02-2026 18:04:48</t>
   </si>
   <si>
+    <t>02-02-2026 18:58:21</t>
+  </si>
+  <si>
+    <t>03-02-2026 18:13:13</t>
+  </si>
+  <si>
     <t>03-02-2026 18:15:25</t>
   </si>
   <si>
-    <t>03-02-2026 18:13:13</t>
-  </si>
-  <si>
-    <t>02-02-2026 18:58:21</t>
+    <t>06-02-2026 18:08:40</t>
+  </si>
+  <si>
+    <t>07-02-2026 13:12:39</t>
   </si>
   <si>
     <t>03-02-2026 15:21:47</t>
   </si>
   <si>
-    <t>06-02-2026 18:08:40</t>
-  </si>
-  <si>
-    <t>07-02-2026 13:12:39</t>
-  </si>
-  <si>
     <t>09-02-2026 17:30:19</t>
   </si>
   <si>
+    <t>13-02-2026 16:39:06</t>
+  </si>
+  <si>
+    <t>16-02-2026 14:52:00</t>
+  </si>
+  <si>
+    <t>17-02-2026 20:21:36</t>
+  </si>
+  <si>
+    <t>16-02-2026 19:05:10</t>
+  </si>
+  <si>
+    <t>13-02-2026 16:29:54</t>
+  </si>
+  <si>
     <t>10-02-2026 17:22:03</t>
   </si>
   <si>
-    <t>13-02-2026 16:39:06</t>
-  </si>
-  <si>
-    <t>13-02-2026 16:29:54</t>
+    <t>17-02-2026 20:26:49</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>2</t>
+    <t>26040522389000002737</t>
   </si>
   <si>
     <t>26040522019480001886</t>
   </si>
   <si>
+    <t>26040522442460002883</t>
+  </si>
+  <si>
+    <t>26040522368800002698</t>
+  </si>
+  <si>
     <t>26040522205360002366</t>
   </si>
   <si>
+    <t>26040521997910001841</t>
+  </si>
+  <si>
+    <t>26040522021440001894</t>
+  </si>
+  <si>
+    <t>26040522119630002171</t>
+  </si>
+  <si>
+    <t>26040522078180002033</t>
+  </si>
+  <si>
+    <t>26040522052270001977</t>
+  </si>
+  <si>
     <t>26040522052400001978</t>
   </si>
   <si>
-    <t>26040521997910001841</t>
-  </si>
-  <si>
-    <t>26040522052270001977</t>
-  </si>
-  <si>
-    <t>26040522021440001894</t>
-  </si>
-  <si>
-    <t>26040522119630002171</t>
+    <t>26040522074180002020</t>
   </si>
   <si>
     <t>26040522012290001872</t>
   </si>
   <si>
-    <t>26040522074180002020</t>
+    <t>26040522144380002227</t>
+  </si>
+  <si>
+    <t>26040522161580002258</t>
+  </si>
+  <si>
+    <t>26040522042820001942</t>
   </si>
   <si>
     <t>26040522041570001940</t>
   </si>
   <si>
-    <t>26040522078180002033</t>
-  </si>
-  <si>
-    <t>26040522042820001942</t>
-  </si>
-  <si>
-    <t>26040522144380002227</t>
-  </si>
-  <si>
-    <t>26040522161580002258</t>
+    <t>26040522202510002352</t>
+  </si>
+  <si>
+    <t>26040522324550002655</t>
+  </si>
+  <si>
+    <t>26040522408860002801</t>
+  </si>
+  <si>
+    <t>26040522438040002865</t>
+  </si>
+  <si>
+    <t>26040522369220002705</t>
+  </si>
+  <si>
+    <t>26040522391260002745</t>
+  </si>
+  <si>
+    <t>26040522369090002701</t>
   </si>
   <si>
     <t>26040522155670002240</t>
   </si>
   <si>
-    <t>26040522202510002352</t>
+    <t>26040522367230002693</t>
+  </si>
+  <si>
+    <t>26040522446310002893</t>
+  </si>
+  <si>
+    <t>26040522394190002754</t>
+  </si>
+  <si>
+    <t>26040522407060002792</t>
+  </si>
+  <si>
+    <t>26040522324290002650</t>
+  </si>
+  <si>
+    <t>26040522371170002712</t>
   </si>
   <si>
     <t>26040522273970002541</t>
   </si>
   <si>
+    <t>26040522369190002704</t>
+  </si>
+  <si>
     <t>26040522239600002442</t>
   </si>
   <si>
-    <t>26040522324550002655</t>
-  </si>
-  <si>
-    <t>26040522367230002693</t>
-  </si>
-  <si>
-    <t>26040522324290002650</t>
+    <t>26040522446490002894</t>
   </si>
   <si>
     <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
   </si>
   <si>
+    <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
   </si>
   <si>
-    <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-  </si>
-  <si>
     <t>Pedro Fernando  Salas RECEPCION</t>
   </si>
   <si>
     <t>1899</t>
+  </si>
+  <si>
+    <t>1500</t>
   </si>
   <si>
     <t>N/D</t>
@@ -1331,7 +1838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -1428,76 +1935,85 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="F2" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H2" t="s">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="I2" t="s">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="J2" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="K2" t="s">
-        <v>167</v>
+        <v>250</v>
       </c>
       <c r="L2" t="s">
-        <v>188</v>
+        <v>285</v>
       </c>
       <c r="M2" t="s">
-        <v>209</v>
-      </c>
-      <c r="N2" t="s">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="O2" t="s">
-        <v>231</v>
+        <v>357</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>360</v>
       </c>
       <c r="Q2" t="s">
-        <v>238</v>
+        <v>367</v>
       </c>
       <c r="R2" t="s">
-        <v>242</v>
+        <v>373</v>
       </c>
       <c r="S2" t="s">
-        <v>263</v>
+        <v>408</v>
+      </c>
+      <c r="T2" t="s">
+        <v>423</v>
       </c>
       <c r="U2" t="s">
-        <v>286</v>
+        <v>440</v>
+      </c>
+      <c r="V2" t="s">
+        <v>441</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>288</v>
+        <v>442</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>478</v>
       </c>
       <c r="AA2" t="s">
-        <v>238</v>
+        <v>367</v>
       </c>
       <c r="AB2" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="AC2" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -1505,82 +2021,76 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="F3" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H3" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="I3" t="s">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="J3" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="K3" t="s">
-        <v>168</v>
+        <v>251</v>
       </c>
       <c r="L3" t="s">
-        <v>189</v>
+        <v>286</v>
       </c>
       <c r="M3" t="s">
-        <v>210</v>
+        <v>321</v>
+      </c>
+      <c r="N3" t="s">
+        <v>355</v>
       </c>
       <c r="O3" t="s">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="P3" t="s">
-        <v>234</v>
+        <v>361</v>
       </c>
       <c r="Q3" t="s">
-        <v>239</v>
+        <v>368</v>
       </c>
       <c r="R3" t="s">
-        <v>243</v>
+        <v>374</v>
       </c>
       <c r="S3" t="s">
-        <v>264</v>
-      </c>
-      <c r="T3" t="s">
-        <v>275</v>
+        <v>409</v>
       </c>
       <c r="U3" t="s">
-        <v>287</v>
-      </c>
-      <c r="V3" t="s">
-        <v>286</v>
+        <v>441</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>289</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>309</v>
+        <v>443</v>
       </c>
       <c r="AA3" t="s">
-        <v>239</v>
+        <v>368</v>
       </c>
       <c r="AB3" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="AC3" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -1588,85 +2098,85 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="F4" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="G4" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H4" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="I4" t="s">
-        <v>156</v>
+        <v>233</v>
       </c>
       <c r="J4" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="K4" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="L4" t="s">
-        <v>190</v>
+        <v>287</v>
       </c>
       <c r="M4" t="s">
-        <v>211</v>
+        <v>322</v>
+      </c>
+      <c r="N4" t="s">
+        <v>356</v>
       </c>
       <c r="O4" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="P4" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="Q4" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="R4" t="s">
-        <v>244</v>
+        <v>375</v>
       </c>
       <c r="S4" t="s">
-        <v>265</v>
+        <v>410</v>
       </c>
       <c r="T4" t="s">
-        <v>276</v>
+        <v>424</v>
       </c>
       <c r="U4" t="s">
-        <v>287</v>
+        <v>440</v>
       </c>
       <c r="V4" t="s">
-        <v>286</v>
+        <v>440</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>290</v>
+        <v>444</v>
       </c>
       <c r="Y4" t="s">
-        <v>309</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>310</v>
+        <v>477</v>
       </c>
       <c r="AA4" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="AB4" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="AC4" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1674,70 +2184,79 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="G5" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H5" t="s">
-        <v>136</v>
+        <v>199</v>
+      </c>
+      <c r="I5" t="s">
+        <v>234</v>
       </c>
       <c r="J5" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K5" t="s">
-        <v>170</v>
+        <v>253</v>
       </c>
       <c r="L5" t="s">
-        <v>191</v>
+        <v>288</v>
       </c>
       <c r="M5" t="s">
-        <v>212</v>
+        <v>323</v>
       </c>
       <c r="O5" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="P5" t="s">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="Q5" t="s">
-        <v>240</v>
+        <v>369</v>
       </c>
       <c r="R5" t="s">
-        <v>245</v>
+        <v>376</v>
       </c>
       <c r="S5" t="s">
-        <v>266</v>
+        <v>411</v>
       </c>
       <c r="U5" t="s">
-        <v>286</v>
+        <v>440</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>291</v>
+        <v>445</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>479</v>
       </c>
       <c r="AA5" t="s">
-        <v>313</v>
+        <v>481</v>
       </c>
       <c r="AB5" t="s">
-        <v>315</v>
+        <v>483</v>
       </c>
       <c r="AC5" t="s">
-        <v>319</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1745,85 +2264,82 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="F6" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G6" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H6" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="I6" t="s">
-        <v>156</v>
+        <v>235</v>
       </c>
       <c r="J6" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="K6" t="s">
-        <v>171</v>
+        <v>254</v>
       </c>
       <c r="L6" t="s">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="M6" t="s">
-        <v>213</v>
+        <v>324</v>
       </c>
       <c r="O6" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="P6" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="Q6" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="R6" t="s">
-        <v>246</v>
+        <v>377</v>
       </c>
       <c r="S6" t="s">
-        <v>265</v>
+        <v>412</v>
       </c>
       <c r="T6" t="s">
-        <v>277</v>
+        <v>425</v>
       </c>
       <c r="U6" t="s">
-        <v>287</v>
+        <v>440</v>
       </c>
       <c r="V6" t="s">
-        <v>286</v>
+        <v>441</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>292</v>
+        <v>446</v>
       </c>
       <c r="Y6" t="s">
-        <v>309</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>310</v>
+        <v>477</v>
       </c>
       <c r="AA6" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="AB6" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="AC6" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1831,79 +2347,70 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="F7" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="G7" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H7" t="s">
-        <v>138</v>
-      </c>
-      <c r="I7" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="J7" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
+        <v>255</v>
       </c>
       <c r="L7" t="s">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="M7" t="s">
-        <v>214</v>
+        <v>325</v>
       </c>
       <c r="O7" t="s">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>363</v>
       </c>
       <c r="Q7" t="s">
-        <v>239</v>
+        <v>369</v>
       </c>
       <c r="R7" t="s">
-        <v>247</v>
+        <v>378</v>
       </c>
       <c r="S7" t="s">
-        <v>263</v>
-      </c>
-      <c r="T7" t="s">
-        <v>278</v>
+        <v>413</v>
       </c>
       <c r="U7" t="s">
-        <v>287</v>
-      </c>
-      <c r="V7" t="s">
-        <v>287</v>
+        <v>441</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>293</v>
+        <v>447</v>
       </c>
       <c r="AA7" t="s">
-        <v>239</v>
+        <v>481</v>
       </c>
       <c r="AB7" t="s">
-        <v>314</v>
+        <v>484</v>
       </c>
       <c r="AC7" t="s">
-        <v>318</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1911,79 +2418,79 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="F8" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="G8" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H8" t="s">
-        <v>139</v>
+        <v>202</v>
+      </c>
+      <c r="I8" t="s">
+        <v>236</v>
       </c>
       <c r="J8" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="K8" t="s">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="L8" t="s">
-        <v>194</v>
+        <v>291</v>
       </c>
       <c r="M8" t="s">
-        <v>215</v>
-      </c>
-      <c r="N8" t="s">
-        <v>230</v>
+        <v>326</v>
       </c>
       <c r="O8" t="s">
-        <v>231</v>
+        <v>357</v>
       </c>
       <c r="P8" t="s">
-        <v>237</v>
+        <v>362</v>
       </c>
       <c r="Q8" t="s">
-        <v>241</v>
+        <v>367</v>
       </c>
       <c r="R8" t="s">
-        <v>248</v>
+        <v>379</v>
       </c>
       <c r="S8" t="s">
-        <v>267</v>
+        <v>409</v>
+      </c>
+      <c r="T8" t="s">
+        <v>426</v>
       </c>
       <c r="U8" t="s">
-        <v>287</v>
+        <v>440</v>
+      </c>
+      <c r="V8" t="s">
+        <v>440</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>294</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>309</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>311</v>
+        <v>448</v>
       </c>
       <c r="AA8" t="s">
-        <v>241</v>
+        <v>367</v>
       </c>
       <c r="AB8" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="AC8" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1991,73 +2498,79 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="F9" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="G9" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H9" t="s">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="J9" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="K9" t="s">
-        <v>174</v>
+        <v>257</v>
       </c>
       <c r="L9" t="s">
-        <v>195</v>
+        <v>292</v>
       </c>
       <c r="M9" t="s">
-        <v>216</v>
+        <v>327</v>
       </c>
       <c r="N9" t="s">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="O9" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="P9" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
       <c r="Q9" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="R9" t="s">
-        <v>249</v>
+        <v>380</v>
       </c>
       <c r="S9" t="s">
-        <v>263</v>
+        <v>414</v>
       </c>
       <c r="U9" t="s">
-        <v>286</v>
+        <v>440</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>295</v>
+        <v>449</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>478</v>
       </c>
       <c r="AA9" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="AB9" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="AC9" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -2065,73 +2578,73 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="F10" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H10" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="J10" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K10" t="s">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="L10" t="s">
-        <v>196</v>
+        <v>293</v>
       </c>
       <c r="M10" t="s">
-        <v>217</v>
+        <v>328</v>
       </c>
       <c r="N10" t="s">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="O10" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="P10" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
       <c r="Q10" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="R10" t="s">
-        <v>250</v>
+        <v>381</v>
       </c>
       <c r="S10" t="s">
-        <v>268</v>
+        <v>415</v>
       </c>
       <c r="U10" t="s">
-        <v>286</v>
+        <v>440</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>296</v>
+        <v>450</v>
       </c>
       <c r="AA10" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="AB10" t="s">
-        <v>314</v>
+        <v>484</v>
       </c>
       <c r="AC10" t="s">
-        <v>318</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -2139,73 +2652,85 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="G11" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H11" t="s">
-        <v>142</v>
+        <v>205</v>
+      </c>
+      <c r="I11" t="s">
+        <v>153</v>
       </c>
       <c r="J11" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="K11" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="L11" t="s">
-        <v>197</v>
+        <v>294</v>
       </c>
       <c r="M11" t="s">
-        <v>218</v>
-      </c>
-      <c r="N11" t="s">
-        <v>230</v>
+        <v>329</v>
       </c>
       <c r="O11" t="s">
-        <v>231</v>
+        <v>357</v>
       </c>
       <c r="P11" t="s">
-        <v>237</v>
+        <v>360</v>
       </c>
       <c r="Q11" t="s">
-        <v>241</v>
+        <v>367</v>
       </c>
       <c r="R11" t="s">
-        <v>251</v>
+        <v>382</v>
       </c>
       <c r="S11" t="s">
-        <v>265</v>
+        <v>416</v>
+      </c>
+      <c r="T11" t="s">
+        <v>427</v>
       </c>
       <c r="U11" t="s">
-        <v>286</v>
+        <v>440</v>
+      </c>
+      <c r="V11" t="s">
+        <v>441</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>297</v>
+        <v>451</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>479</v>
       </c>
       <c r="AA11" t="s">
-        <v>241</v>
+        <v>367</v>
       </c>
       <c r="AB11" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="AC11" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -2213,73 +2738,85 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="F12" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="G12" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H12" t="s">
-        <v>143</v>
+        <v>206</v>
+      </c>
+      <c r="I12" t="s">
+        <v>153</v>
       </c>
       <c r="J12" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="K12" t="s">
-        <v>177</v>
+        <v>260</v>
       </c>
       <c r="L12" t="s">
-        <v>198</v>
+        <v>295</v>
       </c>
       <c r="M12" t="s">
-        <v>219</v>
-      </c>
-      <c r="N12" t="s">
-        <v>230</v>
+        <v>330</v>
       </c>
       <c r="O12" t="s">
-        <v>231</v>
+        <v>357</v>
       </c>
       <c r="P12" t="s">
-        <v>237</v>
+        <v>360</v>
       </c>
       <c r="Q12" t="s">
-        <v>241</v>
+        <v>367</v>
       </c>
       <c r="R12" t="s">
-        <v>252</v>
+        <v>383</v>
       </c>
       <c r="S12" t="s">
-        <v>268</v>
+        <v>416</v>
+      </c>
+      <c r="T12" t="s">
+        <v>428</v>
       </c>
       <c r="U12" t="s">
-        <v>287</v>
+        <v>440</v>
+      </c>
+      <c r="V12" t="s">
+        <v>441</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>298</v>
+        <v>452</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>479</v>
       </c>
       <c r="AA12" t="s">
-        <v>241</v>
+        <v>367</v>
       </c>
       <c r="AB12" t="s">
-        <v>315</v>
+        <v>483</v>
       </c>
       <c r="AC12" t="s">
-        <v>319</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -2287,79 +2824,73 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="F13" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="G13" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H13" t="s">
-        <v>144</v>
-      </c>
-      <c r="I13" t="s">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="J13" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K13" t="s">
-        <v>178</v>
+        <v>261</v>
       </c>
       <c r="L13" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="M13" t="s">
-        <v>220</v>
+        <v>331</v>
+      </c>
+      <c r="N13" t="s">
+        <v>355</v>
       </c>
       <c r="O13" t="s">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="P13" t="s">
-        <v>234</v>
+        <v>364</v>
       </c>
       <c r="Q13" t="s">
-        <v>239</v>
+        <v>370</v>
       </c>
       <c r="R13" t="s">
-        <v>253</v>
+        <v>384</v>
       </c>
       <c r="S13" t="s">
-        <v>265</v>
-      </c>
-      <c r="T13" t="s">
-        <v>279</v>
+        <v>415</v>
       </c>
       <c r="U13" t="s">
-        <v>287</v>
-      </c>
-      <c r="V13" t="s">
-        <v>286</v>
+        <v>441</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>299</v>
+        <v>453</v>
       </c>
       <c r="AA13" t="s">
-        <v>239</v>
+        <v>370</v>
       </c>
       <c r="AB13" t="s">
-        <v>315</v>
+        <v>483</v>
       </c>
       <c r="AC13" t="s">
-        <v>319</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -2367,79 +2898,73 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="F14" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="G14" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H14" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" t="s">
-        <v>159</v>
+        <v>208</v>
       </c>
       <c r="J14" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K14" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="L14" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="M14" t="s">
-        <v>221</v>
+        <v>332</v>
+      </c>
+      <c r="N14" t="s">
+        <v>355</v>
       </c>
       <c r="O14" t="s">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="P14" t="s">
-        <v>234</v>
+        <v>364</v>
       </c>
       <c r="Q14" t="s">
-        <v>239</v>
+        <v>370</v>
       </c>
       <c r="R14" t="s">
-        <v>254</v>
+        <v>385</v>
       </c>
       <c r="S14" t="s">
-        <v>269</v>
-      </c>
-      <c r="T14" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="U14" t="s">
-        <v>287</v>
-      </c>
-      <c r="V14" t="s">
-        <v>286</v>
+        <v>441</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>300</v>
+        <v>454</v>
       </c>
       <c r="AA14" t="s">
-        <v>239</v>
+        <v>370</v>
       </c>
       <c r="AB14" t="s">
-        <v>315</v>
+        <v>483</v>
       </c>
       <c r="AC14" t="s">
-        <v>319</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -2447,79 +2972,79 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="F15" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
       <c r="G15" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H15" t="s">
-        <v>146</v>
+        <v>209</v>
       </c>
       <c r="I15" t="s">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="J15" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K15" t="s">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="L15" t="s">
-        <v>201</v>
+        <v>298</v>
       </c>
       <c r="M15" t="s">
-        <v>222</v>
+        <v>333</v>
       </c>
       <c r="O15" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="P15" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="Q15" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="R15" t="s">
-        <v>255</v>
+        <v>386</v>
       </c>
       <c r="S15" t="s">
-        <v>270</v>
+        <v>417</v>
       </c>
       <c r="T15" t="s">
-        <v>281</v>
+        <v>429</v>
       </c>
       <c r="U15" t="s">
-        <v>287</v>
+        <v>440</v>
       </c>
       <c r="V15" t="s">
-        <v>287</v>
+        <v>441</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>301</v>
+        <v>455</v>
       </c>
       <c r="AA15" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="AB15" t="s">
-        <v>316</v>
+        <v>484</v>
       </c>
       <c r="AC15" t="s">
-        <v>319</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2527,73 +3052,79 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="F16" t="s">
-        <v>125</v>
+        <v>180</v>
       </c>
       <c r="G16" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H16" t="s">
-        <v>147</v>
+        <v>210</v>
+      </c>
+      <c r="I16" t="s">
+        <v>238</v>
       </c>
       <c r="J16" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K16" t="s">
-        <v>181</v>
+        <v>264</v>
       </c>
       <c r="L16" t="s">
-        <v>202</v>
+        <v>299</v>
       </c>
       <c r="M16" t="s">
-        <v>223</v>
-      </c>
-      <c r="N16" t="s">
-        <v>230</v>
+        <v>334</v>
       </c>
       <c r="O16" t="s">
-        <v>231</v>
+        <v>357</v>
       </c>
       <c r="P16" t="s">
-        <v>233</v>
+        <v>362</v>
       </c>
       <c r="Q16" t="s">
-        <v>238</v>
+        <v>367</v>
       </c>
       <c r="R16" t="s">
-        <v>256</v>
+        <v>387</v>
       </c>
       <c r="S16" t="s">
-        <v>270</v>
+        <v>418</v>
+      </c>
+      <c r="T16" t="s">
+        <v>430</v>
       </c>
       <c r="U16" t="s">
-        <v>287</v>
+        <v>440</v>
+      </c>
+      <c r="V16" t="s">
+        <v>440</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>302</v>
+        <v>456</v>
       </c>
       <c r="AA16" t="s">
-        <v>238</v>
+        <v>367</v>
       </c>
       <c r="AB16" t="s">
-        <v>314</v>
+        <v>485</v>
       </c>
       <c r="AC16" t="s">
-        <v>318</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2601,79 +3132,79 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="F17" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="G17" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H17" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="I17" t="s">
-        <v>161</v>
+        <v>239</v>
       </c>
       <c r="J17" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="K17" t="s">
-        <v>182</v>
+        <v>265</v>
       </c>
       <c r="L17" t="s">
-        <v>203</v>
+        <v>300</v>
       </c>
       <c r="M17" t="s">
-        <v>224</v>
+        <v>335</v>
       </c>
       <c r="O17" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="P17" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="Q17" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="R17" t="s">
-        <v>257</v>
+        <v>388</v>
       </c>
       <c r="S17" t="s">
-        <v>264</v>
+        <v>416</v>
       </c>
       <c r="T17" t="s">
-        <v>282</v>
+        <v>431</v>
       </c>
       <c r="U17" t="s">
-        <v>287</v>
+        <v>440</v>
       </c>
       <c r="V17" t="s">
-        <v>286</v>
+        <v>441</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>303</v>
+        <v>457</v>
       </c>
       <c r="AA17" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="AB17" t="s">
-        <v>314</v>
+        <v>484</v>
       </c>
       <c r="AC17" t="s">
-        <v>318</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2681,79 +3212,73 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="F18" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H18" t="s">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="J18" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="K18" t="s">
-        <v>183</v>
+        <v>266</v>
       </c>
       <c r="L18" t="s">
-        <v>204</v>
+        <v>301</v>
       </c>
       <c r="M18" t="s">
-        <v>225</v>
+        <v>336</v>
       </c>
       <c r="N18" t="s">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="O18" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="P18" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
       <c r="Q18" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="R18" t="s">
-        <v>258</v>
+        <v>389</v>
       </c>
       <c r="S18" t="s">
-        <v>271</v>
+        <v>416</v>
       </c>
       <c r="U18" t="s">
-        <v>287</v>
+        <v>441</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>304</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>309</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="AA18" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="AB18" t="s">
-        <v>315</v>
+        <v>483</v>
       </c>
       <c r="AC18" t="s">
-        <v>319</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2761,79 +3286,79 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="F19" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H19" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="I19" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="J19" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="K19" t="s">
-        <v>184</v>
+        <v>267</v>
       </c>
       <c r="L19" t="s">
-        <v>205</v>
+        <v>302</v>
       </c>
       <c r="M19" t="s">
-        <v>226</v>
+        <v>337</v>
       </c>
       <c r="O19" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="P19" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="Q19" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="R19" t="s">
-        <v>259</v>
+        <v>390</v>
       </c>
       <c r="S19" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="T19" t="s">
-        <v>283</v>
+        <v>432</v>
       </c>
       <c r="U19" t="s">
-        <v>287</v>
+        <v>440</v>
       </c>
       <c r="V19" t="s">
-        <v>287</v>
+        <v>441</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>305</v>
+        <v>459</v>
       </c>
       <c r="AA19" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="AB19" t="s">
-        <v>317</v>
+        <v>483</v>
       </c>
       <c r="AC19" t="s">
-        <v>319</v>
+        <v>487</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2841,79 +3366,79 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="G20" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H20" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="I20" t="s">
-        <v>163</v>
+        <v>241</v>
       </c>
       <c r="J20" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K20" t="s">
-        <v>185</v>
+        <v>268</v>
       </c>
       <c r="L20" t="s">
-        <v>206</v>
+        <v>303</v>
       </c>
       <c r="M20" t="s">
-        <v>227</v>
+        <v>338</v>
       </c>
       <c r="O20" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="P20" t="s">
-        <v>234</v>
+        <v>362</v>
       </c>
       <c r="Q20" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="R20" t="s">
-        <v>260</v>
+        <v>391</v>
       </c>
       <c r="S20" t="s">
-        <v>273</v>
+        <v>419</v>
       </c>
       <c r="T20" t="s">
-        <v>284</v>
+        <v>433</v>
       </c>
       <c r="U20" t="s">
-        <v>287</v>
+        <v>440</v>
       </c>
       <c r="V20" t="s">
-        <v>286</v>
+        <v>441</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="AA20" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="AB20" t="s">
-        <v>317</v>
+        <v>486</v>
       </c>
       <c r="AC20" t="s">
-        <v>319</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2921,73 +3446,73 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="F21" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G21" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H21" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="J21" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K21" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="L21" t="s">
-        <v>207</v>
+        <v>304</v>
       </c>
       <c r="M21" t="s">
-        <v>228</v>
+        <v>339</v>
       </c>
       <c r="N21" t="s">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="O21" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="P21" t="s">
-        <v>237</v>
+        <v>361</v>
       </c>
       <c r="Q21" t="s">
-        <v>241</v>
+        <v>368</v>
       </c>
       <c r="R21" t="s">
-        <v>261</v>
+        <v>392</v>
       </c>
       <c r="S21" t="s">
-        <v>274</v>
+        <v>408</v>
       </c>
       <c r="U21" t="s">
-        <v>287</v>
+        <v>441</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>307</v>
+        <v>461</v>
       </c>
       <c r="AA21" t="s">
-        <v>241</v>
+        <v>368</v>
       </c>
       <c r="AB21" t="s">
-        <v>314</v>
+        <v>483</v>
       </c>
       <c r="AC21" t="s">
-        <v>318</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2995,79 +3520,1145 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="F22" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="G22" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
       <c r="H22" t="s">
-        <v>153</v>
-      </c>
-      <c r="I22" t="s">
-        <v>164</v>
+        <v>216</v>
       </c>
       <c r="J22" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="K22" t="s">
-        <v>187</v>
+        <v>270</v>
       </c>
       <c r="L22" t="s">
-        <v>208</v>
+        <v>305</v>
       </c>
       <c r="M22" t="s">
-        <v>229</v>
+        <v>340</v>
+      </c>
+      <c r="N22" t="s">
+        <v>355</v>
       </c>
       <c r="O22" t="s">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="P22" t="s">
-        <v>234</v>
+        <v>364</v>
       </c>
       <c r="Q22" t="s">
-        <v>239</v>
+        <v>370</v>
       </c>
       <c r="R22" t="s">
-        <v>262</v>
+        <v>393</v>
       </c>
       <c r="S22" t="s">
-        <v>273</v>
-      </c>
-      <c r="T22" t="s">
-        <v>285</v>
+        <v>410</v>
       </c>
       <c r="U22" t="s">
-        <v>287</v>
-      </c>
-      <c r="V22" t="s">
-        <v>286</v>
+        <v>440</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
+        <v>462</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>370</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>483</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>155</v>
+      </c>
+      <c r="F23" t="s">
+        <v>185</v>
+      </c>
+      <c r="G23" t="s">
+        <v>195</v>
+      </c>
+      <c r="H23" t="s">
+        <v>217</v>
+      </c>
+      <c r="J23" t="s">
+        <v>248</v>
+      </c>
+      <c r="K23" t="s">
+        <v>271</v>
+      </c>
+      <c r="L23" t="s">
+        <v>306</v>
+      </c>
+      <c r="M23" t="s">
+        <v>341</v>
+      </c>
+      <c r="O23" t="s">
+        <v>358</v>
+      </c>
+      <c r="P23" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>369</v>
+      </c>
+      <c r="R23" t="s">
+        <v>394</v>
+      </c>
+      <c r="S23" t="s">
+        <v>411</v>
+      </c>
+      <c r="U23" t="s">
+        <v>441</v>
+      </c>
+      <c r="W23" t="s">
+        <v>2</v>
+      </c>
+      <c r="X23" t="s">
+        <v>463</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>481</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>485</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" t="s">
+        <v>186</v>
+      </c>
+      <c r="G24" t="s">
+        <v>195</v>
+      </c>
+      <c r="H24" t="s">
+        <v>218</v>
+      </c>
+      <c r="I24" t="s">
+        <v>242</v>
+      </c>
+      <c r="J24" t="s">
+        <v>248</v>
+      </c>
+      <c r="K24" t="s">
+        <v>272</v>
+      </c>
+      <c r="L24" t="s">
+        <v>307</v>
+      </c>
+      <c r="M24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N24" t="s">
+        <v>355</v>
+      </c>
+      <c r="O24" t="s">
+        <v>359</v>
+      </c>
+      <c r="P24" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>371</v>
+      </c>
+      <c r="R24" t="s">
+        <v>395</v>
+      </c>
+      <c r="S24" t="s">
+        <v>408</v>
+      </c>
+      <c r="T24" t="s">
+        <v>434</v>
+      </c>
+      <c r="U24" t="s">
+        <v>440</v>
+      </c>
+      <c r="V24" t="s">
+        <v>440</v>
+      </c>
+      <c r="W24" t="s">
+        <v>2</v>
+      </c>
+      <c r="X24" t="s">
+        <v>464</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>371</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>484</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>153</v>
+      </c>
+      <c r="F25" t="s">
+        <v>155</v>
+      </c>
+      <c r="G25" t="s">
+        <v>195</v>
+      </c>
+      <c r="H25" t="s">
+        <v>219</v>
+      </c>
+      <c r="J25" t="s">
+        <v>248</v>
+      </c>
+      <c r="K25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L25" t="s">
         <v>308</v>
       </c>
-      <c r="AA22" t="s">
-        <v>239</v>
-      </c>
-      <c r="AB22" t="s">
+      <c r="M25" t="s">
+        <v>343</v>
+      </c>
+      <c r="O25" t="s">
+        <v>358</v>
+      </c>
+      <c r="P25" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>372</v>
+      </c>
+      <c r="R25" t="s">
+        <v>396</v>
+      </c>
+      <c r="S25" t="s">
+        <v>411</v>
+      </c>
+      <c r="U25" t="s">
+        <v>440</v>
+      </c>
+      <c r="W25" t="s">
+        <v>2</v>
+      </c>
+      <c r="X25" t="s">
+        <v>465</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>482</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>485</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" t="s">
+        <v>124</v>
+      </c>
+      <c r="E26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" t="s">
+        <v>195</v>
+      </c>
+      <c r="H26" t="s">
+        <v>220</v>
+      </c>
+      <c r="J26" t="s">
+        <v>249</v>
+      </c>
+      <c r="K26" t="s">
+        <v>274</v>
+      </c>
+      <c r="L26" t="s">
+        <v>309</v>
+      </c>
+      <c r="M26" t="s">
+        <v>344</v>
+      </c>
+      <c r="N26" t="s">
+        <v>355</v>
+      </c>
+      <c r="O26" t="s">
+        <v>358</v>
+      </c>
+      <c r="P26" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>368</v>
+      </c>
+      <c r="R26" t="s">
+        <v>397</v>
+      </c>
+      <c r="S26" t="s">
+        <v>418</v>
+      </c>
+      <c r="U26" t="s">
+        <v>440</v>
+      </c>
+      <c r="W26" t="s">
+        <v>2</v>
+      </c>
+      <c r="X26" t="s">
+        <v>466</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>368</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>483</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" t="s">
+        <v>160</v>
+      </c>
+      <c r="G27" t="s">
+        <v>195</v>
+      </c>
+      <c r="H27" t="s">
+        <v>221</v>
+      </c>
+      <c r="J27" t="s">
+        <v>249</v>
+      </c>
+      <c r="K27" t="s">
+        <v>275</v>
+      </c>
+      <c r="L27" t="s">
+        <v>310</v>
+      </c>
+      <c r="M27" t="s">
+        <v>345</v>
+      </c>
+      <c r="N27" t="s">
+        <v>355</v>
+      </c>
+      <c r="O27" t="s">
+        <v>358</v>
+      </c>
+      <c r="P27" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>370</v>
+      </c>
+      <c r="R27" t="s">
+        <v>398</v>
+      </c>
+      <c r="S27" t="s">
+        <v>420</v>
+      </c>
+      <c r="U27" t="s">
+        <v>440</v>
+      </c>
+      <c r="W27" t="s">
+        <v>2</v>
+      </c>
+      <c r="X27" t="s">
+        <v>467</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>370</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>484</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" t="s">
+        <v>188</v>
+      </c>
+      <c r="G28" t="s">
+        <v>195</v>
+      </c>
+      <c r="H28" t="s">
+        <v>222</v>
+      </c>
+      <c r="I28" t="s">
+        <v>243</v>
+      </c>
+      <c r="J28" t="s">
+        <v>248</v>
+      </c>
+      <c r="K28" t="s">
+        <v>276</v>
+      </c>
+      <c r="L28" t="s">
+        <v>311</v>
+      </c>
+      <c r="M28" t="s">
+        <v>346</v>
+      </c>
+      <c r="O28" t="s">
+        <v>357</v>
+      </c>
+      <c r="P28" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>367</v>
+      </c>
+      <c r="R28" t="s">
+        <v>399</v>
+      </c>
+      <c r="S28" t="s">
+        <v>410</v>
+      </c>
+      <c r="T28" t="s">
+        <v>435</v>
+      </c>
+      <c r="U28" t="s">
+        <v>440</v>
+      </c>
+      <c r="V28" t="s">
+        <v>440</v>
+      </c>
+      <c r="W28" t="s">
+        <v>2</v>
+      </c>
+      <c r="X28" t="s">
+        <v>468</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>483</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" t="s">
+        <v>185</v>
+      </c>
+      <c r="G29" t="s">
+        <v>195</v>
+      </c>
+      <c r="H29" t="s">
+        <v>223</v>
+      </c>
+      <c r="J29" t="s">
+        <v>248</v>
+      </c>
+      <c r="K29" t="s">
+        <v>277</v>
+      </c>
+      <c r="L29" t="s">
+        <v>312</v>
+      </c>
+      <c r="M29" t="s">
+        <v>347</v>
+      </c>
+      <c r="N29" t="s">
+        <v>355</v>
+      </c>
+      <c r="O29" t="s">
+        <v>358</v>
+      </c>
+      <c r="P29" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>370</v>
+      </c>
+      <c r="R29" t="s">
+        <v>400</v>
+      </c>
+      <c r="S29" t="s">
+        <v>408</v>
+      </c>
+      <c r="U29" t="s">
+        <v>441</v>
+      </c>
+      <c r="W29" t="s">
+        <v>2</v>
+      </c>
+      <c r="X29" t="s">
+        <v>469</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>370</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>483</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" t="s">
+        <v>161</v>
+      </c>
+      <c r="F30" t="s">
+        <v>189</v>
+      </c>
+      <c r="G30" t="s">
+        <v>195</v>
+      </c>
+      <c r="H30" t="s">
+        <v>224</v>
+      </c>
+      <c r="I30" t="s">
+        <v>244</v>
+      </c>
+      <c r="J30" t="s">
+        <v>249</v>
+      </c>
+      <c r="K30" t="s">
+        <v>278</v>
+      </c>
+      <c r="L30" t="s">
+        <v>313</v>
+      </c>
+      <c r="M30" t="s">
+        <v>348</v>
+      </c>
+      <c r="N30" t="s">
+        <v>356</v>
+      </c>
+      <c r="O30" t="s">
+        <v>357</v>
+      </c>
+      <c r="P30" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>367</v>
+      </c>
+      <c r="R30" t="s">
+        <v>401</v>
+      </c>
+      <c r="S30" t="s">
+        <v>408</v>
+      </c>
+      <c r="T30" t="s">
+        <v>436</v>
+      </c>
+      <c r="U30" t="s">
+        <v>440</v>
+      </c>
+      <c r="V30" t="s">
+        <v>440</v>
+      </c>
+      <c r="W30" t="s">
+        <v>2</v>
+      </c>
+      <c r="X30" t="s">
+        <v>470</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>484</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" t="s">
+        <v>195</v>
+      </c>
+      <c r="H31" t="s">
+        <v>225</v>
+      </c>
+      <c r="I31" t="s">
+        <v>245</v>
+      </c>
+      <c r="J31" t="s">
+        <v>249</v>
+      </c>
+      <c r="K31" t="s">
+        <v>279</v>
+      </c>
+      <c r="L31" t="s">
+        <v>314</v>
+      </c>
+      <c r="M31" t="s">
+        <v>349</v>
+      </c>
+      <c r="O31" t="s">
+        <v>357</v>
+      </c>
+      <c r="P31" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>367</v>
+      </c>
+      <c r="R31" t="s">
+        <v>402</v>
+      </c>
+      <c r="S31" t="s">
+        <v>419</v>
+      </c>
+      <c r="T31" t="s">
+        <v>437</v>
+      </c>
+      <c r="U31" t="s">
+        <v>440</v>
+      </c>
+      <c r="V31" t="s">
+        <v>441</v>
+      </c>
+      <c r="W31" t="s">
+        <v>2</v>
+      </c>
+      <c r="X31" t="s">
+        <v>471</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>486</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" t="s">
+        <v>195</v>
+      </c>
+      <c r="H32" t="s">
+        <v>226</v>
+      </c>
+      <c r="J32" t="s">
+        <v>248</v>
+      </c>
+      <c r="K32" t="s">
+        <v>280</v>
+      </c>
+      <c r="L32" t="s">
+        <v>315</v>
+      </c>
+      <c r="M32" t="s">
+        <v>350</v>
+      </c>
+      <c r="O32" t="s">
+        <v>358</v>
+      </c>
+      <c r="P32" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>369</v>
+      </c>
+      <c r="R32" t="s">
+        <v>403</v>
+      </c>
+      <c r="S32" t="s">
+        <v>411</v>
+      </c>
+      <c r="U32" t="s">
+        <v>440</v>
+      </c>
+      <c r="W32" t="s">
+        <v>2</v>
+      </c>
+      <c r="X32" t="s">
+        <v>472</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>481</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>485</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" t="s">
+        <v>191</v>
+      </c>
+      <c r="G33" t="s">
+        <v>195</v>
+      </c>
+      <c r="H33" t="s">
+        <v>227</v>
+      </c>
+      <c r="J33" t="s">
+        <v>249</v>
+      </c>
+      <c r="K33" t="s">
+        <v>281</v>
+      </c>
+      <c r="L33" t="s">
+        <v>316</v>
+      </c>
+      <c r="M33" t="s">
+        <v>351</v>
+      </c>
+      <c r="N33" t="s">
+        <v>355</v>
+      </c>
+      <c r="O33" t="s">
+        <v>358</v>
+      </c>
+      <c r="P33" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>370</v>
+      </c>
+      <c r="R33" t="s">
+        <v>404</v>
+      </c>
+      <c r="S33" t="s">
+        <v>421</v>
+      </c>
+      <c r="U33" t="s">
+        <v>440</v>
+      </c>
+      <c r="W33" t="s">
+        <v>2</v>
+      </c>
+      <c r="X33" t="s">
+        <v>473</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>477</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>480</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>370</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>484</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" t="s">
+        <v>132</v>
+      </c>
+      <c r="E34" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" t="s">
+        <v>192</v>
+      </c>
+      <c r="G34" t="s">
+        <v>195</v>
+      </c>
+      <c r="H34" t="s">
+        <v>228</v>
+      </c>
+      <c r="J34" t="s">
+        <v>249</v>
+      </c>
+      <c r="K34" t="s">
+        <v>282</v>
+      </c>
+      <c r="L34" t="s">
         <v>317</v>
       </c>
-      <c r="AC22" t="s">
+      <c r="M34" t="s">
+        <v>352</v>
+      </c>
+      <c r="O34" t="s">
+        <v>358</v>
+      </c>
+      <c r="P34" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>372</v>
+      </c>
+      <c r="R34" t="s">
+        <v>405</v>
+      </c>
+      <c r="S34" t="s">
+        <v>411</v>
+      </c>
+      <c r="U34" t="s">
+        <v>440</v>
+      </c>
+      <c r="W34" t="s">
+        <v>2</v>
+      </c>
+      <c r="X34" t="s">
+        <v>474</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>482</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>485</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" t="s">
+        <v>165</v>
+      </c>
+      <c r="F35" t="s">
+        <v>193</v>
+      </c>
+      <c r="G35" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" t="s">
+        <v>229</v>
+      </c>
+      <c r="I35" t="s">
+        <v>246</v>
+      </c>
+      <c r="J35" t="s">
+        <v>249</v>
+      </c>
+      <c r="K35" t="s">
+        <v>283</v>
+      </c>
+      <c r="L35" t="s">
+        <v>318</v>
+      </c>
+      <c r="M35" t="s">
+        <v>353</v>
+      </c>
+      <c r="O35" t="s">
+        <v>357</v>
+      </c>
+      <c r="P35" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>367</v>
+      </c>
+      <c r="R35" t="s">
+        <v>406</v>
+      </c>
+      <c r="S35" t="s">
+        <v>422</v>
+      </c>
+      <c r="T35" t="s">
+        <v>438</v>
+      </c>
+      <c r="U35" t="s">
+        <v>440</v>
+      </c>
+      <c r="V35" t="s">
+        <v>440</v>
+      </c>
+      <c r="W35" t="s">
+        <v>2</v>
+      </c>
+      <c r="X35" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>486</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" t="s">
+        <v>166</v>
+      </c>
+      <c r="F36" t="s">
+        <v>194</v>
+      </c>
+      <c r="G36" t="s">
+        <v>195</v>
+      </c>
+      <c r="H36" t="s">
+        <v>230</v>
+      </c>
+      <c r="I36" t="s">
+        <v>247</v>
+      </c>
+      <c r="J36" t="s">
+        <v>248</v>
+      </c>
+      <c r="K36" t="s">
+        <v>284</v>
+      </c>
+      <c r="L36" t="s">
         <v>319</v>
+      </c>
+      <c r="M36" t="s">
+        <v>354</v>
+      </c>
+      <c r="O36" t="s">
+        <v>357</v>
+      </c>
+      <c r="P36" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>367</v>
+      </c>
+      <c r="R36" t="s">
+        <v>407</v>
+      </c>
+      <c r="S36" t="s">
+        <v>410</v>
+      </c>
+      <c r="T36" t="s">
+        <v>439</v>
+      </c>
+      <c r="U36" t="s">
+        <v>440</v>
+      </c>
+      <c r="V36" t="s">
+        <v>440</v>
+      </c>
+      <c r="W36" t="s">
+        <v>2</v>
+      </c>
+      <c r="X36" t="s">
+        <v>476</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>483</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>84873</t>
+          <t>302189</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82656</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t xml:space="preserve">NIDIA ADME </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,32 +756,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6671055229</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>C. TENOTITLAN 4418</t>
-        </is>
-      </c>
+          <t>6671760805</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30-11-1979</t>
+          <t>01-10-1977</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ALBERTOTOMARQUEZ79@HOTMAIL.COM</t>
+          <t>NIDIAMEDINA@LIVE.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12-04-2022 08:01:19</t>
+          <t>05-07-2025 06:34:10</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -802,12 +798,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>16-02-2026 04:14:14</t>
+          <t>22-02-2026 14:25:33</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>22-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -824,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26040522368800002698</t>
+          <t>26040522564200003144</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -832,11 +828,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1899</t>
@@ -856,12 +848,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>338748</t>
+          <t>84873</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>82656</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +863,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZEL VALERIA </t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MENDIVIL</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,75 +883,67 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6673260503</t>
+          <t>6671055229</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANUBIO </t>
+          <t>C. TENOTITLAN 4418</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>18-12-2008</t>
+          <t>30-11-1979</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ITZELPEREZ1812@GMAIL.COM</t>
+          <t>ALBERTOTOMARQUEZ79@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>28-01-2026 14:48:02</t>
+          <t>12-04-2022 08:01:19</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:35</t>
+          <t>16-02-2026 04:14:14</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>16-02-2026 13:40:08</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -967,7 +951,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26040522389000002737</t>
+          <t>26040522368800002698</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -977,12 +961,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -999,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>339855</t>
+          <t>338748</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t xml:space="preserve">ITZEL VALERIA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAS </t>
+          <t>MENDIVIL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,63 +1018,75 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6681452661</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6673260503</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DANUBIO </t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>06-12-1998</t>
+          <t>18-12-2008</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JUAN18752@GMAIL.COM</t>
+          <t>ITZELPEREZ1812@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 05:48:09</t>
+          <t>28-01-2026 14:48:02</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 05:49:53</t>
+          <t>16-02-2026 13:40:35</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>16-02-2026 13:40:08</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1098,36 +1094,44 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26040521997910001841</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26040522389000002737</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>98101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>95858</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAHI DE MARIA </t>
+          <t>DANIEL ALBERTO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUIAR </t>
+          <t xml:space="preserve">VIZCARRA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,53 +1161,57 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6674761021</t>
+          <t>6675383330</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUGAMBILIAS </t>
+          <t>C. GABRIELA MISTRAL 3445</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22-12-2001</t>
+          <t>17-05-1998</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SARAHIAGUIAR001@GMAIL.COM</t>
+          <t>DANIELVIZCARRA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-02-2026 18:57:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>06-06-2022 19:25:07</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:53</t>
+          <t>02-02-2026 17:55:17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1211,21 +1219,13 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-02-2026 18:58:21</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1233,14 +1233,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26040522021440001894</t>
+          <t>26040522019480001886</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340598</t>
+          <t>338906</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAURA LILIA </t>
+          <t xml:space="preserve">ALMA LETICIA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONTIVEROS </t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUARTE </t>
+          <t>FIERROS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,10 +1435,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6673537007</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6672011841</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACHIGULATO </t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1446,56 +1450,60 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>17-02-2009</t>
+          <t>04-03-1983</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
+          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-02-2026 14:38:21</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>28-01-2026 19:52:18</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-02-2026 14:39:22</t>
+          <t>09-02-2026 18:05:21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>09-02-2026 18:04:48</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1503,14 +1511,18 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26040522041570001940</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26040522205360002366</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1527,12 +1539,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>98101</t>
+          <t>340598</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>95858</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DANIEL ALBERTO</t>
+          <t xml:space="preserve">LAURA LILIA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIZCARRA </t>
+          <t xml:space="preserve">ONTIVEROS </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">DUARTE </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,32 +1574,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6675383330</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>C. GABRIELA MISTRAL 3445</t>
-        </is>
-      </c>
+          <t>6673537007</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>17-05-1998</t>
+          <t>17-02-2009</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DANIELVIZCARRA@HOTMAIL.COM</t>
+          <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>06-06-2022 19:25:07</t>
+          <t>03-02-2026 14:38:21</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1602,22 +1610,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 17:55:17</t>
+          <t>03-02-2026 14:39:22</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1634,14 +1642,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26040522019480001886</t>
+          <t>26040522041570001940</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1658,12 +1666,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340980</t>
+          <t>340164</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1673,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">DYLAN ARTURO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t xml:space="preserve">RUBIO </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1693,7 +1701,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6673450501</t>
+          <t>6674732132</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1704,17 +1712,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>25-09-2010</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
+          <t>DYLANRUBIO2509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>04-02-2026 13:04:54</t>
+          <t>02-02-2026 14:14:23</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1739,12 +1747,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-02-2026 13:06:15</t>
+          <t>02-02-2026 14:15:24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1761,7 +1769,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26040522074180002020</t>
+          <t>26040522012290001872</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1785,12 +1793,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>338906</t>
+          <t>338858</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1800,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMA LETICIA </t>
+          <t xml:space="preserve">MANUEL FERNANDO </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t xml:space="preserve">LAMAS </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FIERROS</t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1820,12 +1828,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6672011841</t>
+          <t>6674956589</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACHIGULATO </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1835,17 +1843,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>04-03-1983</t>
+          <t>22-06-2005</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
+          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>28-01-2026 19:52:18</t>
+          <t>28-01-2026 17:57:35</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1856,7 +1864,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1866,17 +1874,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-02-2026 18:05:21</t>
+          <t>03-02-2026 18:15:55</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>09-02-2026 18:04:48</t>
+          <t>03-02-2026 18:15:25</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1896,7 +1904,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26040522205360002366</t>
+          <t>26040522052400001978</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1904,7 +1912,11 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>499</t>
@@ -1924,12 +1936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340164</t>
+          <t>340619</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1951,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DYLAN ARTURO </t>
+          <t xml:space="preserve">JOSE RAUL </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBIO </t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,10 +1971,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6674732132</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6672537304</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACHIGUALTO </t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1970,56 +1986,60 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25-09-2010</t>
+          <t>01-09-1999</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>DYLANRUBIO2509@GMAIL.COM</t>
+          <t>JRAULMV1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 14:14:23</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>03-02-2026 15:16:06</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-02-2026 14:15:24</t>
+          <t>03-02-2026 15:23:17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-02-2026 15:21:47</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2027,36 +2047,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26040522012290001872</t>
+          <t>26040522042820001942</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>338858</t>
+          <t>341050</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,17 +2086,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUEL FERNANDO </t>
+          <t xml:space="preserve">JESUS IVAN </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMAS </t>
+          <t>REATIGA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t>ARCE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2086,75 +2106,67 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6674956589</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRES </t>
-        </is>
-      </c>
+          <t>6675777773</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-06-2005</t>
+          <t>23-03-2011</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
+          <t>JESUSIVANREATIGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>28-01-2026 17:57:35</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>04-02-2026 15:49:35</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 18:15:55</t>
+          <t>04-02-2026 15:52:13</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>03-02-2026 18:15:25</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2162,44 +2174,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26040522052400001978</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522078180002033</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341050</t>
+          <t>341744</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2209,17 +2213,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS IVAN </t>
+          <t xml:space="preserve">PEDRO </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>REATIGA</t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ARCE</t>
+          <t xml:space="preserve">HARO </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2229,7 +2233,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6675777773</t>
+          <t>3221713510</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,17 +2244,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23-03-2011</t>
+          <t>12-12-1974</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JESUSIVANREATIGA@GMAIL.COM</t>
+          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-02-2026 15:49:35</t>
+          <t>07-02-2026 07:59:31</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2265,22 +2269,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-02-2026 15:52:13</t>
+          <t>07-02-2026 08:01:13</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2297,36 +2301,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26040522078180002033</t>
+          <t>26040522155670002240</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340619</t>
+          <t>341657</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2336,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE RAUL </t>
+          <t xml:space="preserve">KEVIN RICARDO </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2356,12 +2360,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6672537304</t>
+          <t>3224537874</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACHIGUALTO </t>
+          <t xml:space="preserve">LA ESTANCIA </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2371,17 +2375,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>01-09-1999</t>
+          <t>05-08-1995</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JRAULMV1@GMAIL.COM</t>
+          <t>DISTRITOTRECEE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-02-2026 15:16:06</t>
+          <t>06-02-2026 18:05:27</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2402,17 +2406,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-02-2026 15:23:17</t>
+          <t>06-02-2026 18:09:06</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>03-02-2026 15:21:47</t>
+          <t>06-02-2026 18:08:40</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2432,7 +2436,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26040522042820001942</t>
+          <t>26040522144380002227</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2456,12 +2460,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341744</t>
+          <t>339855</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>17673</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2471,17 +2475,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t xml:space="preserve">JUAN PABLO </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARO </t>
+          <t xml:space="preserve">SALAS </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2491,7 +2495,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3221713510</t>
+          <t>6681452661</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2502,24 +2506,20 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12-12-1974</t>
+          <t>06-12-1998</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
+          <t>JUAN18752@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>07-02-2026 07:59:31</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 05:48:09</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -2527,28 +2527,28 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>07-02-2026 08:01:13</t>
+          <t>02-02-2026 05:49:53</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>02-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2559,36 +2559,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26040522155670002240</t>
+          <t>26040521997910001841</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>342397</t>
+          <t>341829</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2598,17 +2598,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t>EDGAR FRANCISCO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEYVA </t>
+          <t xml:space="preserve">MANZANO </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2618,10 +2618,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6674049839</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6676987648</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BLVD FLOR DE LIZ</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2629,56 +2633,60 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15-10-1992</t>
+          <t>15-06-1994</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
+          <t>EDGAR.VLA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:08</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>07-02-2026 13:08:56</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>11-02-2026 18:23:52</t>
+          <t>07-02-2026 13:12:58</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>07-02-2026 13:12:39</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2686,27 +2694,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26040522273970002541</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Pedro Fernando  Salas RECEPCION</t>
-        </is>
-      </c>
+          <t>26040522161580002258</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2718,12 +2718,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341657</t>
+          <t>342397</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2733,17 +2733,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN RICARDO </t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">LEYVA </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2753,14 +2753,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3224537874</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA ESTANCIA </t>
-        </is>
-      </c>
+          <t>6674049839</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2768,60 +2764,56 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>05-08-1995</t>
+          <t>15-10-1992</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>DISTRITOTRECEE@GMAIL.COM</t>
+          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>06-02-2026 18:05:27</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>09-02-2026 18:34:08</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>06-02-2026 18:09:06</t>
+          <t>11-02-2026 18:23:52</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>06-02-2026 18:08:40</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2829,14 +2821,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26040522144380002227</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26040522273970002541</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Pedro Fernando  Salas RECEPCION</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2853,12 +2853,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>341829</t>
+          <t>340357</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2868,17 +2868,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EDGAR FRANCISCO</t>
+          <t xml:space="preserve">SARAHI DE MARIA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANO </t>
+          <t xml:space="preserve">AGUIAR </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2888,32 +2888,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6676987648</t>
+          <t>6674761021</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>BLVD FLOR DE LIZ</t>
+          <t xml:space="preserve">BUGAMBILIAS </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>15-06-1994</t>
+          <t>22-12-2001</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>EDGAR.VLA@HOTMAIL.COM</t>
+          <t>SARAHIAGUIAR001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>07-02-2026 13:08:56</t>
+          <t>02-02-2026 18:57:00</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2934,17 +2934,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>07-02-2026 13:12:58</t>
+          <t>02-02-2026 18:58:53</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>07-02-2026 13:12:39</t>
+          <t>02-02-2026 18:58:21</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26040522161580002258</t>
+          <t>26040522021440001894</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -2976,24 +2976,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342743</t>
+          <t>342326</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3003,17 +3003,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCTAVIANO </t>
+          <t xml:space="preserve">MARIAN </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDA </t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3023,32 +3023,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6731436529</t>
+          <t>6675145803</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRRANOVA </t>
+          <t xml:space="preserve">VILLAS DEL RIO </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20-11-2000</t>
+          <t>21-12-1999</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
+          <t>MARIANONTES125@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10-02-2026 17:15:49</t>
+          <t>09-02-2026 17:29:11</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3069,17 +3069,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10-02-2026 17:22:40</t>
+          <t>09-02-2026 17:30:56</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>10-02-2026 17:22:03</t>
+          <t>09-02-2026 17:30:19</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26040522239600002442</t>
+          <t>26040522202510002352</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3111,24 +3111,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342326</t>
+          <t>342743</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3138,17 +3138,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIAN </t>
+          <t xml:space="preserve">OCTAVIANO </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t xml:space="preserve">SAUCEDA </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3158,32 +3158,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6675145803</t>
+          <t>6731436529</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAS DEL RIO </t>
+          <t xml:space="preserve">TRRANOVA </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21-12-1999</t>
+          <t>20-11-2000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MARIANONTES125@GMAIL.COM</t>
+          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 17:29:11</t>
+          <t>10-02-2026 17:15:49</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3204,17 +3204,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:56</t>
+          <t>10-02-2026 17:22:40</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:19</t>
+          <t>10-02-2026 17:22:03</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26040522202510002352</t>
+          <t>26040522239600002442</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3246,24 +3246,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>344617</t>
+          <t>343530</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTO </t>
+          <t>MAURO EMMANUEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3293,10 +3293,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6671751779</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6674640838</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CULIACANCITO </t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3304,56 +3308,60 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21-02-2000</t>
+          <t>04-04-2005</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ALBERTOROJO21@HOTMAIL.COM</t>
+          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>17-02-2026 17:34:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:28:11</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>17-02-2026 17:35:27</t>
+          <t>13-02-2026 16:30:21</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:29:54</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3361,36 +3369,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26040522438040002865</t>
+          <t>26040522324290002650</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>343530</t>
+          <t>340395</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3400,17 +3408,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MAURO EMMANUEL</t>
+          <t>SARAH FABIOLA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">BORRAZ </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3420,75 +3428,67 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6674640838</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CULIACANCITO </t>
-        </is>
-      </c>
+          <t>6674779002</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>04-04-2005</t>
+          <t>05-10-2004</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
+          <t>SARAHABORRAZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:11</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>02-02-2026 20:56:33</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>13-02-2026 16:30:21</t>
+          <t>05-02-2026 20:14:53</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>13-02-2026 16:29:54</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3496,36 +3496,44 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26040522324290002650</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26040522119630002171</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>343909</t>
+          <t>340980</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3535,17 +3543,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA GUADALUPE </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3555,31 +3563,35 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6672155907</t>
+          <t>6673450501</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>26-10-1982</t>
+          <t>08-10-2007</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PARRAGLORIA321@GMAIL.COM</t>
+          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16-02-2026 04:41:54</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>04-02-2026 13:04:54</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3587,22 +3599,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>16-02-2026 04:45:09</t>
+          <t>04-02-2026 13:06:15</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3619,36 +3631,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26040522369220002705</t>
+          <t>26040522074180002020</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>343908</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3658,17 +3670,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA FERNANDA </t>
+          <t>LUIS JESUS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AMEZQUITA</t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACHADO </t>
+          <t xml:space="preserve">ANGULO </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3678,79 +3690,63 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6862342452</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTA ROCIO </t>
-        </is>
-      </c>
+          <t>6672551941</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>27-01-1995</t>
+          <t>20-01-2010</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
+          <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16-02-2026 14:49:21</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 04:37:58</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-02-2026 14:53:31</t>
+          <t>16-02-2026 04:39:44</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>16-02-2026 14:52:00</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3758,19 +3754,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26040522391260002745</t>
+          <t>26040522369190002704</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3782,12 +3778,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340395</t>
+          <t>343909</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3797,17 +3793,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SARAH FABIOLA</t>
+          <t xml:space="preserve">GLORIA GUADALUPE </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORRAZ </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3817,7 +3813,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6674779002</t>
+          <t>6672155907</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3828,24 +3824,20 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>05-10-2004</t>
+          <t>26-10-1982</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>SARAHABORRAZ05@GMAIL.COM</t>
+          <t>PARRAGLORIA321@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-02-2026 20:56:33</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 04:41:54</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3853,28 +3845,28 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-02-2026 20:14:53</t>
+          <t>16-02-2026 04:45:09</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3885,44 +3877,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26040522119630002171</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522369220002705</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>343908</t>
+          <t>344104</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3932,17 +3916,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LUIS JESUS</t>
+          <t xml:space="preserve">MARIA FERNANDA </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t>AMEZQUITA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGULO </t>
+          <t xml:space="preserve">MACHADO </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3952,63 +3936,79 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6672551941</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6862342452</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA ROCIO </t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20-01-2010</t>
+          <t>27-01-1995</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
+          <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>16-02-2026 04:37:58</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>16-02-2026 14:49:21</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>16-02-2026 04:39:44</t>
+          <t>16-02-2026 14:53:31</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:52:00</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4016,19 +4016,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26040522369190002704</t>
+          <t>26040522391260002745</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4040,12 +4040,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>344702</t>
+          <t>343922</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4055,17 +4055,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLETH </t>
+          <t xml:space="preserve">IRENE </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OROPEZA</t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOMINGUEZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4075,14 +4075,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6671444793</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
-        </is>
-      </c>
+          <t>6674077607</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4090,60 +4086,52 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>27-05-2005</t>
+          <t>19-10-1976</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MARLETH5002@GMAIL.COM</t>
+          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>17-02-2026 20:20:03</t>
+          <t>16-02-2026 06:00:38</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>17-02-2026 20:22:39</t>
+          <t>16-02-2026 06:02:04</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>17-02-2026 20:21:36</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4151,36 +4139,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26040522446310002893</t>
+          <t>26040522371170002712</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>344131</t>
+          <t>343533</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4190,17 +4178,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MILDERED HARUMI</t>
+          <t>JOSE GUADALLUPE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCHA </t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4210,39 +4198,35 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6673878560</t>
+          <t>6673961529</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
+          <t xml:space="preserve">ARGENTINA </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01-09-1992</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
+          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>16-02-2026 15:42:58</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:37:04</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4260,17 +4244,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>18-02-2026 15:55:22</t>
+          <t>13-02-2026 16:39:33</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>18-02-2026 15:33:30</t>
+          <t>13-02-2026 16:39:06</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4290,19 +4274,11 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26040522465030002939</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522324550002655</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>499</t>
@@ -4310,24 +4286,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343922</t>
+          <t>343614</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4337,17 +4313,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRENE </t>
+          <t xml:space="preserve">JUAN FRANCISCO </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4357,31 +4333,35 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6674077607</t>
+          <t>6671911835</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>19-10-1976</t>
+          <t>17-03-2007</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
+          <t>JFX4318@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>16-02-2026 06:00:38</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>13-02-2026 20:07:29</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4389,28 +4369,28 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16-02-2026 06:02:04</t>
+          <t>16-02-2026 19:40:20</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -4421,36 +4401,36 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26040522371170002712</t>
+          <t>26040522408860002801</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>344705</t>
+          <t>344702</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4460,17 +4440,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t xml:space="preserve">MARLETH </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>OROPEZA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">DOMINGUEZ </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4480,12 +4460,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6673290828</t>
+          <t>6671444793</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TERRAZAS</t>
+          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4495,17 +4475,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16-03-2004</t>
+          <t>27-05-2005</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>DIANA_SR16@OUTLOOK.COM</t>
+          <t>MARLETH5002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17-02-2026 20:25:26</t>
+          <t>17-02-2026 20:20:03</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4526,7 +4506,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>17-02-2026 20:27:25</t>
+          <t>17-02-2026 20:22:39</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4536,7 +4516,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>17-02-2026 20:26:49</t>
+          <t>17-02-2026 20:21:36</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4556,7 +4536,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26040522446490002894</t>
+          <t>26040522446310002893</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4568,24 +4548,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>344131</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4595,17 +4575,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOSE GUADALLUPE</t>
+          <t>MILDERED HARUMI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t xml:space="preserve">ROCHA </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4615,35 +4595,39 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6673961529</t>
+          <t>6673878560</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGENTINA </t>
+          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>01-09-1992</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
+          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>13-02-2026 16:37:04</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>16-02-2026 15:42:58</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4661,17 +4645,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:33</t>
+          <t>18-02-2026 15:55:22</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:06</t>
+          <t>18-02-2026 15:33:30</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4691,11 +4675,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26040522324550002655</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26040522465030002939</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>499</t>
@@ -4703,24 +4695,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343614</t>
+          <t>343865</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4730,17 +4722,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN FRANCISCO </t>
+          <t xml:space="preserve">VLADIMIR </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4750,7 +4742,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6671911835</t>
+          <t>6872535687</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4761,17 +4753,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>17-03-2007</t>
+          <t>23-01-2009</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>JFX4318@GMAIL.COM</t>
+          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>13-02-2026 20:07:29</t>
+          <t>15-02-2026 14:10:10</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4786,28 +4778,28 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16-02-2026 19:40:20</t>
+          <t>15-02-2026 14:11:41</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -4818,36 +4810,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26040522408860002801</t>
+          <t>26040522367230002693</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343865</t>
+          <t>344705</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4857,17 +4849,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">VLADIMIR </t>
+          <t xml:space="preserve">DIANA LAURA </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4877,67 +4869,75 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6872535687</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6673290828</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TERRAZAS</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23-01-2009</t>
+          <t>16-03-2004</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
+          <t>DIANA_SR16@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15-02-2026 14:10:10</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>17-02-2026 20:25:26</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>15-02-2026 14:11:41</t>
+          <t>17-02-2026 20:27:25</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>17-02-2026 20:26:49</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4945,19 +4945,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26040522367230002693</t>
+          <t>26040522446490002894</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4969,12 +4969,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>344139</t>
+          <t>343897</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">KATHERINE </t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>OCEGUEDA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5004,28 +5004,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6671456800</t>
+          <t>6671043288</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>05-01-2008</t>
+          <t>13-11-2000</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>KAT0508SAN@GMAIL.COM</t>
+          <t>MIGUELHO13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>16-02-2026 15:58:58</t>
+          <t>15-02-2026 21:36:16</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5040,28 +5040,28 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>16-02-2026 16:00:45</t>
+          <t>19-02-2026 04:36:58</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -5072,14 +5072,22 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26040522394190002754</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>26040522478480002982</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5096,12 +5104,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5111,17 +5119,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS ALONSO </t>
+          <t xml:space="preserve">KATHERINE </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTA </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5131,57 +5139,53 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6721229789</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>CAMPO BELLO</t>
-        </is>
-      </c>
+          <t>6671456800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>08-11-1995</t>
+          <t>05-01-2008</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
+          <t>KAT0508SAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16-02-2026 19:03:39</t>
+          <t>16-02-2026 15:58:58</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>16-02-2026 19:05:32</t>
+          <t>16-02-2026 16:00:45</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5189,21 +5193,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>16-02-2026 19:05:10</t>
-        </is>
-      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5211,36 +5207,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26040522407060002792</t>
+          <t>26040522394190002754</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343906</t>
+          <t>344328</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5250,17 +5246,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA REBECA </t>
+          <t xml:space="preserve">CARLOS ALONSO </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">COTA </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5270,63 +5266,79 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6674722142</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6721229789</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CAMPO BELLO</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>25-11-2005</t>
+          <t>08-11-1995</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ADRIANAPARRA2500@GMAIL.COM</t>
+          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16-02-2026 04:24:57</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>16-02-2026 19:03:39</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>16-02-2026 04:34:04</t>
+          <t>16-02-2026 19:05:32</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:05:10</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5334,24 +5346,536 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26040522369090002701</t>
+          <t>26040522407060002792</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>343906</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21723</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADRIANA REBECA </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARRA </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6674722142</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>25-11-2005</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ADRIANAPARRA2500@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>16-02-2026 04:24:57</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>16-02-2026 04:34:04</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26040522369090002701</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>344617</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>22434</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALBERTO </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROJO </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6671751779</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>21-02-2000</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>ALBERTOROJO21@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:34:00</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:35:27</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26040522438040002865</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>345025</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>87190</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MORELIA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BARCENAS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6675028294</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>31-12-9999</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>more312barcenas@gmail.com</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>03-05-2022 16:58:45</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>03-02-2026 20:16:29</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26040522491060002999</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>345143</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>87308</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>KAREM YAZMIN</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAYAN </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6677974107</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>RIO MOCORITO</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>07-08-1988</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>KARENY1288@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:26:39</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:31:08</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:30:30</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26040522501600003040</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>338906</t>
+          <t>263988</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>61492</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMA LETICIA </t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t xml:space="preserve">RENDON </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FIERROS</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,35 +1435,39 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6672011841</t>
+          <t>6677676285</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACHIGULATO </t>
+          <t xml:space="preserve">BACHIGUALATO </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>04-03-1983</t>
+          <t>02-10-2001</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
+          <t>RENDONCR01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>28-01-2026 19:52:18</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>28-10-2024 20:24:06</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1481,17 +1485,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>09-02-2026 18:05:21</t>
+          <t>23-02-2026 13:36:54</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>09-02-2026 18:04:48</t>
+          <t>23-02-2026 13:36:26</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1511,12 +1515,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26040522205360002366</t>
+          <t>26040522580840003185</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr"/>
@@ -1527,12 +1531,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1670,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340164</t>
+          <t>338858</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DYLAN ARTURO </t>
+          <t xml:space="preserve">MANUEL FERNANDO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBIO </t>
+          <t xml:space="preserve">LAMAS </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,67 +1705,75 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6674732132</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6674956589</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES </t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25-09-2010</t>
+          <t>22-06-2005</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>DYLANRUBIO2509@GMAIL.COM</t>
+          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-02-2026 14:14:23</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>28-01-2026 17:57:35</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-02-2026 14:15:24</t>
+          <t>03-02-2026 18:15:55</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>03-02-2026 18:15:25</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1769,14 +1781,22 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26040522012290001872</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26040522052400001978</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1793,12 +1813,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>338858</t>
+          <t>340164</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUEL FERNANDO </t>
+          <t xml:space="preserve">DYLAN ARTURO </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMAS </t>
+          <t xml:space="preserve">RUBIO </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,75 +1848,67 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6674956589</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRES </t>
-        </is>
-      </c>
+          <t>6674732132</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22-06-2005</t>
+          <t>25-09-2010</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
+          <t>DYLANRUBIO2509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>28-01-2026 17:57:35</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>02-02-2026 14:14:23</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-02-2026 18:15:55</t>
+          <t>02-02-2026 14:15:24</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>03-02-2026 18:15:25</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1904,22 +1916,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26040522052400001978</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522012290001872</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1936,12 +1940,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340619</t>
+          <t>338906</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1951,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE RAUL </t>
+          <t xml:space="preserve">ALMA LETICIA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>FIERROS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1971,32 +1975,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6672537304</t>
+          <t>6672011841</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACHIGUALTO </t>
+          <t xml:space="preserve">BACHIGULATO </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>01-09-1999</t>
+          <t>04-03-1983</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JRAULMV1@GMAIL.COM</t>
+          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-02-2026 15:16:06</t>
+          <t>28-01-2026 19:52:18</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2017,17 +2021,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-02-2026 15:23:17</t>
+          <t>09-02-2026 18:05:21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03-02-2026 15:21:47</t>
+          <t>09-02-2026 18:04:48</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2047,10 +2051,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26040522042820001942</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26040522205360002366</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2059,12 +2067,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2206,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341744</t>
+          <t>340619</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2213,17 +2221,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t xml:space="preserve">JOSE RAUL </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARO </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2233,10 +2241,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3221713510</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6672537304</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACHIGUALTO </t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2244,56 +2256,60 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12-12-1974</t>
+          <t>01-09-1999</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
+          <t>JRAULMV1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>07-02-2026 07:59:31</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>03-02-2026 15:16:06</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>07-02-2026 08:01:13</t>
+          <t>03-02-2026 15:23:17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03-02-2026 15:21:47</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2301,36 +2317,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26040522155670002240</t>
+          <t>26040522042820001942</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341657</t>
+          <t>341744</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2340,17 +2356,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN RICARDO </t>
+          <t xml:space="preserve">PEDRO </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">HARO </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2360,14 +2376,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3224537874</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA ESTANCIA </t>
-        </is>
-      </c>
+          <t>3221713510</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2375,60 +2387,56 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>05-08-1995</t>
+          <t>12-12-1974</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DISTRITOTRECEE@GMAIL.COM</t>
+          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>06-02-2026 18:05:27</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>07-02-2026 07:59:31</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>06-02-2026 18:09:06</t>
+          <t>07-02-2026 08:01:13</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>06-02-2026 18:08:40</t>
-        </is>
-      </c>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2436,24 +2444,24 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26040522144380002227</t>
+          <t>26040522155670002240</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2591,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341829</t>
+          <t>341657</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2598,17 +2606,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EDGAR FRANCISCO</t>
+          <t xml:space="preserve">KEVIN RICARDO </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANO </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2618,12 +2626,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6676987648</t>
+          <t>3224537874</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BLVD FLOR DE LIZ</t>
+          <t xml:space="preserve">LA ESTANCIA </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2633,17 +2641,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15-06-1994</t>
+          <t>05-08-1995</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EDGAR.VLA@HOTMAIL.COM</t>
+          <t>DISTRITOTRECEE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>07-02-2026 13:08:56</t>
+          <t>06-02-2026 18:05:27</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2664,17 +2672,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-02-2026 13:12:58</t>
+          <t>06-02-2026 18:09:06</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>07-02-2026 13:12:39</t>
+          <t>06-02-2026 18:08:40</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2684,7 +2692,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2694,7 +2702,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26040522161580002258</t>
+          <t>26040522144380002227</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2706,7 +2714,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2988,12 +2996,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342326</t>
+          <t>341829</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3003,17 +3011,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIAN </t>
+          <t>EDGAR FRANCISCO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t xml:space="preserve">MANZANO </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3023,32 +3031,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6675145803</t>
+          <t>6676987648</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAS DEL RIO </t>
+          <t>BLVD FLOR DE LIZ</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21-12-1999</t>
+          <t>15-06-1994</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MARIANONTES125@GMAIL.COM</t>
+          <t>EDGAR.VLA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 17:29:11</t>
+          <t>07-02-2026 13:08:56</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3069,17 +3077,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:56</t>
+          <t>07-02-2026 13:12:58</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:19</t>
+          <t>07-02-2026 13:12:39</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3089,7 +3097,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3099,7 +3107,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26040522202510002352</t>
+          <t>26040522161580002258</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3111,24 +3119,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342743</t>
+          <t>342326</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3138,17 +3146,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCTAVIANO </t>
+          <t xml:space="preserve">MARIAN </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDA </t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3158,32 +3166,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6731436529</t>
+          <t>6675145803</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRRANOVA </t>
+          <t xml:space="preserve">VILLAS DEL RIO </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20-11-2000</t>
+          <t>21-12-1999</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
+          <t>MARIANONTES125@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:15:49</t>
+          <t>09-02-2026 17:29:11</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3204,17 +3212,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:22:40</t>
+          <t>09-02-2026 17:30:56</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>10-02-2026 17:22:03</t>
+          <t>09-02-2026 17:30:19</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3224,7 +3232,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3234,7 +3242,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26040522239600002442</t>
+          <t>26040522202510002352</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3246,24 +3254,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>343530</t>
+          <t>342743</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3273,17 +3281,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MAURO EMMANUEL</t>
+          <t xml:space="preserve">OCTAVIANO </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t xml:space="preserve">SAUCEDA </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3293,12 +3301,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6674640838</t>
+          <t>6731436529</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CULIACANCITO </t>
+          <t xml:space="preserve">TRRANOVA </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3308,17 +3316,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>04-04-2005</t>
+          <t>20-11-2000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
+          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:11</t>
+          <t>10-02-2026 17:15:49</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3339,17 +3347,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>13-02-2026 16:30:21</t>
+          <t>10-02-2026 17:22:40</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>13-02-2026 16:29:54</t>
+          <t>10-02-2026 17:22:03</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3359,7 +3367,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3369,7 +3377,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26040522324290002650</t>
+          <t>26040522239600002442</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3393,12 +3401,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340395</t>
+          <t>343891</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3408,17 +3416,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SARAH FABIOLA</t>
+          <t>SETH SEBASTIAN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORRAZ </t>
+          <t xml:space="preserve">SANDOVAL </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3428,67 +3436,79 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6674779002</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6871298029</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUARUTO </t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>05-10-2004</t>
+          <t>04-06-2008</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SARAHABORRAZ05@GMAIL.COM</t>
+          <t>SETHSEBASTIANSANDOVALFLORES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-02-2026 20:56:33</t>
+          <t>15-02-2026 19:53:47</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-02-2026 20:14:53</t>
+          <t>23-02-2026 13:01:00</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>23-02-2026 13:00:32</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3496,7 +3516,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26040522119630002171</t>
+          <t>26040522579910003180</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3504,14 +3524,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3528,12 +3544,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>340980</t>
+          <t>343909</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3543,17 +3559,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">GLORIA GUADALUPE </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3563,35 +3579,31 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6673450501</t>
+          <t>6672155907</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>26-10-1982</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
+          <t>PARRAGLORIA321@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-02-2026 13:04:54</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 04:41:54</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3599,22 +3611,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04-02-2026 13:06:15</t>
+          <t>16-02-2026 04:45:09</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3631,36 +3643,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26040522074180002020</t>
+          <t>26040522369220002705</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>343908</t>
+          <t>340980</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3670,17 +3682,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LUIS JESUS</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGULO </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3690,7 +3702,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6672551941</t>
+          <t>6673450501</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3701,20 +3713,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20-01-2010</t>
+          <t>08-10-2007</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
+          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16-02-2026 04:37:58</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>04-02-2026 13:04:54</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3722,28 +3738,28 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-02-2026 04:39:44</t>
+          <t>04-02-2026 13:06:15</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -3754,36 +3770,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26040522369190002704</t>
+          <t>26040522074180002020</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343909</t>
+          <t>340395</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3793,17 +3809,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA GUADALUPE </t>
+          <t>SARAH FABIOLA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">BORRAZ </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3813,7 +3829,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6672155907</t>
+          <t>6674779002</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3824,20 +3840,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>26-10-1982</t>
+          <t>05-10-2004</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PARRAGLORIA321@GMAIL.COM</t>
+          <t>SARAHABORRAZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>16-02-2026 04:41:54</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>02-02-2026 20:56:33</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3845,28 +3865,28 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>16-02-2026 04:45:09</t>
+          <t>05-02-2026 20:14:53</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3877,24 +3897,32 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26040522369220002705</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26040522119630002171</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4068,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>343922</t>
+          <t>343530</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4055,17 +4083,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRENE </t>
+          <t>MAURO EMMANUEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4075,63 +4103,75 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6674077607</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6674640838</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CULIACANCITO </t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19-10-1976</t>
+          <t>04-04-2005</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
+          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>16-02-2026 06:00:38</t>
+          <t>13-02-2026 16:28:11</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>16-02-2026 06:02:04</t>
+          <t>13-02-2026 16:30:21</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:29:54</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4139,19 +4179,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26040522371170002712</t>
+          <t>26040522324290002650</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4163,12 +4203,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>344702</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4178,17 +4218,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JOSE GUADALLUPE</t>
+          <t xml:space="preserve">MARLETH </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t>OROPEZA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t xml:space="preserve">DOMINGUEZ </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4198,32 +4238,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6673961529</t>
+          <t>6671444793</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGENTINA </t>
+          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>27-05-2005</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
+          <t>MARLETH5002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13-02-2026 16:37:04</t>
+          <t>17-02-2026 20:20:03</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4234,7 +4274,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4244,17 +4284,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:33</t>
+          <t>17-02-2026 20:22:39</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:06</t>
+          <t>17-02-2026 20:21:36</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4264,7 +4304,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4274,7 +4314,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26040522324550002655</t>
+          <t>26040522446310002893</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4286,7 +4326,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4298,12 +4338,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343614</t>
+          <t>343908</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4313,17 +4353,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN FRANCISCO </t>
+          <t>LUIS JESUS</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">ANGULO </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4333,7 +4373,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6671911835</t>
+          <t>6672551941</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4344,24 +4384,20 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17-03-2007</t>
+          <t>20-01-2010</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>JFX4318@GMAIL.COM</t>
+          <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>13-02-2026 20:07:29</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 04:37:58</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4369,28 +4405,28 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16-02-2026 19:40:20</t>
+          <t>16-02-2026 04:39:44</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -4401,36 +4437,36 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26040522408860002801</t>
+          <t>26040522369190002704</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>344702</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4440,17 +4476,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLETH </t>
+          <t xml:space="preserve">ANA LUCIA </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OROPEZA</t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOMINGUEZ </t>
+          <t xml:space="preserve">JUAN QUI </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4460,12 +4496,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6671444793</t>
+          <t>6673938349</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
+          <t xml:space="preserve">AGUARUTO </t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4475,20 +4511,24 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>27-05-2005</t>
+          <t>23-09-2008</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>MARLETH5002@GMAIL.COM</t>
+          <t>ANAJUANQUI08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17-02-2026 20:20:03</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>15-02-2026 19:50:41</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4496,7 +4536,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4506,17 +4546,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>17-02-2026 20:22:39</t>
+          <t>23-02-2026 12:57:58</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>17-02-2026 20:21:36</t>
+          <t>23-02-2026 12:51:21</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4526,7 +4566,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4536,10 +4576,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26040522446310002893</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
+          <t>26040522579820003179</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4548,24 +4592,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>344131</t>
+          <t>343896</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21713</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4575,17 +4619,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MILDERED HARUMI</t>
+          <t xml:space="preserve">KARLA SOFIA </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCHA </t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t>JUAN QUI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4595,12 +4639,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6673878560</t>
+          <t>6677758152</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
+          <t>AGUARUTO</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4610,17 +4654,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>01-09-1992</t>
+          <t>04-12-2010</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
+          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>16-02-2026 15:42:58</t>
+          <t>15-02-2026 21:30:58</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4645,17 +4689,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>18-02-2026 15:55:22</t>
+          <t>23-02-2026 13:06:24</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>18-02-2026 15:33:30</t>
+          <t>23-02-2026 13:05:56</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4675,7 +4719,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26040522465030002939</t>
+          <t>26040522580090003182</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4683,11 +4727,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>499</t>
@@ -4707,12 +4747,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343865</t>
+          <t>343922</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4722,17 +4762,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">VLADIMIR </t>
+          <t xml:space="preserve">IRENE </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4742,35 +4782,31 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6872535687</t>
+          <t>6674077607</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>23-01-2009</t>
+          <t>19-10-1976</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
+          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>15-02-2026 14:10:10</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 06:00:38</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4778,22 +4814,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>15-02-2026 14:11:41</t>
+          <t>16-02-2026 06:02:04</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4810,19 +4846,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26040522367230002693</t>
+          <t>26040522371170002712</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4834,12 +4870,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>344705</t>
+          <t>344131</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4849,17 +4885,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t>MILDERED HARUMI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">ROCHA </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4869,12 +4905,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6673290828</t>
+          <t>6673878560</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TERRAZAS</t>
+          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4884,20 +4920,24 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16-03-2004</t>
+          <t>01-09-1992</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>DIANA_SR16@OUTLOOK.COM</t>
+          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>17-02-2026 20:25:26</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>16-02-2026 15:42:58</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4905,7 +4945,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4915,17 +4955,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>17-02-2026 20:27:25</t>
+          <t>18-02-2026 15:55:22</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17-02-2026 20:26:49</t>
+          <t>18-02-2026 15:33:30</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4935,7 +4975,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4945,11 +4985,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26040522446490002894</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26040522465030002939</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>499</t>
@@ -4957,24 +5005,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343897</t>
+          <t>343533</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4984,17 +5032,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>JOSE GUADALLUPE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OCEGUEDA</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5004,10 +5052,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6671043288</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6673961529</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARGENTINA </t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5015,56 +5067,60 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>13-11-2000</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MIGUELHO13@GMAIL.COM</t>
+          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15-02-2026 21:36:16</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:37:04</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>19-02-2026 04:36:58</t>
+          <t>13-02-2026 16:39:33</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:39:06</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5072,44 +5128,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26040522478480002982</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522324550002655</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344139</t>
+          <t>343614</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5119,17 +5167,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">KATHERINE </t>
+          <t xml:space="preserve">JUAN FRANCISCO </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5139,28 +5187,28 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6671456800</t>
+          <t>6671911835</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>05-01-2008</t>
+          <t>17-03-2007</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>KAT0508SAN@GMAIL.COM</t>
+          <t>JFX4318@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16-02-2026 15:58:58</t>
+          <t>13-02-2026 20:07:29</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5175,17 +5223,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>16-02-2026 16:00:45</t>
+          <t>16-02-2026 19:40:20</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5207,14 +5255,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26040522394190002754</t>
+          <t>26040522408860002801</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5231,12 +5279,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>343865</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5246,17 +5294,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS ALONSO </t>
+          <t xml:space="preserve">VLADIMIR </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTA </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5266,14 +5314,10 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6721229789</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>CAMPO BELLO</t>
-        </is>
-      </c>
+          <t>6872535687</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5281,64 +5325,56 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>08-11-1995</t>
+          <t>23-01-2009</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
+          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>16-02-2026 19:03:39</t>
+          <t>15-02-2026 14:10:10</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>16-02-2026 19:05:32</t>
+          <t>15-02-2026 14:11:41</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>16-02-2026 19:05:10</t>
-        </is>
-      </c>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5346,14 +5382,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26040522407060002792</t>
+          <t>26040522367230002693</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5370,12 +5406,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343906</t>
+          <t>344705</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5385,17 +5421,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA REBECA </t>
+          <t xml:space="preserve">DIANA LAURA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5405,10 +5441,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6674722142</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6673290828</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>TERRAZAS</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5416,52 +5456,60 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>25-11-2005</t>
+          <t>16-03-2004</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ADRIANAPARRA2500@GMAIL.COM</t>
+          <t>DIANA_SR16@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16-02-2026 04:24:57</t>
+          <t>17-02-2026 20:25:26</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>16-02-2026 04:34:04</t>
+          <t>17-02-2026 20:27:25</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>17-02-2026 20:26:49</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5469,14 +5517,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26040522369090002701</t>
+          <t>26040522446490002894</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5493,12 +5541,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344617</t>
+          <t>345887</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>88052</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5508,17 +5556,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTO </t>
+          <t xml:space="preserve">BRAYAN </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJO </t>
+          <t xml:space="preserve">NORIEGA </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">DUARTE </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5528,7 +5576,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6671751779</t>
+          <t>6677804463</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5539,24 +5587,20 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21-02-2000</t>
+          <t>04-03-2010</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ALBERTOROJO21@HOTMAIL.COM</t>
+          <t>NORIEGADUARTEBRAYAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17-02-2026 17:34:00</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>23-02-2026 16:43:27</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5564,28 +5608,28 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>17-02-2026 17:35:27</t>
+          <t>23-02-2026 16:44:27</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5596,14 +5640,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26040522438040002865</t>
+          <t>26040522588220003214</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5620,12 +5664,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>345025</t>
+          <t>345655</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5635,17 +5679,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t>ITZEL PAULINA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BARCENAS</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5655,7 +5699,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6675028294</t>
+          <t>6183256686</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5666,17 +5710,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>31-12-9999</t>
+          <t>10-10-1997</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>more312barcenas@gmail.com</t>
+          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-05-2022 16:58:45</t>
+          <t>23-02-2026 07:26:26</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5687,28 +5731,28 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-02-2026 20:16:29</t>
+          <t>23-02-2026 07:29:03</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5719,163 +5763,1183 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26040522491060002999</t>
+          <t>26040522572610003158</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>343897</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21714</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MIGUEL ANGEL</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>OCEGUEDA</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6671043288</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>13-11-2000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>MIGUELHO13@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>15-02-2026 21:36:16</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>19-02-2026 04:36:58</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26040522478480002982</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>344617</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>22434</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALBERTO </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROJO </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6671751779</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>21-02-2000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ALBERTOROJO21@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:34:00</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>17-02-2026 17:35:27</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26040522438040002865</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>343906</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21723</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADRIANA REBECA </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARRA </t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6674722142</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>25-11-2005</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ADRIANAPARRA2500@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>16-02-2026 04:24:57</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>16-02-2026 04:34:04</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26040522369090002701</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Henry Thomas  Carrasco Cazares</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>344139</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21956</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KATHERINE </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANCHEZ </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6671456800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>05-01-2008</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>KAT0508SAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>16-02-2026 15:58:58</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>16-02-2026 16:00:45</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26040522394190002754</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>344328</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>22145</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLOS ALONSO </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COTA </t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6721229789</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>CAMPO BELLO</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>08-11-1995</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:03:39</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:05:32</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:05:10</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26040522407060002792</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>345025</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>87190</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MORELIA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BARCENAS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6675028294</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>31-12-9999</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>more312barcenas@gmail.com</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>03-05-2022 16:58:45</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>03-02-2026 20:16:29</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26040522491060002999</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>345143</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>87308</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>AZAHARES CUL</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>KAREM YAZMIN</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t xml:space="preserve">PAYAN </t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>MARTINEZ</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>6677974107</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>RIO MOCORITO</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>07-08-1988</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>KARENY1288@HOTMAIL.COM</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>19-02-2026 17:26:39</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>inscripcion promo 199</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>19-02-2026 17:31:08</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>19-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>19-02-2026 17:30:30</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>26040522501600003040</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr">
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>345640</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>87805</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>JOSE GUILLERMO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LEYVA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JACOBO </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6671911283</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>16-02-1991</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>23-02-2026 04:19:03</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>23-02-2026 04:20:44</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26040522565240003147</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>345656</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>87821</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ROJILY VANESSA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6672345223</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>27-03-1982</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>RUCALETA2703@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:31:25</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:33:17</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26040522572650003159</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Henry Thomas  Carrasco Cazares</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>330960</t>
+          <t>98101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>95858</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KARLA JANETH</t>
+          <t>DANIEL ALBERTO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑUELAS </t>
+          <t xml:space="preserve">VIZCARRA </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERALES </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,79 +613,71 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6671284496</t>
+          <t>6675383330</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ESTANCIA</t>
+          <t>C. GABRIELA MISTRAL 3445</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23-10-1995</t>
+          <t>17-05-1998</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>KARLAPERALES23@HOTMAIL.COM</t>
+          <t>DANIELVIZCARRA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>29-12-2025 18:55:46</t>
+          <t>06-06-2022 19:25:07</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17-02-2026 18:46:14</t>
+          <t>02-02-2026 17:55:17</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>17-02-2026 18:45:49</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,18 +685,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26040522442460002883</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522019480001886</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -721,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>302189</t>
+          <t>305321</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99687</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIDIA ADME </t>
+          <t>LESLYE LIBIER</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MEDRANO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,10 +744,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6671760805</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6671399083</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BARRANCOS</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -767,52 +759,64 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>01-10-1977</t>
+          <t>24-01-2002</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NIDIAMEDINA@LIVE.COM</t>
+          <t>MEDRANO_LESLYE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>05-07-2025 06:34:10</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>22-07-2025 10:29:16</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>22-02-2026 14:25:33</t>
+          <t>24-02-2026 13:58:09</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>22-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>24-02-2026 13:56:59</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,28 +824,24 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26040522564200003144</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522619700003290</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>338748</t>
+          <t>302189</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZEL VALERIA </t>
+          <t xml:space="preserve">NIDIA ADME </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MENDIVIL</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,14 +1018,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6673260503</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DANUBIO </t>
-        </is>
-      </c>
+          <t>6671760805</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1033,60 +1029,52 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>18-12-2008</t>
+          <t>01-10-1977</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ITZELPEREZ1812@GMAIL.COM</t>
+          <t>NIDIAMEDINA@LIVE.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28-01-2026 14:48:02</t>
+          <t>05-07-2025 06:34:10</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:35</t>
+          <t>22-02-2026 14:25:33</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>16-02-2026 13:40:08</t>
-        </is>
-      </c>
+          <t>22-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,7 +1082,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26040522389000002737</t>
+          <t>26040522564200003144</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1102,14 +1090,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1126,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>98101</t>
+          <t>338748</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>95858</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DANIEL ALBERTO</t>
+          <t xml:space="preserve">ITZEL VALERIA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIZCARRA </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MENDIVIL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,71 +1145,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6675383330</t>
+          <t>6673260503</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C. GABRIELA MISTRAL 3445</t>
+          <t xml:space="preserve">DANUBIO </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>17-05-1998</t>
+          <t>18-12-2008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>DANIELVIZCARRA@HOTMAIL.COM</t>
+          <t>ITZELPEREZ1812@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>06-06-2022 19:25:07</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>28-01-2026 14:48:02</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 17:55:17</t>
+          <t>16-02-2026 13:40:35</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>16-02-2026 13:40:08</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1233,14 +1221,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26040522019480001886</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26040522389000002737</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1543,12 +1539,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340598</t>
+          <t>330960</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1558,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAURA LILIA </t>
+          <t>KARLA JANETH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONTIVEROS </t>
+          <t xml:space="preserve">PEÑUELAS </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUARTE </t>
+          <t xml:space="preserve">PERALES </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1578,10 +1574,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6673537007</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6671284496</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ESTANCIA</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1589,56 +1589,64 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>17-02-2009</t>
+          <t>23-10-1995</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
+          <t>KARLAPERALES23@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-02-2026 14:38:21</t>
+          <t>29-12-2025 18:55:46</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-02-2026 14:39:22</t>
+          <t>17-02-2026 18:46:14</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>17-02-2026 18:45:49</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1646,14 +1654,18 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26040522041570001940</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26040522442460002883</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1670,12 +1682,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>338858</t>
+          <t>338906</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1685,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUEL FERNANDO </t>
+          <t xml:space="preserve">ALMA LETICIA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMAS </t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t>FIERROS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1705,12 +1717,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6674956589</t>
+          <t>6672011841</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">BACHIGULATO </t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1720,17 +1732,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22-06-2005</t>
+          <t>04-03-1983</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
+          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>28-01-2026 17:57:35</t>
+          <t>28-01-2026 19:52:18</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1741,7 +1753,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1751,17 +1763,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-02-2026 18:15:55</t>
+          <t>09-02-2026 18:05:21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>03-02-2026 18:15:25</t>
+          <t>09-02-2026 18:04:48</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1781,7 +1793,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26040522052400001978</t>
+          <t>26040522205360002366</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1789,11 +1801,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>499</t>
@@ -1940,12 +1948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>338906</t>
+          <t>341050</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMA LETICIA </t>
+          <t xml:space="preserve">JESUS IVAN </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t>REATIGA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FIERROS</t>
+          <t>ARCE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,75 +1983,67 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6672011841</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BACHIGULATO </t>
-        </is>
-      </c>
+          <t>6675777773</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>04-03-1983</t>
+          <t>23-03-2011</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
+          <t>JESUSIVANREATIGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>28-01-2026 19:52:18</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>04-02-2026 15:49:35</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>09-02-2026 18:05:21</t>
+          <t>04-02-2026 15:52:13</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:04:48</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2051,40 +2051,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26040522205360002366</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522078180002033</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341050</t>
+          <t>340619</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2094,17 +2090,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS IVAN </t>
+          <t xml:space="preserve">JOSE RAUL </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>REATIGA</t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ARCE</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2114,10 +2110,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6675777773</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6672537304</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACHIGUALTO </t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2125,56 +2125,60 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>23-03-2011</t>
+          <t>01-09-1999</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JESUSIVANREATIGA@GMAIL.COM</t>
+          <t>JRAULMV1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>04-02-2026 15:49:35</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>03-02-2026 15:16:06</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-02-2026 15:52:13</t>
+          <t>03-02-2026 15:23:17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-02-2026 15:21:47</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2182,14 +2186,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26040522078180002033</t>
+          <t>26040522042820001942</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2206,12 +2210,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340619</t>
+          <t>340598</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2221,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE RAUL </t>
+          <t xml:space="preserve">LAURA LILIA </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">ONTIVEROS </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">DUARTE </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2241,53 +2245,53 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6672537304</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BACHIGUALTO </t>
-        </is>
-      </c>
+          <t>6673537007</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>01-09-1999</t>
+          <t>17-02-2009</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JRAULMV1@GMAIL.COM</t>
+          <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-02-2026 15:16:06</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>03-02-2026 14:38:21</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 15:23:17</t>
+          <t>03-02-2026 14:39:22</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2295,21 +2299,13 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>03-02-2026 15:21:47</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2317,36 +2313,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26040522042820001942</t>
+          <t>26040522041570001940</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341744</t>
+          <t>341657</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2356,17 +2352,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t xml:space="preserve">KEVIN RICARDO </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARO </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2376,10 +2372,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3221713510</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>3224537874</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA ESTANCIA </t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2387,56 +2387,60 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12-12-1974</t>
+          <t>05-08-1995</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
+          <t>DISTRITOTRECEE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>07-02-2026 07:59:31</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>06-02-2026 18:05:27</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>07-02-2026 08:01:13</t>
+          <t>06-02-2026 18:09:06</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>06-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>06-02-2026 18:08:40</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2444,36 +2448,36 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26040522155670002240</t>
+          <t>26040522144380002227</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>339855</t>
+          <t>341829</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2483,17 +2487,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t>EDGAR FRANCISCO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t xml:space="preserve">MANZANO </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAS </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2503,10 +2507,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6681452661</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6676987648</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BLVD FLOR DE LIZ</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2514,52 +2522,60 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>06-12-1998</t>
+          <t>15-06-1994</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JUAN18752@GMAIL.COM</t>
+          <t>EDGAR.VLA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 05:48:09</t>
+          <t>07-02-2026 13:08:56</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 05:49:53</t>
+          <t>07-02-2026 13:12:58</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>07-02-2026 13:12:39</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2567,19 +2583,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26040521997910001841</t>
+          <t>26040522161580002258</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2591,12 +2607,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341657</t>
+          <t>339855</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>17673</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2606,17 +2622,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN RICARDO </t>
+          <t xml:space="preserve">JUAN PABLO </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">SALAS </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2626,14 +2642,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3224537874</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA ESTANCIA </t>
-        </is>
-      </c>
+          <t>6681452661</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2641,60 +2653,52 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>05-08-1995</t>
+          <t>06-12-1998</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>DISTRITOTRECEE@GMAIL.COM</t>
+          <t>JUAN18752@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>06-02-2026 18:05:27</t>
+          <t>02-02-2026 05:48:09</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>06-02-2026 18:09:06</t>
+          <t>02-02-2026 05:49:53</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>06-02-2026 18:08:40</t>
-        </is>
-      </c>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2702,14 +2706,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26040522144380002227</t>
+          <t>26040521997910001841</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2726,12 +2730,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>342397</t>
+          <t>341744</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2741,17 +2745,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t xml:space="preserve">PEDRO </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEYVA </t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t xml:space="preserve">HARO </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2761,7 +2765,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6674049839</t>
+          <t>3221713510</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2772,17 +2776,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15-10-1992</t>
+          <t>12-12-1974</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
+          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:08</t>
+          <t>07-02-2026 07:59:31</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2797,22 +2801,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>11-02-2026 18:23:52</t>
+          <t>07-02-2026 08:01:13</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2829,44 +2833,36 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26040522273970002541</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Pedro Fernando  Salas RECEPCION</t>
-        </is>
-      </c>
+          <t>26040522155670002240</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>338858</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2876,17 +2872,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAHI DE MARIA </t>
+          <t xml:space="preserve">MANUEL FERNANDO </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUIAR </t>
+          <t xml:space="preserve">LAMAS </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2896,12 +2892,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6674761021</t>
+          <t>6674956589</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUGAMBILIAS </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2911,17 +2907,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-12-2001</t>
+          <t>22-06-2005</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>SARAHIAGUIAR001@GMAIL.COM</t>
+          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 18:57:00</t>
+          <t>28-01-2026 17:57:35</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2932,7 +2928,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2942,17 +2938,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:53</t>
+          <t>03-02-2026 18:15:55</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:21</t>
+          <t>03-02-2026 18:15:25</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2962,7 +2958,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2972,11 +2968,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26040522021440001894</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26040522052400001978</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>499</t>
@@ -2996,12 +3000,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341829</t>
+          <t>340357</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3011,17 +3015,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EDGAR FRANCISCO</t>
+          <t xml:space="preserve">SARAHI DE MARIA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANO </t>
+          <t xml:space="preserve">AGUIAR </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3031,32 +3035,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6676987648</t>
+          <t>6674761021</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BLVD FLOR DE LIZ</t>
+          <t xml:space="preserve">BUGAMBILIAS </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>15-06-1994</t>
+          <t>22-12-2001</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>EDGAR.VLA@HOTMAIL.COM</t>
+          <t>SARAHIAGUIAR001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>07-02-2026 13:08:56</t>
+          <t>02-02-2026 18:57:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3077,17 +3081,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>07-02-2026 13:12:58</t>
+          <t>02-02-2026 18:58:53</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>07-02-2026 13:12:39</t>
+          <t>02-02-2026 18:58:21</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3107,7 +3111,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26040522161580002258</t>
+          <t>26040522021440001894</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3119,24 +3123,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342326</t>
+          <t>342397</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3146,17 +3150,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIAN </t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t xml:space="preserve">LEYVA </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3166,75 +3170,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6675145803</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VILLAS DEL RIO </t>
-        </is>
-      </c>
+          <t>6674049839</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21-12-1999</t>
+          <t>15-10-1992</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MARIANONTES125@GMAIL.COM</t>
+          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 17:29:11</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>09-02-2026 18:34:08</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:56</t>
+          <t>11-02-2026 18:23:52</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:30:19</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3242,36 +3238,44 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26040522202510002352</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26040522273970002541</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Pedro Fernando  Salas RECEPCION</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342743</t>
+          <t>340980</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3281,17 +3285,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCTAVIANO </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3301,14 +3305,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6731436529</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRRANOVA </t>
-        </is>
-      </c>
+          <t>6673450501</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3316,60 +3316,56 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20-11-2000</t>
+          <t>08-10-2007</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
+          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10-02-2026 17:15:49</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>04-02-2026 13:04:54</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10-02-2026 17:22:40</t>
+          <t>04-02-2026 13:06:15</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>10-02-2026 17:22:03</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3377,24 +3373,24 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26040522239600002442</t>
+          <t>26040522074180002020</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3667,12 +3663,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340980</t>
+          <t>344104</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3682,17 +3678,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">MARIA FERNANDA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t>AMEZQUITA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">MACHADO </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3702,28 +3698,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6673450501</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>6862342452</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA ROCIO </t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>27-01-1995</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
+          <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-02-2026 13:04:54</t>
+          <t>16-02-2026 14:49:21</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3733,36 +3733,44 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-02-2026 13:06:15</t>
+          <t>16-02-2026 14:53:31</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:52:00</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3770,36 +3778,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26040522074180002020</t>
+          <t>26040522391260002745</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340395</t>
+          <t>343530</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3809,17 +3817,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SARAH FABIOLA</t>
+          <t>MAURO EMMANUEL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORRAZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3829,67 +3837,75 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6674779002</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6674640838</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CULIACANCITO </t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>05-10-2004</t>
+          <t>04-04-2005</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>SARAHABORRAZ05@GMAIL.COM</t>
+          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-02-2026 20:56:33</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:28:11</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-02-2026 20:14:53</t>
+          <t>13-02-2026 16:30:21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:29:54</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3897,44 +3913,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26040522119630002171</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522324290002650</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>344702</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3944,17 +3952,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA FERNANDA </t>
+          <t xml:space="preserve">MARLETH </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AMEZQUITA</t>
+          <t>OROPEZA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACHADO </t>
+          <t xml:space="preserve">DOMINGUEZ </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3964,12 +3972,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6862342452</t>
+          <t>6671444793</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA ROCIO </t>
+          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3979,52 +3987,48 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>27-01-1995</t>
+          <t>27-05-2005</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
+          <t>MARLETH5002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>16-02-2026 14:49:21</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>17-02-2026 20:20:03</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>16-02-2026 14:53:31</t>
+          <t>17-02-2026 20:22:39</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>16-02-2026 14:52:00</t>
+          <t>17-02-2026 20:21:36</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4044,19 +4048,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26040522391260002745</t>
+          <t>26040522446310002893</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4068,12 +4072,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>343530</t>
+          <t>340395</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4083,17 +4087,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MAURO EMMANUEL</t>
+          <t>SARAH FABIOLA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">BORRAZ </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4103,75 +4107,67 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6674640838</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CULIACANCITO </t>
-        </is>
-      </c>
+          <t>6674779002</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>04-04-2005</t>
+          <t>05-10-2004</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
+          <t>SARAHABORRAZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:11</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>02-02-2026 20:56:33</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>13-02-2026 16:30:21</t>
+          <t>05-02-2026 20:14:53</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>13-02-2026 16:29:54</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4179,36 +4175,44 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26040522324290002650</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26040522119630002171</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>344702</t>
+          <t>342743</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4218,17 +4222,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLETH </t>
+          <t xml:space="preserve">OCTAVIANO </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OROPEZA</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOMINGUEZ </t>
+          <t xml:space="preserve">SAUCEDA </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4238,32 +4242,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6671444793</t>
+          <t>6731436529</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
+          <t xml:space="preserve">TRRANOVA </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27-05-2005</t>
+          <t>20-11-2000</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MARLETH5002@GMAIL.COM</t>
+          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17-02-2026 20:20:03</t>
+          <t>10-02-2026 17:15:49</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4274,7 +4278,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4284,17 +4288,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>17-02-2026 20:22:39</t>
+          <t>10-02-2026 17:22:40</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>17-02-2026 20:21:36</t>
+          <t>10-02-2026 17:22:03</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4314,7 +4318,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26040522446310002893</t>
+          <t>26040522239600002442</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4326,7 +4330,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4461,12 +4465,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>343890</t>
+          <t>343533</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21707</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4476,17 +4480,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA LUCIA </t>
+          <t>JOSE GUADALLUPE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMARILLAS </t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN QUI </t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4496,39 +4500,35 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6673938349</t>
+          <t>6673961529</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUARUTO </t>
+          <t xml:space="preserve">ARGENTINA </t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>23-09-2008</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ANAJUANQUI08@GMAIL.COM</t>
+          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15-02-2026 19:50:41</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:37:04</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4546,17 +4546,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>23-02-2026 12:57:58</t>
+          <t>13-02-2026 16:39:33</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>23-02-2026 12:51:21</t>
+          <t>13-02-2026 16:39:06</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4576,14 +4576,10 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26040522579820003179</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522324550002655</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
@@ -4592,24 +4588,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343896</t>
+          <t>343614</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4619,17 +4615,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA SOFIA </t>
+          <t xml:space="preserve">JUAN FRANCISCO </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMARILLAS </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>JUAN QUI</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4639,79 +4635,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6677758152</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>AGUARUTO</t>
-        </is>
-      </c>
+          <t>6671911835</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>04-12-2010</t>
+          <t>17-03-2007</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
+          <t>JFX4318@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>15-02-2026 21:30:58</t>
+          <t>13-02-2026 20:07:29</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>23-02-2026 13:06:24</t>
+          <t>16-02-2026 19:40:20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>23-02-2026 13:05:56</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4719,18 +4703,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26040522580090003182</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522408860002801</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4747,12 +4727,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343922</t>
+          <t>343865</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4762,17 +4742,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRENE </t>
+          <t xml:space="preserve">VLADIMIR </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4782,31 +4762,35 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6674077607</t>
+          <t>6872535687</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19-10-1976</t>
+          <t>23-01-2009</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
+          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16-02-2026 06:00:38</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>15-02-2026 14:10:10</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4814,22 +4798,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16-02-2026 06:02:04</t>
+          <t>15-02-2026 14:11:41</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4846,19 +4830,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26040522371170002712</t>
+          <t>26040522367230002693</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4870,12 +4854,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>344131</t>
+          <t>346066</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>88231</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4885,17 +4869,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MILDERED HARUMI</t>
+          <t>CARLOS RODRIGO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCHA </t>
+          <t>NIEBLAS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4905,79 +4889,63 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6673878560</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
-        </is>
-      </c>
+          <t>6673160433</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01-09-1992</t>
+          <t>13-03-1994</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
+          <t>RODRIGORODRIGO1994RIVERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16-02-2026 15:42:58</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>24-02-2026 06:14:38</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>18-02-2026 15:55:22</t>
+          <t>24-02-2026 06:16:43</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>18-02-2026 15:33:30</t>
-        </is>
-      </c>
+          <t>24-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4985,44 +4953,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26040522465030002939</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522610020003260</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>342326</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5032,17 +4992,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JOSE GUADALLUPE</t>
+          <t xml:space="preserve">MARIAN </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5052,32 +5012,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6673961529</t>
+          <t>6675145803</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGENTINA </t>
+          <t xml:space="preserve">VILLAS DEL RIO </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>21-12-1999</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
+          <t>MARIANONTES125@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>13-02-2026 16:37:04</t>
+          <t>09-02-2026 17:29:11</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5098,17 +5058,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:33</t>
+          <t>09-02-2026 17:30:56</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:06</t>
+          <t>09-02-2026 17:30:19</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5128,7 +5088,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26040522324550002655</t>
+          <t>26040522202510002352</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5140,24 +5100,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343614</t>
+          <t>344131</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5167,17 +5127,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN FRANCISCO </t>
+          <t>MILDERED HARUMI</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">ROCHA </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5187,67 +5147,79 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6671911835</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6673878560</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17-03-2007</t>
+          <t>01-09-1992</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>JFX4318@GMAIL.COM</t>
+          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>13-02-2026 20:07:29</t>
+          <t>16-02-2026 15:42:58</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>16-02-2026 19:40:20</t>
+          <t>18-02-2026 15:55:22</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>18-02-2026 15:33:30</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5255,36 +5227,44 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26040522408860002801</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26040522465030002939</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343865</t>
+          <t>345887</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>88052</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5294,17 +5274,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">VLADIMIR </t>
+          <t xml:space="preserve">BRAYAN </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t xml:space="preserve">NORIEGA </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">DUARTE </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5314,7 +5294,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6872535687</t>
+          <t>6677804463</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5325,24 +5305,20 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>23-01-2009</t>
+          <t>04-03-2010</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
+          <t>NORIEGADUARTEBRAYAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>15-02-2026 14:10:10</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>23-02-2026 16:43:27</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5350,28 +5326,28 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>15-02-2026 14:11:41</t>
+          <t>23-02-2026 16:44:27</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -5382,24 +5358,24 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26040522367230002693</t>
+          <t>26040522588220003214</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5517,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>345887</t>
+          <t>343897</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>88052</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5556,17 +5532,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAYAN </t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORIEGA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUARTE </t>
+          <t>OCEGUEDA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5576,7 +5552,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6677804463</t>
+          <t>6671043288</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5587,20 +5563,24 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>04-03-2010</t>
+          <t>13-11-2000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>NORIEGADUARTEBRAYAN@GMAIL.COM</t>
+          <t>MIGUELHO13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>23-02-2026 16:43:27</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>15-02-2026 21:36:16</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5608,28 +5588,28 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>23-02-2026 16:44:27</t>
+          <t>19-02-2026 04:36:58</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5640,14 +5620,22 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26040522588220003214</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+          <t>26040522478480002982</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5664,12 +5652,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>345655</t>
+          <t>343888</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>87820</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5679,17 +5667,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ITZEL PAULINA</t>
+          <t>LIZBETH YARELI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">GASTELUM </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5699,7 +5687,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6183256686</t>
+          <t>6672004222</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5710,20 +5698,24 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>10-10-1997</t>
+          <t>22-10-2001</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
+          <t>LIZBETHHERNANDEZ4222@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>23-02-2026 07:26:26</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>15-02-2026 18:04:14</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5731,28 +5723,28 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>23-02-2026 07:29:03</t>
+          <t>25-02-2026 13:14:17</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5763,36 +5755,44 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26040522572610003158</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>26040522652230003366</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343897</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t xml:space="preserve">ANA LUCIA </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OCEGUEDA</t>
+          <t xml:space="preserve">JUAN QUI </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5822,67 +5822,79 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6671043288</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6673938349</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUARUTO </t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>13-11-2000</t>
+          <t>23-09-2008</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>MIGUELHO13@GMAIL.COM</t>
+          <t>ANAJUANQUI08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>15-02-2026 21:36:16</t>
+          <t>15-02-2026 19:50:41</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>19-02-2026 04:36:58</t>
+          <t>23-02-2026 12:57:58</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:51:21</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5890,22 +5902,18 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26040522478480002982</t>
+          <t>26040522579820003179</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5922,12 +5930,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344617</t>
+          <t>343896</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>21713</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5937,17 +5945,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTO </t>
+          <t xml:space="preserve">KARLA SOFIA </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJO </t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>JUAN QUI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5957,67 +5965,79 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6671751779</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>6677758152</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AGUARUTO</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21-02-2000</t>
+          <t>04-12-2010</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ALBERTOROJO21@HOTMAIL.COM</t>
+          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>17-02-2026 17:34:00</t>
+          <t>15-02-2026 21:30:58</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>17-02-2026 17:35:27</t>
+          <t>23-02-2026 13:06:24</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>23-02-2026 13:05:56</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6025,14 +6045,18 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26040522438040002865</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
+          <t>26040522580090003182</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6049,12 +6073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>343906</t>
+          <t>343922</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6064,17 +6088,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA REBECA </t>
+          <t xml:space="preserve">IRENE </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6084,7 +6108,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6674722142</t>
+          <t>6674077607</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6095,17 +6119,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>25-11-2005</t>
+          <t>19-10-1976</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ADRIANAPARRA2500@GMAIL.COM</t>
+          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-02-2026 04:24:57</t>
+          <t>16-02-2026 06:00:38</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6116,17 +6140,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-02-2026 04:34:04</t>
+          <t>16-02-2026 06:02:04</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6148,14 +6172,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26040522369090002701</t>
+          <t>26040522371170002712</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6172,12 +6196,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>344139</t>
+          <t>345655</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6187,17 +6211,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">KATHERINE </t>
+          <t>ITZEL PAULINA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6207,7 +6231,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6671456800</t>
+          <t>6183256686</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6218,24 +6242,20 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>05-01-2008</t>
+          <t>10-10-1997</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>KAT0508SAN@GMAIL.COM</t>
+          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>16-02-2026 15:58:58</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>23-02-2026 07:26:26</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6243,28 +6263,28 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>16-02-2026 16:00:45</t>
+          <t>23-02-2026 07:29:03</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -6275,19 +6295,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26040522394190002754</t>
+          <t>26040522572610003158</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6299,12 +6319,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>344617</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6314,17 +6334,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS ALONSO </t>
+          <t xml:space="preserve">ALBERTO </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">ROJO </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTA </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6334,14 +6354,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6721229789</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>CAMPO BELLO</t>
-        </is>
-      </c>
+          <t>6671751779</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6349,64 +6365,56 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>08-11-1995</t>
+          <t>21-02-2000</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
+          <t>ALBERTOROJO21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-02-2026 19:03:39</t>
+          <t>17-02-2026 17:34:00</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16-02-2026 19:05:32</t>
+          <t>17-02-2026 17:35:27</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>16-02-2026 19:05:10</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6414,36 +6422,36 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26040522407060002792</t>
+          <t>26040522438040002865</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>345025</t>
+          <t>343906</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6453,17 +6461,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t xml:space="preserve">ADRIANA REBECA </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BARCENAS</t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6473,7 +6481,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6675028294</t>
+          <t>6674722142</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6484,17 +6492,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>31-12-9999</t>
+          <t>25-11-2005</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>more312barcenas@gmail.com</t>
+          <t>ADRIANAPARRA2500@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>03-05-2022 16:58:45</t>
+          <t>16-02-2026 04:24:57</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6505,28 +6513,28 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>03-02-2026 20:16:29</t>
+          <t>16-02-2026 04:34:04</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V46" t="inlineStr"/>
@@ -6537,36 +6545,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26040522491060002999</t>
+          <t>26040522369090002701</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>345143</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>87308</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6576,17 +6584,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KAREM YAZMIN</t>
+          <t xml:space="preserve">KATHERINE </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAYAN </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6596,14 +6604,10 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6677974107</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>RIO MOCORITO</t>
-        </is>
-      </c>
+          <t>6671456800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6611,64 +6615,56 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>07-08-1988</t>
+          <t>05-01-2008</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>KARENY1288@HOTMAIL.COM</t>
+          <t>KAT0508SAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19-02-2026 17:26:39</t>
+          <t>16-02-2026 15:58:58</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>19-02-2026 17:31:08</t>
+          <t>16-02-2026 16:00:45</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>19-02-2026 17:30:30</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6676,36 +6672,36 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26040522501600003040</t>
+          <t>26040522394190002754</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>345640</t>
+          <t>344328</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>87805</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6715,17 +6711,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JOSE GUILLERMO</t>
+          <t xml:space="preserve">CARLOS ALONSO </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">JACOBO </t>
+          <t xml:space="preserve">COTA </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6735,10 +6731,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6671911283</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6721229789</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CAMPO BELLO</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6746,52 +6746,64 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>16-02-1991</t>
+          <t>08-11-1995</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
+          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>23-02-2026 04:19:03</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>16-02-2026 19:03:39</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>23-02-2026 04:20:44</t>
+          <t>16-02-2026 19:05:32</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:05:10</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6799,36 +6811,36 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26040522565240003147</t>
+          <t>26040522407060002792</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>345656</t>
+          <t>345025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>87821</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6838,17 +6850,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ROJILY VANESSA</t>
+          <t>MORELIA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>BARCENAS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6858,10 +6870,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6672345223</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6675028294</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA ESTANCIA </t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6869,52 +6885,60 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>27-03-1982</t>
+          <t>06-09-2002</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>RUCALETA2703@GMAIL.COM</t>
+          <t>MORE312BARCENAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>23-02-2026 07:31:25</t>
+          <t>03-05-2022 16:58:45</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>23-02-2026 07:33:17</t>
+          <t>03-02-2026 20:16:29</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>03-02-2026 20:16:29</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6922,24 +6946,679 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26040522572650003159</t>
+          <t>26040522491060002999</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>345961</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>88126</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARJORIE </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VELAZQUEZ </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X </t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6674972190</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>31-12-2004</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>MARJORIEV312@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:08:53</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>25-02-2026 18:17:21</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>25-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26040522662960003400</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>345143</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>87308</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>KAREM YAZMIN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAYAN </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6677974107</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>RIO MOCORITO</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>07-08-1988</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>KARENY1288@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:26:39</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:31:08</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:30:30</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26040522501600003040</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>345640</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>87805</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>JOSE GUILLERMO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LEYVA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JACOBO </t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6671911283</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>16-02-1991</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>23-02-2026 04:19:03</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>23-02-2026 04:20:44</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26040522565240003147</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
           <t>1899</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>345656</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>87821</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ROJILY VANESSA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6672345223</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>27-03-1982</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>RUCALETA2703@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:31:25</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:33:17</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26040522572650003159</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
         <is>
           <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>346409</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>88574</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA ELIZABETH </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ROJAS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALENZUELA </t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3141032513</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUARUTO </t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>24-01-2011</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>GUADALUPE160509@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>25-02-2026 09:54:31</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>25-02-2026 09:59:54</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>25-02-2026 09:58:27</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26040522648990003357</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -1110,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>338748</t>
+          <t>263988</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>61492</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZEL VALERIA </t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">RENDON </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MENDIVIL</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,35 +1145,39 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6673260503</t>
+          <t>6677676285</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANUBIO </t>
+          <t xml:space="preserve">BACHIGUALATO </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18-12-2008</t>
+          <t>02-10-2001</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ITZELPEREZ1812@GMAIL.COM</t>
+          <t>RENDONCR01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>28-01-2026 14:48:02</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>28-10-2024 20:24:06</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1181,7 +1185,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1191,17 +1195,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:35</t>
+          <t>23-02-2026 13:36:54</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:08</t>
+          <t>23-02-2026 13:36:26</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1221,19 +1225,15 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26040522389000002737</t>
+          <t>26040522580840003185</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>499</t>
@@ -1241,24 +1241,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>338861</t>
+          <t>338748</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA </t>
+          <t xml:space="preserve">ITZEL VALERIA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMAS </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t>MENDIVIL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6671901936</t>
+          <t>6673260503</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">DANUBIO </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-06-2001</t>
+          <t>18-12-2008</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>VLAMASGALINDO@GMIAL.COM</t>
+          <t>ITZELPEREZ1812@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>28-01-2026 18:02:40</t>
+          <t>28-01-2026 14:48:02</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1334,17 +1334,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-02-2026 18:13:35</t>
+          <t>16-02-2026 13:40:35</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-02-2026 18:13:13</t>
+          <t>16-02-2026 13:40:08</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26040522052270001977</t>
+          <t>26040522389000002737</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>263988</t>
+          <t>330960</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>61492</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t>KARLA JANETH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENDON </t>
+          <t xml:space="preserve">PEÑUELAS </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t xml:space="preserve">PERALES </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6677676285</t>
+          <t>6671284496</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACHIGUALATO </t>
+          <t>ESTANCIA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>02-10-2001</t>
+          <t>23-10-1995</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>RENDONCR01@GMAIL.COM</t>
+          <t>KARLAPERALES23@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>28-10-2024 20:24:06</t>
+          <t>29-12-2025 18:55:46</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>23-02-2026 13:36:54</t>
+          <t>17-02-2026 18:46:14</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>23-02-2026 13:36:26</t>
+          <t>17-02-2026 18:45:49</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26040522580840003185</t>
+          <t>26040522442460002883</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr"/>
@@ -1527,24 +1527,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>330960</t>
+          <t>338906</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KARLA JANETH</t>
+          <t xml:space="preserve">ALMA LETICIA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑUELAS </t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERALES </t>
+          <t>FIERROS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6671284496</t>
+          <t>6672011841</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ESTANCIA</t>
+          <t xml:space="preserve">BACHIGULATO </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1589,24 +1589,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>23-10-1995</t>
+          <t>04-03-1983</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>KARLAPERALES23@HOTMAIL.COM</t>
+          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>29-12-2025 18:55:46</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>28-01-2026 19:52:18</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1624,17 +1620,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>17-02-2026 18:46:14</t>
+          <t>09-02-2026 18:05:21</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>17-02-2026 18:45:49</t>
+          <t>09-02-2026 18:04:48</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1644,7 +1640,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1654,7 +1650,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26040522442460002883</t>
+          <t>26040522205360002366</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1682,12 +1678,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>338906</t>
+          <t>338861</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1697,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMA LETICIA </t>
+          <t xml:space="preserve">VALERIA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t xml:space="preserve">LAMAS </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FIERROS</t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1717,12 +1713,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6672011841</t>
+          <t>6671901936</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACHIGULATO </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1732,17 +1728,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>04-03-1983</t>
+          <t>12-06-2001</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
+          <t>VLAMASGALINDO@GMIAL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>28-01-2026 19:52:18</t>
+          <t>28-01-2026 18:02:40</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1753,7 +1749,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1763,17 +1759,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>09-02-2026 18:05:21</t>
+          <t>03-02-2026 18:13:35</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>09-02-2026 18:04:48</t>
+          <t>03-02-2026 18:13:13</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1793,7 +1789,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26040522205360002366</t>
+          <t>26040522052270001977</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1801,7 +1797,11 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>499</t>
@@ -1948,12 +1948,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341050</t>
+          <t>340598</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS IVAN </t>
+          <t xml:space="preserve">LAURA LILIA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>REATIGA</t>
+          <t xml:space="preserve">ONTIVEROS </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ARCE</t>
+          <t xml:space="preserve">DUARTE </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1983,28 +1983,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6675777773</t>
+          <t>6673537007</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23-03-2011</t>
+          <t>17-02-2009</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JESUSIVANREATIGA@GMAIL.COM</t>
+          <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>04-02-2026 15:49:35</t>
+          <t>03-02-2026 14:38:21</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2029,18 +2029,18 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-02-2026 15:52:13</t>
+          <t>03-02-2026 14:39:22</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26040522078180002033</t>
+          <t>26040522041570001940</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340598</t>
+          <t>338858</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAURA LILIA </t>
+          <t xml:space="preserve">MANUEL FERNANDO </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONTIVEROS </t>
+          <t xml:space="preserve">LAMAS </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUARTE </t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2245,10 +2245,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6673537007</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6674956589</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES </t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2256,42 +2260,38 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>17-02-2009</t>
+          <t>22-06-2005</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
+          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-02-2026 14:38:21</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>28-01-2026 17:57:35</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 14:39:22</t>
+          <t>03-02-2026 18:15:55</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2299,13 +2299,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03-02-2026 18:15:25</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2313,14 +2321,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26040522041570001940</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26040522052400001978</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2337,12 +2353,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341657</t>
+          <t>339855</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>17673</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN RICARDO </t>
+          <t xml:space="preserve">JUAN PABLO </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">PADILLA </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">SALAS </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2372,14 +2388,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3224537874</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA ESTANCIA </t>
-        </is>
-      </c>
+          <t>6681452661</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2387,60 +2399,52 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>05-08-1995</t>
+          <t>06-12-1998</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DISTRITOTRECEE@GMAIL.COM</t>
+          <t>JUAN18752@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>06-02-2026 18:05:27</t>
+          <t>02-02-2026 05:48:09</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>06-02-2026 18:09:06</t>
+          <t>02-02-2026 05:49:53</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>06-02-2026 18:08:40</t>
-        </is>
-      </c>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2448,14 +2452,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26040522144380002227</t>
+          <t>26040521997910001841</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2472,12 +2476,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341829</t>
+          <t>341744</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2487,17 +2491,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDGAR FRANCISCO</t>
+          <t xml:space="preserve">PEDRO </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANO </t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">HARO </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2507,14 +2511,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6676987648</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>BLVD FLOR DE LIZ</t>
-        </is>
-      </c>
+          <t>3221713510</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2522,38 +2522,42 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15-06-1994</t>
+          <t>12-12-1974</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>EDGAR.VLA@HOTMAIL.COM</t>
+          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>07-02-2026 13:08:56</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>07-02-2026 07:59:31</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>07-02-2026 13:12:58</t>
+          <t>07-02-2026 08:01:13</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2561,21 +2565,13 @@
           <t>07-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>07-02-2026 13:12:39</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2583,36 +2579,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26040522161580002258</t>
+          <t>26040522155670002240</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>339855</t>
+          <t>340357</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2622,17 +2618,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t xml:space="preserve">SARAHI DE MARIA </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">PADILLA </t>
+          <t xml:space="preserve">AGUIAR </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAS </t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2642,63 +2638,75 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6681452661</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6674761021</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUGAMBILIAS </t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>06-12-1998</t>
+          <t>22-12-2001</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>JUAN18752@GMAIL.COM</t>
+          <t>SARAHIAGUIAR001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 05:48:09</t>
+          <t>02-02-2026 18:57:00</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-02-2026 05:49:53</t>
+          <t>02-02-2026 18:58:53</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-02-2026 18:58:21</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2706,36 +2714,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26040521997910001841</t>
+          <t>26040522021440001894</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341744</t>
+          <t>341050</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2745,17 +2753,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t xml:space="preserve">JESUS IVAN </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t>REATIGA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARO </t>
+          <t>ARCE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2765,7 +2773,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3221713510</t>
+          <t>6675777773</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2776,17 +2784,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12-12-1974</t>
+          <t>23-03-2011</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
+          <t>JESUSIVANREATIGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>07-02-2026 07:59:31</t>
+          <t>04-02-2026 15:49:35</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2801,22 +2809,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>07-02-2026 08:01:13</t>
+          <t>04-02-2026 15:52:13</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2833,36 +2841,36 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26040522155670002240</t>
+          <t>26040522078180002033</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>338858</t>
+          <t>342397</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2872,17 +2880,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUEL FERNANDO </t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMAS </t>
+          <t xml:space="preserve">LEYVA </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2892,75 +2900,67 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6674956589</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRES </t>
-        </is>
-      </c>
+          <t>6674049839</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-06-2005</t>
+          <t>15-10-1992</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
+          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>28-01-2026 17:57:35</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>09-02-2026 18:34:08</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-02-2026 18:15:55</t>
+          <t>11-02-2026 18:23:52</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>03-02-2026 18:15:25</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26040522052400001978</t>
+          <t>26040522273970002541</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2978,34 +2978,34 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+          <t>Pedro Fernando  Salas RECEPCION</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>341657</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3015,17 +3015,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAHI DE MARIA </t>
+          <t xml:space="preserve">KEVIN RICARDO </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUIAR </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3035,32 +3035,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6674761021</t>
+          <t>3224537874</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUGAMBILIAS </t>
+          <t xml:space="preserve">LA ESTANCIA </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22-12-2001</t>
+          <t>05-08-1995</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>SARAHIAGUIAR001@GMAIL.COM</t>
+          <t>DISTRITOTRECEE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-02-2026 18:57:00</t>
+          <t>06-02-2026 18:05:27</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3081,17 +3081,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:53</t>
+          <t>06-02-2026 18:09:06</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:21</t>
+          <t>06-02-2026 18:08:40</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26040522021440001894</t>
+          <t>26040522144380002227</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3123,24 +3123,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342397</t>
+          <t>341829</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3150,17 +3150,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t>EDGAR FRANCISCO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEYVA </t>
+          <t xml:space="preserve">MANZANO </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3170,10 +3170,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6674049839</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6676987648</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BLVD FLOR DE LIZ</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3181,56 +3185,60 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>15-10-1992</t>
+          <t>15-06-1994</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
+          <t>EDGAR.VLA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:08</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>07-02-2026 13:08:56</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>11-02-2026 18:23:52</t>
+          <t>07-02-2026 13:12:58</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>07-02-2026 13:12:39</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3238,27 +3246,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26040522273970002541</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Pedro Fernando  Salas RECEPCION</t>
-        </is>
-      </c>
+          <t>26040522161580002258</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3270,12 +3270,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340980</t>
+          <t>340395</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3285,17 +3285,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>SARAH FABIOLA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t xml:space="preserve">BORRAZ </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3305,28 +3305,28 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6673450501</t>
+          <t>6674779002</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>05-10-2004</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
+          <t>SARAHABORRAZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-02-2026 13:04:54</t>
+          <t>02-02-2026 20:56:33</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3351,18 +3351,18 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>04-02-2026 13:06:15</t>
+          <t>05-02-2026 20:14:53</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -3373,11 +3373,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26040522074180002020</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26040522119630002171</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>549</t>
@@ -3397,12 +3405,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>343891</t>
+          <t>340980</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3412,17 +3420,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SETH SEBASTIAN</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDOVAL </t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3432,14 +3440,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6871298029</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AUARUTO </t>
-        </is>
-      </c>
+          <t>6673450501</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3447,64 +3451,56 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>04-06-2008</t>
+          <t>08-10-2007</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SETHSEBASTIANSANDOVALFLORES@GMAIL.COM</t>
+          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>15-02-2026 19:53:47</t>
+          <t>04-02-2026 13:04:54</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>23-02-2026 13:01:00</t>
+          <t>04-02-2026 13:06:15</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>23-02-2026 13:00:32</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3512,18 +3508,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26040522579910003180</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522074180002020</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3540,12 +3532,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>343909</t>
+          <t>342743</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3555,17 +3547,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA GUADALUPE </t>
+          <t xml:space="preserve">OCTAVIANO </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">SAUCEDA </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3575,63 +3567,75 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6672155907</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6731436529</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRRANOVA </t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>26-10-1982</t>
+          <t>20-11-2000</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PARRAGLORIA321@GMAIL.COM</t>
+          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16-02-2026 04:41:54</t>
+          <t>10-02-2026 17:15:49</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>16-02-2026 04:45:09</t>
+          <t>10-02-2026 17:22:40</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>10-02-2026 17:22:03</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3639,19 +3643,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26040522369220002705</t>
+          <t>26040522239600002442</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3663,12 +3667,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>343530</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3678,17 +3682,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA FERNANDA </t>
+          <t>MAURO EMMANUEL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AMEZQUITA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACHADO </t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3698,67 +3702,63 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6862342452</t>
+          <t>6674640838</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA ROCIO </t>
+          <t xml:space="preserve">CULIACANCITO </t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>27-01-1995</t>
+          <t>04-04-2005</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
+          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16-02-2026 14:49:21</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:28:11</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-02-2026 14:53:31</t>
+          <t>13-02-2026 16:30:21</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16-02-2026 14:52:00</t>
+          <t>13-02-2026 16:29:54</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3778,19 +3778,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26040522391260002745</t>
+          <t>26040522324290002650</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343530</t>
+          <t>342326</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3817,17 +3817,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MAURO EMMANUEL</t>
+          <t xml:space="preserve">MARIAN </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3837,32 +3837,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6674640838</t>
+          <t>6675145803</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CULIACANCITO </t>
+          <t xml:space="preserve">VILLAS DEL RIO </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>04-04-2005</t>
+          <t>21-12-1999</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
+          <t>MARIANONTES125@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:11</t>
+          <t>09-02-2026 17:29:11</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3883,17 +3883,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>13-02-2026 16:30:21</t>
+          <t>09-02-2026 17:30:56</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13-02-2026 16:29:54</t>
+          <t>09-02-2026 17:30:19</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26040522324290002650</t>
+          <t>26040522202510002352</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3925,24 +3925,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>344702</t>
+          <t>343908</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3952,17 +3952,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLETH </t>
+          <t>LUIS JESUS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OROPEZA</t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOMINGUEZ </t>
+          <t xml:space="preserve">ANGULO </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3972,75 +3972,63 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6671444793</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
-        </is>
-      </c>
+          <t>6672551941</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>27-05-2005</t>
+          <t>20-01-2010</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>MARLETH5002@GMAIL.COM</t>
+          <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>17-02-2026 20:20:03</t>
+          <t>16-02-2026 04:37:58</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>17-02-2026 20:22:39</t>
+          <t>16-02-2026 04:39:44</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>17-02-2026 20:21:36</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4048,14 +4036,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26040522446310002893</t>
+          <t>26040522369190002704</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4072,12 +4060,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>340395</t>
+          <t>343533</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4087,17 +4075,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SARAH FABIOLA</t>
+          <t>JOSE GUADALLUPE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORRAZ </t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4107,67 +4095,75 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6674779002</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6673961529</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARGENTINA </t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>05-10-2004</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>SARAHABORRAZ05@GMAIL.COM</t>
+          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-02-2026 20:56:33</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:37:04</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>05-02-2026 20:14:53</t>
+          <t>13-02-2026 16:39:33</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:39:06</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4175,44 +4171,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26040522119630002171</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522324550002655</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342743</t>
+          <t>343614</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4222,17 +4210,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCTAVIANO </t>
+          <t xml:space="preserve">JUAN FRANCISCO </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDA </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4242,14 +4230,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6731436529</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRRANOVA </t>
-        </is>
-      </c>
+          <t>6671911835</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4257,60 +4241,56 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20-11-2000</t>
+          <t>17-03-2007</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
+          <t>JFX4318@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-02-2026 17:15:49</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>13-02-2026 20:07:29</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-02-2026 17:22:40</t>
+          <t>16-02-2026 19:40:20</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>10-02-2026 17:22:03</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4318,36 +4298,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26040522239600002442</t>
+          <t>26040522408860002801</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343908</t>
+          <t>343865</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4357,17 +4337,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LUIS JESUS</t>
+          <t xml:space="preserve">VLADIMIR </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGULO </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4377,7 +4357,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6672551941</t>
+          <t>6872535687</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4388,20 +4368,24 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20-01-2010</t>
+          <t>23-01-2009</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
+          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>16-02-2026 04:37:58</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>15-02-2026 14:10:10</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4409,22 +4393,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>16-02-2026 04:39:44</t>
+          <t>15-02-2026 14:11:41</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4441,19 +4425,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26040522369190002704</t>
+          <t>26040522367230002693</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4465,12 +4449,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>344131</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4480,17 +4464,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JOSE GUADALLUPE</t>
+          <t>MILDERED HARUMI</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t xml:space="preserve">ROCHA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4500,35 +4484,39 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6673961529</t>
+          <t>6673878560</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARGENTINA </t>
+          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>01-09-1992</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
+          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13-02-2026 16:37:04</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>16-02-2026 15:42:58</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4546,17 +4534,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:33</t>
+          <t>18-02-2026 15:55:22</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:06</t>
+          <t>18-02-2026 15:33:30</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4576,11 +4564,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26040522324550002655</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
+          <t>26040522465030002939</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>499</t>
@@ -4600,12 +4596,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343614</t>
+          <t>343897</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4615,17 +4611,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN FRANCISCO </t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t>OCEGUEDA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4635,7 +4631,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6671911835</t>
+          <t>6671043288</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4646,17 +4642,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>17-03-2007</t>
+          <t>13-11-2000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>JFX4318@GMAIL.COM</t>
+          <t>MIGUELHO13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>13-02-2026 20:07:29</t>
+          <t>15-02-2026 21:36:16</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4681,18 +4677,18 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>16-02-2026 19:40:20</t>
+          <t>19-02-2026 04:36:58</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
@@ -4703,11 +4699,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26040522408860002801</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26040522478480002982</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>899</t>
@@ -4727,12 +4731,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343865</t>
+          <t>343888</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4742,17 +4746,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">VLADIMIR </t>
+          <t>LIZBETH YARELI</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">GASTELUM </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4762,28 +4766,28 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6872535687</t>
+          <t>6672004222</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>23-01-2009</t>
+          <t>22-10-2001</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
+          <t>LIZBETHHERNANDEZ4222@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>15-02-2026 14:10:10</t>
+          <t>15-02-2026 18:04:14</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4808,18 +4812,18 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>15-02-2026 14:11:41</t>
+          <t>25-02-2026 13:14:17</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -4830,11 +4834,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26040522367230002693</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26040522652230003366</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>549</t>
@@ -4854,12 +4866,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>346066</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>88231</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4869,17 +4881,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CARLOS RODRIGO</t>
+          <t xml:space="preserve">ANA LUCIA </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NIEBLAS</t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t xml:space="preserve">JUAN QUI </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4889,63 +4901,79 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6673160433</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6673938349</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUARUTO </t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>13-03-1994</t>
+          <t>23-09-2008</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>RODRIGORODRIGO1994RIVERA@GMAIL.COM</t>
+          <t>ANAJUANQUI08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>24-02-2026 06:14:38</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>15-02-2026 19:50:41</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>24-02-2026 06:16:43</t>
+          <t>23-02-2026 12:57:58</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>24-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:51:21</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4953,36 +4981,40 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26040522610020003260</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
+          <t>26040522579820003179</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342326</t>
+          <t>343896</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>21713</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4992,17 +5024,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIAN </t>
+          <t xml:space="preserve">KARLA SOFIA </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t>JUAN QUI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5012,12 +5044,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6675145803</t>
+          <t>6677758152</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAS DEL RIO </t>
+          <t>AGUARUTO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5027,20 +5059,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21-12-1999</t>
+          <t>04-12-2010</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MARIANONTES125@GMAIL.COM</t>
+          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:29:11</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>15-02-2026 21:30:58</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5058,17 +5094,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:56</t>
+          <t>23-02-2026 13:06:24</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:19</t>
+          <t>23-02-2026 13:05:56</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5088,10 +5124,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26040522202510002352</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
+          <t>26040522580090003182</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
@@ -5112,12 +5152,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>344131</t>
+          <t>343922</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5127,17 +5167,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MILDERED HARUMI</t>
+          <t xml:space="preserve">IRENE </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCHA </t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5147,14 +5187,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6673878560</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
-        </is>
-      </c>
+          <t>6674077607</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5162,64 +5198,52 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>01-09-1992</t>
+          <t>19-10-1976</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
+          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16-02-2026 15:42:58</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>16-02-2026 06:00:38</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>18-02-2026 15:55:22</t>
+          <t>16-02-2026 06:02:04</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>18-02-2026 15:33:30</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5227,27 +5251,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26040522465030002939</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522371170002712</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5382,12 +5398,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>344705</t>
+          <t>343906</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5397,17 +5413,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t xml:space="preserve">ADRIANA REBECA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5417,14 +5433,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6673290828</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>TERRAZAS</t>
-        </is>
-      </c>
+          <t>6674722142</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5432,60 +5444,52 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>16-03-2004</t>
+          <t>25-11-2005</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>DIANA_SR16@OUTLOOK.COM</t>
+          <t>ADRIANAPARRA2500@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17-02-2026 20:25:26</t>
+          <t>16-02-2026 04:24:57</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>17-02-2026 20:27:25</t>
+          <t>16-02-2026 04:34:04</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>17-02-2026 20:26:49</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5493,14 +5497,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26040522446490002894</t>
+          <t>26040522369090002701</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5517,12 +5521,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343897</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5532,17 +5536,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t xml:space="preserve">KATHERINE </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>OCEGUEDA</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5552,28 +5556,28 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6671043288</t>
+          <t>6671456800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>13-11-2000</t>
+          <t>05-01-2008</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MIGUELHO13@GMAIL.COM</t>
+          <t>KAT0508SAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>15-02-2026 21:36:16</t>
+          <t>16-02-2026 15:58:58</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5588,28 +5592,28 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>19-02-2026 04:36:58</t>
+          <t>16-02-2026 16:00:45</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -5620,44 +5624,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26040522478480002982</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522394190002754</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343888</t>
+          <t>344617</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5667,17 +5663,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LIZBETH YARELI</t>
+          <t xml:space="preserve">ALBERTO </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">ROJO </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">GASTELUM </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5687,28 +5683,28 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6672004222</t>
+          <t>6671751779</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>22-10-2001</t>
+          <t>21-02-2000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>LIZBETHHERNANDEZ4222@GMAIL.COM</t>
+          <t>ALBERTOROJO21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>15-02-2026 18:04:14</t>
+          <t>17-02-2026 17:34:00</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5733,18 +5729,18 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>25-02-2026 13:14:17</t>
+          <t>17-02-2026 17:35:27</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5755,19 +5751,11 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26040522652230003366</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522438040002865</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
           <t>549</t>
@@ -5787,12 +5775,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343890</t>
+          <t>344328</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21707</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5802,17 +5790,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA LUCIA </t>
+          <t xml:space="preserve">CARLOS ALONSO </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMARILLAS </t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN QUI </t>
+          <t xml:space="preserve">COTA </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5822,32 +5810,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6673938349</t>
+          <t>6721229789</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUARUTO </t>
+          <t>CAMPO BELLO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>23-09-2008</t>
+          <t>08-11-1995</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ANAJUANQUI08@GMAIL.COM</t>
+          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>15-02-2026 19:50:41</t>
+          <t>16-02-2026 19:03:39</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5872,17 +5860,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>23-02-2026 12:57:58</t>
+          <t>16-02-2026 19:05:32</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>23-02-2026 12:51:21</t>
+          <t>16-02-2026 19:05:10</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5892,7 +5880,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5902,14 +5890,10 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26040522579820003179</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522407060002792</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
@@ -5918,24 +5902,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>343896</t>
+          <t>344705</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5945,17 +5929,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA SOFIA </t>
+          <t xml:space="preserve">DIANA LAURA </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMARILLAS </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JUAN QUI</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5965,12 +5949,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6677758152</t>
+          <t>6673290828</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AGUARUTO</t>
+          <t>TERRAZAS</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5980,24 +5964,20 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>04-12-2010</t>
+          <t>16-03-2004</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
+          <t>DIANA_SR16@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>15-02-2026 21:30:58</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>17-02-2026 20:25:26</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6005,7 +5985,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6015,17 +5995,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>23-02-2026 13:06:24</t>
+          <t>17-02-2026 20:27:25</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>23-02-2026 13:05:56</t>
+          <t>17-02-2026 20:26:49</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6035,7 +6015,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6045,14 +6025,10 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26040522580090003182</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522446490002894</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
@@ -6061,24 +6037,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>343922</t>
+          <t>345025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6088,17 +6064,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRENE </t>
+          <t>MORELIA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t>BARCENAS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6108,10 +6084,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6674077607</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6675028294</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA ESTANCIA </t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6119,52 +6099,60 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19-10-1976</t>
+          <t>06-09-2002</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
+          <t>MORE312BARCENAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-02-2026 06:00:38</t>
+          <t>03-05-2022 16:58:45</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-02-2026 06:02:04</t>
+          <t>03-02-2026 20:16:29</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>03-02-2026 20:16:29</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6172,36 +6160,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26040522371170002712</t>
+          <t>26040522491060002999</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>345655</t>
+          <t>345143</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>87820</t>
+          <t>87308</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6211,12 +6199,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ITZEL PAULINA</t>
+          <t>KAREM YAZMIN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">PAYAN </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6231,10 +6219,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6183256686</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6677974107</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>RIO MOCORITO</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6242,52 +6234,64 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>10-10-1997</t>
+          <t>07-08-1988</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
+          <t>KARENY1288@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>23-02-2026 07:26:26</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>19-02-2026 17:26:39</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>23-02-2026 07:29:03</t>
+          <t>19-02-2026 17:31:08</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:30:30</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6295,36 +6299,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26040522572610003158</t>
+          <t>26040522501600003040</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344617</t>
+          <t>345640</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>87805</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6334,17 +6338,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTO </t>
+          <t>JOSE GUILLERMO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJO </t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">JACOBO </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6354,7 +6358,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6671751779</t>
+          <t>6671911283</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6365,24 +6369,20 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21-02-2000</t>
+          <t>16-02-1991</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ALBERTOROJO21@HOTMAIL.COM</t>
+          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>17-02-2026 17:34:00</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>23-02-2026 04:19:03</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6390,22 +6390,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>17-02-2026 17:35:27</t>
+          <t>23-02-2026 04:20:44</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -6422,14 +6422,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26040522438040002865</t>
+          <t>26040522565240003147</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6446,12 +6446,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343906</t>
+          <t>345656</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>87821</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6461,17 +6461,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA REBECA </t>
+          <t>ROJILY VANESSA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t>X</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6674722142</t>
+          <t>6672345223</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6492,17 +6492,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>25-11-2005</t>
+          <t>27-03-1982</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ADRIANAPARRA2500@GMAIL.COM</t>
+          <t>RUCALETA2703@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16-02-2026 04:24:57</t>
+          <t>23-02-2026 07:31:25</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6513,22 +6513,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>16-02-2026 04:34:04</t>
+          <t>23-02-2026 07:33:17</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -6545,14 +6545,14 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26040522369090002701</t>
+          <t>26040522572650003159</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6569,12 +6569,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344139</t>
+          <t>345961</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>88126</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6584,17 +6584,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">KATHERINE </t>
+          <t xml:space="preserve">MARJORIE </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">X </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6671456800</t>
+          <t>6674972190</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6615,24 +6615,20 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>05-01-2008</t>
+          <t>31-12-2004</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>KAT0508SAN@GMAIL.COM</t>
+          <t>MARJORIEV312@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 15:58:58</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>23-02-2026 18:08:53</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6640,22 +6636,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>16-02-2026 16:00:45</t>
+          <t>25-02-2026 18:17:21</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>25-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -6672,36 +6668,44 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26040522394190002754</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
+          <t>26040522662960003400</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>343891</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6711,17 +6715,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS ALONSO </t>
+          <t>SETH SEBASTIAN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">SANDOVAL </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTA </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6731,12 +6735,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6721229789</t>
+          <t>6871298029</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CAMPO BELLO</t>
+          <t xml:space="preserve">AUARUTO </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6746,17 +6750,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>08-11-1995</t>
+          <t>04-06-2008</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
+          <t>SETHSEBASTIANSANDOVALFLORES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 19:03:39</t>
+          <t>15-02-2026 19:53:47</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6781,17 +6785,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 19:05:32</t>
+          <t>23-02-2026 13:01:00</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>16-02-2026 19:05:10</t>
+          <t>23-02-2026 13:00:32</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6801,7 +6805,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6811,10 +6815,14 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26040522407060002792</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
+          <t>26040522579910003180</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6823,24 +6831,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>345025</t>
+          <t>343909</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6850,17 +6858,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t xml:space="preserve">GLORIA GUADALUPE </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BARCENAS</t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6870,14 +6878,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6675028294</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA ESTANCIA </t>
-        </is>
-      </c>
+          <t>6672155907</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6885,60 +6889,52 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>06-09-2002</t>
+          <t>26-10-1982</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MORE312BARCENAS@GMAIL.COM</t>
+          <t>PARRAGLORIA321@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>03-05-2022 16:58:45</t>
+          <t>16-02-2026 04:41:54</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>03-02-2026 20:16:29</t>
+          <t>16-02-2026 04:45:09</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>03-02-2026 20:16:29</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6946,36 +6942,36 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26040522491060002999</t>
+          <t>26040522369220002705</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345961</t>
+          <t>344104</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>88126</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6985,17 +6981,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARJORIE </t>
+          <t xml:space="preserve">MARIA FERNANDA </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t>AMEZQUITA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">X </t>
+          <t xml:space="preserve">MACHADO </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7005,10 +7001,14 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6674972190</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>6862342452</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA ROCIO </t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7016,52 +7016,64 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>31-12-2004</t>
+          <t>27-01-1995</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>MARJORIEV312@GMAIL.COM</t>
+          <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>23-02-2026 18:08:53</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>16-02-2026 14:49:21</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>25-02-2026 18:17:21</t>
+          <t>16-02-2026 14:53:31</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>25-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:52:00</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7069,44 +7081,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26040522662960003400</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522391260002745</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345143</t>
+          <t>345655</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87308</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7116,12 +7120,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAREM YAZMIN</t>
+          <t>ITZEL PAULINA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAYAN </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7136,14 +7140,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6677974107</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>RIO MOCORITO</t>
-        </is>
-      </c>
+          <t>6183256686</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7151,64 +7151,52 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>07-08-1988</t>
+          <t>10-10-1997</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>KARENY1288@HOTMAIL.COM</t>
+          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>19-02-2026 17:26:39</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>23-02-2026 07:26:26</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>19-02-2026 17:31:08</t>
+          <t>23-02-2026 07:29:03</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>19-02-2026 17:30:30</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7216,36 +7204,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26040522501600003040</t>
+          <t>26040522572610003158</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>345640</t>
+          <t>346409</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>87805</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7255,17 +7243,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JOSE GUILLERMO</t>
+          <t xml:space="preserve">MARIA ELIZABETH </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">JACOBO </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7275,63 +7263,79 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6671911283</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>3141032513</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUARUTO </t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>16-02-1991</t>
+          <t>24-01-2011</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
+          <t>GUADALUPE160509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>23-02-2026 04:19:03</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>25-02-2026 09:54:31</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>23-02-2026 04:20:44</t>
+          <t>25-02-2026 09:59:54</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>25-02-2026 09:58:27</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7339,14 +7343,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26040522565240003147</t>
+          <t>26040522648990003357</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7363,12 +7367,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>345656</t>
+          <t>344702</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>87821</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7378,17 +7382,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ROJILY VANESSA</t>
+          <t xml:space="preserve">MARLETH </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>OROPEZA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t xml:space="preserve">DOMINGUEZ </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7398,10 +7402,14 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6672345223</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>6671444793</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7409,52 +7417,60 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>27-03-1982</t>
+          <t>27-05-2005</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>RUCALETA2703@GMAIL.COM</t>
+          <t>MARLETH5002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>23-02-2026 07:31:25</t>
+          <t>17-02-2026 20:20:03</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>23-02-2026 07:33:17</t>
+          <t>17-02-2026 20:22:39</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>17-02-2026 20:21:36</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7462,14 +7478,14 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26040522572650003159</t>
+          <t>26040522446310002893</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7486,12 +7502,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>346409</t>
+          <t>346066</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>88574</t>
+          <t>88231</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7501,17 +7517,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ELIZABETH </t>
+          <t>CARLOS RODRIGO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>NIEBLAS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7521,79 +7537,63 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3141032513</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AGUARUTO </t>
-        </is>
-      </c>
+          <t>6673160433</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>24-01-2011</t>
+          <t>13-03-1994</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>GUADALUPE160509@GMAIL.COM</t>
+          <t>RODRIGORODRIGO1994RIVERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>25-02-2026 09:54:31</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>24-02-2026 06:14:38</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>25-02-2026 09:59:54</t>
+          <t>24-02-2026 06:16:43</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>25-02-2026 09:58:27</t>
-        </is>
-      </c>
+          <t>24-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7601,24 +7601,24 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26040522648990003357</t>
+          <t>26040522610020003260</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>98101</t>
+          <t>84873</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95858</t>
+          <t>82656</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DANIEL ALBERTO</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIZCARRA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>ALBERTO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6675383330</t>
+          <t>6671055229</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C. GABRIELA MISTRAL 3445</t>
+          <t>C. TENOTITLAN 4418</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,24 +628,20 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>17-05-1998</t>
+          <t>30-11-1979</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DANIELVIZCARRA@HOTMAIL.COM</t>
+          <t>ALBERTOTOMARQUEZ79@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>06-06-2022 19:25:07</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>12-04-2022 08:01:19</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -653,28 +649,28 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-02-2026 17:55:17</t>
+          <t>16-02-2026 04:14:14</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -685,14 +681,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26040522019480001886</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26040522368800002698</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -848,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>84873</t>
+          <t>302189</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>82656</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t xml:space="preserve">NIDIA ADME </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ALBERTO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -883,32 +887,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6671055229</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>C. TENOTITLAN 4418</t>
-        </is>
-      </c>
+          <t>6671760805</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30-11-1979</t>
+          <t>01-10-1977</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ALBERTOTOMARQUEZ79@HOTMAIL.COM</t>
+          <t>NIDIAMEDINA@LIVE.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12-04-2022 08:01:19</t>
+          <t>05-07-2025 06:34:10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -929,12 +929,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16-02-2026 04:14:14</t>
+          <t>22-02-2026 14:25:33</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>22-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26040522368800002698</t>
+          <t>26040522564200003144</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -959,11 +959,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1899</t>
@@ -983,12 +979,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>302189</t>
+          <t>98101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99687</t>
+          <t>95858</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIDIA ADME </t>
+          <t>DANIEL ALBERTO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t xml:space="preserve">VIZCARRA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,31 +1014,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6671760805</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6675383330</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C. GABRIELA MISTRAL 3445</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>01-10-1977</t>
+          <t>17-05-1998</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NIDIAMEDINA@LIVE.COM</t>
+          <t>DANIELVIZCARRA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>05-07-2025 06:34:10</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>06-06-2022 19:25:07</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1050,28 +1054,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>22-02-2026 14:25:33</t>
+          <t>02-02-2026 17:55:17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>22-05-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1082,18 +1086,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26040522564200003144</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522019480001886</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1110,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>263988</t>
+          <t>338748</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>61492</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t xml:space="preserve">ITZEL VALERIA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENDON </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MENDIVIL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,39 +1145,35 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6677676285</t>
+          <t>6673260503</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACHIGUALATO </t>
+          <t xml:space="preserve">DANUBIO </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>02-10-2001</t>
+          <t>18-12-2008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>RENDONCR01@GMAIL.COM</t>
+          <t>ITZELPEREZ1812@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>28-10-2024 20:24:06</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>28-01-2026 14:48:02</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1185,7 +1181,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1195,17 +1191,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>23-02-2026 13:36:54</t>
+          <t>16-02-2026 13:40:35</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>23-02-2026 13:36:26</t>
+          <t>16-02-2026 13:40:08</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1225,15 +1221,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26040522580840003185</t>
+          <t>26040522389000002737</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>499</t>
@@ -1241,24 +1241,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>338748</t>
+          <t>338861</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITZEL VALERIA </t>
+          <t xml:space="preserve">VALERIA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">LAMAS </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MENDIVIL</t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6673260503</t>
+          <t>6671901936</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANUBIO </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18-12-2008</t>
+          <t>12-06-2001</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ITZELPEREZ1812@GMAIL.COM</t>
+          <t>VLAMASGALINDO@GMIAL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>28-01-2026 14:48:02</t>
+          <t>28-01-2026 18:02:40</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1334,17 +1334,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:35</t>
+          <t>03-02-2026 18:13:35</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:08</t>
+          <t>03-02-2026 18:13:13</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26040522389000002737</t>
+          <t>26040522052270001977</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>330960</t>
+          <t>263988</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>61492</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KARLA JANETH</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEÑUELAS </t>
+          <t xml:space="preserve">RENDON </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERALES </t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6671284496</t>
+          <t>6677676285</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ESTANCIA</t>
+          <t xml:space="preserve">BACHIGUALATO </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23-10-1995</t>
+          <t>02-10-2001</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>KARLAPERALES23@HOTMAIL.COM</t>
+          <t>RENDONCR01@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>29-12-2025 18:55:46</t>
+          <t>28-10-2024 20:24:06</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>17-02-2026 18:46:14</t>
+          <t>23-02-2026 13:36:54</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>17-02-2026 18:45:49</t>
+          <t>23-02-2026 13:36:26</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26040522442460002883</t>
+          <t>26040522580840003185</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr"/>
@@ -1527,24 +1527,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>338906</t>
+          <t>340164</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALMA LETICIA </t>
+          <t xml:space="preserve">DYLAN ARTURO </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t xml:space="preserve">RUBIO </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FIERROS</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1574,75 +1574,67 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6672011841</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BACHIGULATO </t>
-        </is>
-      </c>
+          <t>6674732132</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>04-03-1983</t>
+          <t>25-09-2010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
+          <t>DYLANRUBIO2509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>28-01-2026 19:52:18</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>02-02-2026 14:14:23</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>09-02-2026 18:05:21</t>
+          <t>02-02-2026 14:15:24</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>09-02-2026 18:04:48</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1650,18 +1642,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26040522205360002366</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522012290001872</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1678,12 +1666,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>338861</t>
+          <t>341050</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16679</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1693,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALERIA </t>
+          <t xml:space="preserve">JESUS IVAN </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMAS </t>
+          <t>REATIGA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t>ARCE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1713,75 +1701,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6671901936</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRES </t>
-        </is>
-      </c>
+          <t>6675777773</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>12-06-2001</t>
+          <t>23-03-2011</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>VLAMASGALINDO@GMIAL.COM</t>
+          <t>JESUSIVANREATIGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>28-01-2026 18:02:40</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>04-02-2026 15:49:35</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-02-2026 18:13:35</t>
+          <t>04-02-2026 15:52:13</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>03-02-2026 18:13:13</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1789,44 +1769,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26040522052270001977</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522078180002033</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340164</t>
+          <t>330960</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1836,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DYLAN ARTURO </t>
+          <t>KARLA JANETH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUBIO </t>
+          <t xml:space="preserve">PEÑUELAS </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t xml:space="preserve">PERALES </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1856,67 +1828,79 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6674732132</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6671284496</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ESTANCIA</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>25-09-2010</t>
+          <t>23-10-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>DYLANRUBIO2509@GMAIL.COM</t>
+          <t>KARLAPERALES23@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 14:14:23</t>
+          <t>29-12-2025 18:55:46</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 14:15:24</t>
+          <t>17-02-2026 18:46:14</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>17-02-2026 18:45:49</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1924,14 +1908,18 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26040522012290001872</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26040522442460002883</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1948,12 +1936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340598</t>
+          <t>340619</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1963,17 +1951,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAURA LILIA </t>
+          <t xml:space="preserve">JOSE RAUL </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONTIVEROS </t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUARTE </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1983,53 +1971,53 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6673537007</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6672537304</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACHIGUALTO </t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17-02-2009</t>
+          <t>01-09-1999</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
+          <t>JRAULMV1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-02-2026 14:38:21</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>03-02-2026 15:16:06</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-02-2026 14:39:22</t>
+          <t>03-02-2026 15:23:17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2037,13 +2025,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-02-2026 15:21:47</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2051,36 +2047,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26040522041570001940</t>
+          <t>26040522042820001942</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340619</t>
+          <t>338906</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2086,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE RAUL </t>
+          <t xml:space="preserve">ALMA LETICIA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>FIERROS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,32 +2106,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6672537304</t>
+          <t>6672011841</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACHIGUALTO </t>
+          <t xml:space="preserve">BACHIGULATO </t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>01-09-1999</t>
+          <t>04-03-1983</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JRAULMV1@GMAIL.COM</t>
+          <t>ALMALETICIACHAIRESFIERRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-02-2026 15:16:06</t>
+          <t>28-01-2026 19:52:18</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2156,17 +2152,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 15:23:17</t>
+          <t>09-02-2026 18:05:21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-02-2026 15:21:47</t>
+          <t>09-02-2026 18:04:48</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2186,10 +2182,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26040522042820001942</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26040522205360002366</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2198,24 +2198,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>338858</t>
+          <t>340598</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2225,17 +2225,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUEL FERNANDO </t>
+          <t xml:space="preserve">LAURA LILIA </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAMAS </t>
+          <t xml:space="preserve">ONTIVEROS </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALINDO </t>
+          <t xml:space="preserve">DUARTE </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2245,14 +2245,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6674956589</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TORRES </t>
-        </is>
-      </c>
+          <t>6673537007</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2260,38 +2256,42 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22-06-2005</t>
+          <t>17-02-2009</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
+          <t>LALY_ONTIVEROS1702@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28-01-2026 17:57:35</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>03-02-2026 14:38:21</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 18:15:55</t>
+          <t>03-02-2026 14:39:22</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2299,21 +2299,13 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>03-02-2026 18:15:25</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2321,22 +2313,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26040522052400001978</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522041570001940</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2476,12 +2460,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341744</t>
+          <t>340357</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2491,17 +2475,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t xml:space="preserve">SARAHI DE MARIA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t xml:space="preserve">AGUIAR </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARO </t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2511,67 +2495,75 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3221713510</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6674761021</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUGAMBILIAS </t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12-12-1974</t>
+          <t>22-12-2001</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
+          <t>SARAHIAGUIAR001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>07-02-2026 07:59:31</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>02-02-2026 18:57:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>07-02-2026 08:01:13</t>
+          <t>02-02-2026 18:58:53</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>02-02-2026 18:58:21</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2579,14 +2571,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26040522155670002240</t>
+          <t>26040522021440001894</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2603,12 +2595,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340357</t>
+          <t>338858</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2618,17 +2610,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAHI DE MARIA </t>
+          <t xml:space="preserve">MANUEL FERNANDO </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUIAR </t>
+          <t xml:space="preserve">LAMAS </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t xml:space="preserve">GALINDO </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2638,12 +2630,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6674761021</t>
+          <t>6674956589</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUGAMBILIAS </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2653,17 +2645,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22-12-2001</t>
+          <t>22-06-2005</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SARAHIAGUIAR001@GMAIL.COM</t>
+          <t>MANUELLAMASGALINDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 18:57:00</t>
+          <t>28-01-2026 17:57:35</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2674,7 +2666,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2684,17 +2676,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:53</t>
+          <t>03-02-2026 18:15:55</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:21</t>
+          <t>03-02-2026 18:15:25</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2704,7 +2696,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2714,11 +2706,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26040522021440001894</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26040522052400001978</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>499</t>
@@ -2738,12 +2738,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341050</t>
+          <t>341744</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2753,17 +2753,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS IVAN </t>
+          <t xml:space="preserve">PEDRO </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>REATIGA</t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ARCE</t>
+          <t xml:space="preserve">HARO </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6675777773</t>
+          <t>3221713510</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2784,17 +2784,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23-03-2011</t>
+          <t>12-12-1974</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JESUSIVANREATIGA@GMAIL.COM</t>
+          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 15:49:35</t>
+          <t>07-02-2026 07:59:31</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2809,22 +2809,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-02-2026 15:52:13</t>
+          <t>07-02-2026 08:01:13</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2841,36 +2841,36 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26040522078180002033</t>
+          <t>26040522155670002240</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342397</t>
+          <t>343530</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2880,17 +2880,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t>MAURO EMMANUEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEYVA </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2900,10 +2900,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6674049839</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6674640838</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CULIACANCITO </t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2911,56 +2915,60 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>15-10-1992</t>
+          <t>04-04-2005</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
+          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:08</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:28:11</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>11-02-2026 18:23:52</t>
+          <t>13-02-2026 16:30:21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:29:54</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2968,27 +2976,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26040522273970002541</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Pedro Fernando  Salas RECEPCION</t>
-        </is>
-      </c>
+          <t>26040522324290002650</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3000,12 +3000,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341657</t>
+          <t>340395</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3015,17 +3015,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN RICARDO </t>
+          <t>SARAH FABIOLA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">BORRAZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3035,75 +3035,67 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3224537874</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA ESTANCIA </t>
-        </is>
-      </c>
+          <t>6674779002</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>05-08-1995</t>
+          <t>05-10-2004</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>DISTRITOTRECEE@GMAIL.COM</t>
+          <t>SARAHABORRAZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>06-02-2026 18:05:27</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>02-02-2026 20:56:33</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>06-02-2026 18:09:06</t>
+          <t>05-02-2026 20:14:53</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>06-02-2026 18:08:40</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3111,36 +3103,44 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26040522144380002227</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26040522119630002171</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341829</t>
+          <t>340980</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3150,17 +3150,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EDGAR FRANCISCO</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANZANO </t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3170,14 +3170,10 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6676987648</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>BLVD FLOR DE LIZ</t>
-        </is>
-      </c>
+          <t>6673450501</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3185,60 +3181,56 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>15-06-1994</t>
+          <t>08-10-2007</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>EDGAR.VLA@HOTMAIL.COM</t>
+          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>07-02-2026 13:08:56</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>04-02-2026 13:04:54</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>07-02-2026 13:12:58</t>
+          <t>04-02-2026 13:06:15</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>07-02-2026 13:12:39</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3246,36 +3238,36 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26040522161580002258</t>
+          <t>26040522074180002020</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340395</t>
+          <t>343891</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3285,17 +3277,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SARAH FABIOLA</t>
+          <t>SETH SEBASTIAN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORRAZ </t>
+          <t xml:space="preserve">SANDOVAL </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3305,67 +3297,79 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6674779002</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6871298029</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AUARUTO </t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>05-10-2004</t>
+          <t>04-06-2008</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SARAHABORRAZ05@GMAIL.COM</t>
+          <t>SETHSEBASTIANSANDOVALFLORES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-02-2026 20:56:33</t>
+          <t>15-02-2026 19:53:47</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>05-02-2026 20:14:53</t>
+          <t>23-02-2026 13:01:00</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>23-02-2026 13:00:32</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3373,7 +3377,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26040522119630002171</t>
+          <t>26040522579910003180</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3381,14 +3385,10 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3405,12 +3405,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340980</t>
+          <t>343909</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3420,17 +3420,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">GLORIA GUADALUPE </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3440,35 +3440,31 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6673450501</t>
+          <t>6672155907</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>26-10-1982</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
+          <t>PARRAGLORIA321@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>04-02-2026 13:04:54</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 04:41:54</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3476,22 +3472,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>04-02-2026 13:06:15</t>
+          <t>16-02-2026 04:45:09</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -3508,36 +3504,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26040522074180002020</t>
+          <t>26040522369220002705</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342743</t>
+          <t>344104</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3547,17 +3543,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCTAVIANO </t>
+          <t xml:space="preserve">MARIA FERNANDA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>AMEZQUITA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAUCEDA </t>
+          <t xml:space="preserve">MACHADO </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3567,63 +3563,67 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6731436529</t>
+          <t>6862342452</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRRANOVA </t>
+          <t xml:space="preserve">SANTA ROCIO </t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20-11-2000</t>
+          <t>27-01-1995</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
+          <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10-02-2026 17:15:49</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>16-02-2026 14:49:21</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10-02-2026 17:22:40</t>
+          <t>16-02-2026 14:53:31</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10-02-2026 17:22:03</t>
+          <t>16-02-2026 14:52:00</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3643,19 +3643,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26040522239600002442</t>
+          <t>26040522391260002745</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3667,12 +3667,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>343530</t>
+          <t>343908</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3682,17 +3682,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MAURO EMMANUEL</t>
+          <t>LUIS JESUS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t xml:space="preserve">ANGULO </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3702,14 +3702,10 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6674640838</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CULIACANCITO </t>
-        </is>
-      </c>
+          <t>6672551941</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3717,60 +3713,52 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>04-04-2005</t>
+          <t>20-01-2010</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
+          <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:11</t>
+          <t>16-02-2026 04:37:58</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>13-02-2026 16:30:21</t>
+          <t>16-02-2026 04:39:44</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>13-02-2026 16:29:54</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3778,19 +3766,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26040522324290002650</t>
+          <t>26040522369190002704</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3802,12 +3790,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>342326</t>
+          <t>341657</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3817,17 +3805,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIAN </t>
+          <t xml:space="preserve">KEVIN RICARDO </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MONTES</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMPOS </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3837,32 +3825,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6675145803</t>
+          <t>3224537874</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAS DEL RIO </t>
+          <t xml:space="preserve">LA ESTANCIA </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21-12-1999</t>
+          <t>05-08-1995</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MARIANONTES125@GMAIL.COM</t>
+          <t>DISTRITOTRECEE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>09-02-2026 17:29:11</t>
+          <t>06-02-2026 18:05:27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3883,17 +3871,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:56</t>
+          <t>06-02-2026 18:09:06</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>09-02-2026 17:30:19</t>
+          <t>06-02-2026 18:08:40</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3913,7 +3901,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26040522202510002352</t>
+          <t>26040522144380002227</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3925,24 +3913,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>343908</t>
+          <t>341829</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3952,17 +3940,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LUIS JESUS</t>
+          <t>EDGAR FRANCISCO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">MANZANO </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGULO </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3972,10 +3960,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6672551941</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6676987648</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BLVD FLOR DE LIZ</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3983,52 +3975,60 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20-01-2010</t>
+          <t>15-06-1994</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>PARRAANGUNGULOLUISJESUS@GMAIL.COM</t>
+          <t>EDGAR.VLA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>16-02-2026 04:37:58</t>
+          <t>07-02-2026 13:08:56</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>16-02-2026 04:39:44</t>
+          <t>07-02-2026 13:12:58</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>07-02-2026 13:12:39</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4036,14 +4036,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26040522369190002704</t>
+          <t>26040522161580002258</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4060,12 +4060,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>342397</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4075,17 +4075,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSE GUADALLUPE</t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t xml:space="preserve">LEYVA </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4095,14 +4095,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6673961529</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARGENTINA </t>
-        </is>
-      </c>
+          <t>6674049839</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4110,60 +4106,56 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>06-09-2006</t>
+          <t>15-10-1992</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
+          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13-02-2026 16:37:04</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>09-02-2026 18:34:08</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>13-02-2026 16:39:33</t>
+          <t>11-02-2026 18:23:52</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>13-02-2026 16:39:06</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4171,19 +4163,27 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26040522324550002655</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26040522273970002541</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Pedro Fernando  Salas RECEPCION</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4195,12 +4195,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>343614</t>
+          <t>344702</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN FRANCISCO </t>
+          <t xml:space="preserve">MARLETH </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>OROPEZA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">DOMINGUEZ </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4230,67 +4230,75 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6671911835</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6671444793</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>17-03-2007</t>
+          <t>27-05-2005</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JFX4318@GMAIL.COM</t>
+          <t>MARLETH5002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13-02-2026 20:07:29</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>17-02-2026 20:20:03</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>16-02-2026 19:40:20</t>
+          <t>17-02-2026 20:22:39</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>17-02-2026 20:21:36</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4298,36 +4306,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26040522408860002801</t>
+          <t>26040522446310002893</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>343865</t>
+          <t>342743</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4337,17 +4345,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VLADIMIR </t>
+          <t xml:space="preserve">OCTAVIANO </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">SAUCEDA </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4357,10 +4365,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6872535687</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6731436529</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRRANOVA </t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4368,56 +4380,60 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>23-01-2009</t>
+          <t>20-11-2000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
+          <t>SAUCEDAOLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15-02-2026 14:10:10</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>10-02-2026 17:15:49</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>15-02-2026 14:11:41</t>
+          <t>10-02-2026 17:22:40</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>10-02-2026 17:22:03</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4425,19 +4441,19 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26040522367230002693</t>
+          <t>26040522239600002442</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4449,12 +4465,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>344131</t>
+          <t>346066</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>88231</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4464,17 +4480,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MILDERED HARUMI</t>
+          <t>CARLOS RODRIGO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCHA </t>
+          <t>NIEBLAS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4484,79 +4500,63 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6673878560</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
-        </is>
-      </c>
+          <t>6673160433</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>01-09-1992</t>
+          <t>13-03-1994</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
+          <t>RODRIGORODRIGO1994RIVERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>16-02-2026 15:42:58</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>24-02-2026 06:14:38</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>18-02-2026 15:55:22</t>
+          <t>24-02-2026 06:16:43</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>18-02-2026 15:33:30</t>
-        </is>
-      </c>
+          <t>24-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4564,27 +4564,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26040522465030002939</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522610020003260</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4596,12 +4588,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343897</t>
+          <t>342326</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4611,17 +4603,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t xml:space="preserve">MARIAN </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MONTES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OCEGUEDA</t>
+          <t xml:space="preserve">CAMPOS </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4631,67 +4623,75 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6671043288</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6675145803</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLAS DEL RIO </t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>13-11-2000</t>
+          <t>21-12-1999</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>MIGUELHO13@GMAIL.COM</t>
+          <t>MARIANONTES125@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>15-02-2026 21:36:16</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:29:11</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>19-02-2026 04:36:58</t>
+          <t>09-02-2026 17:30:56</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:30:19</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4699,22 +4699,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26040522478480002982</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522202510002352</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4731,12 +4723,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343888</t>
+          <t>345887</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>88052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4746,17 +4738,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LIZBETH YARELI</t>
+          <t xml:space="preserve">BRAYAN </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">NORIEGA </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">GASTELUM </t>
+          <t xml:space="preserve">DUARTE </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4766,35 +4758,31 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6672004222</t>
+          <t>6677804463</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>22-10-2001</t>
+          <t>04-03-2010</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>LIZBETHHERNANDEZ4222@GMAIL.COM</t>
+          <t>NORIEGADUARTEBRAYAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>15-02-2026 18:04:14</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>23-02-2026 16:43:27</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4802,22 +4790,22 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>25-02-2026 13:14:17</t>
+          <t>23-02-2026 16:44:27</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -4834,44 +4822,36 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26040522652230003366</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522588220003214</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343890</t>
+          <t>344131</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21707</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4881,17 +4861,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA LUCIA </t>
+          <t>MILDERED HARUMI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMARILLAS </t>
+          <t xml:space="preserve">ROCHA </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN QUI </t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4901,12 +4881,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6673938349</t>
+          <t>6673878560</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUARUTO </t>
+          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4916,17 +4896,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>23-09-2008</t>
+          <t>01-09-1992</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ANAJUANQUI08@GMAIL.COM</t>
+          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15-02-2026 19:50:41</t>
+          <t>16-02-2026 15:42:58</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4951,17 +4931,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>23-02-2026 12:57:58</t>
+          <t>18-02-2026 15:55:22</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>23-02-2026 12:51:21</t>
+          <t>18-02-2026 15:33:30</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4981,7 +4961,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26040522579820003179</t>
+          <t>26040522465030002939</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4989,7 +4969,11 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>499</t>
@@ -4997,24 +4981,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343896</t>
+          <t>343533</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5024,17 +5008,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA SOFIA </t>
+          <t>JOSE GUADALLUPE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMARILLAS </t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JUAN QUI</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5044,39 +5028,35 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6677758152</t>
+          <t>6673961529</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AGUARUTO</t>
+          <t xml:space="preserve">ARGENTINA </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>04-12-2010</t>
+          <t>06-09-2006</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
+          <t>JOSERGUADALUPERGPE0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15-02-2026 21:30:58</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:37:04</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5094,17 +5074,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>23-02-2026 13:06:24</t>
+          <t>13-02-2026 16:39:33</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>23-02-2026 13:05:56</t>
+          <t>13-02-2026 16:39:06</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5124,14 +5104,10 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26040522580090003182</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522324550002655</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
@@ -5140,24 +5116,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343922</t>
+          <t>343614</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5167,17 +5143,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRENE </t>
+          <t xml:space="preserve">JUAN FRANCISCO </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5187,31 +5163,35 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6674077607</t>
+          <t>6671911835</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19-10-1976</t>
+          <t>17-03-2007</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
+          <t>JFX4318@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16-02-2026 06:00:38</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>13-02-2026 20:07:29</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5219,28 +5199,28 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>16-02-2026 06:02:04</t>
+          <t>16-02-2026 19:40:20</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -5251,36 +5231,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26040522371170002712</t>
+          <t>26040522408860002801</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>345887</t>
+          <t>343897</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>88052</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5290,17 +5270,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRAYAN </t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORIEGA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUARTE </t>
+          <t>OCEGUEDA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5310,7 +5290,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6677804463</t>
+          <t>6671043288</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5321,20 +5301,24 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>04-03-2010</t>
+          <t>13-11-2000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NORIEGADUARTEBRAYAN@GMAIL.COM</t>
+          <t>MIGUELHO13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>23-02-2026 16:43:27</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>15-02-2026 21:36:16</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5342,28 +5326,28 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>23-02-2026 16:44:27</t>
+          <t>19-02-2026 04:36:58</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -5374,14 +5358,22 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26040522588220003214</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26040522478480002982</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5398,12 +5390,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343906</t>
+          <t>343888</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5413,17 +5405,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA REBECA </t>
+          <t>LIZBETH YARELI</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">GASTELUM </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5433,7 +5425,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6674722142</t>
+          <t>6672004222</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5444,20 +5436,24 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>25-11-2005</t>
+          <t>22-10-2001</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ADRIANAPARRA2500@GMAIL.COM</t>
+          <t>LIZBETHHERNANDEZ4222@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16-02-2026 04:24:57</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>15-02-2026 18:04:14</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -5465,28 +5461,28 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>16-02-2026 04:34:04</t>
+          <t>25-02-2026 13:14:17</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -5497,19 +5493,27 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26040522369090002701</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26040522652230003366</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5521,12 +5525,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344139</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5536,17 +5540,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">KATHERINE </t>
+          <t xml:space="preserve">ANA LUCIA </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">JUAN QUI </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5556,10 +5560,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6671456800</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6673938349</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUARUTO </t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5567,56 +5575,64 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>05-01-2008</t>
+          <t>23-09-2008</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>KAT0508SAN@GMAIL.COM</t>
+          <t>ANAJUANQUI08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 15:58:58</t>
+          <t>15-02-2026 19:50:41</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>16-02-2026 16:00:45</t>
+          <t>23-02-2026 12:57:58</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>23-02-2026 12:51:21</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5624,36 +5640,40 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26040522394190002754</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
+          <t>26040522579820003179</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>344617</t>
+          <t>343896</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>21713</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5663,17 +5683,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTO </t>
+          <t xml:space="preserve">KARLA SOFIA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJO </t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>JUAN QUI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5683,67 +5703,79 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6671751779</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6677758152</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AGUARUTO</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>21-02-2000</t>
+          <t>04-12-2010</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ALBERTOROJO21@HOTMAIL.COM</t>
+          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>17-02-2026 17:34:00</t>
+          <t>15-02-2026 21:30:58</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-02-2026 17:35:27</t>
+          <t>23-02-2026 13:06:24</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>23-02-2026 13:05:56</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5751,14 +5783,18 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26040522438040002865</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
+          <t>26040522580090003182</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5775,12 +5811,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>343922</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5790,17 +5826,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS ALONSO </t>
+          <t xml:space="preserve">IRENE </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTA </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5810,79 +5846,63 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6721229789</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>CAMPO BELLO</t>
-        </is>
-      </c>
+          <t>6674077607</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>08-11-1995</t>
+          <t>19-10-1976</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
+          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-02-2026 19:03:39</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>16-02-2026 06:00:38</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>16-02-2026 19:05:32</t>
+          <t>16-02-2026 06:02:04</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>16-02-2026 19:05:10</t>
-        </is>
-      </c>
+          <t>16-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5890,19 +5910,19 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26040522407060002792</t>
+          <t>26040522371170002712</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -5914,12 +5934,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344705</t>
+          <t>343865</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5929,17 +5949,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t xml:space="preserve">VLADIMIR </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5949,75 +5969,67 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6673290828</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>TERRAZAS</t>
-        </is>
-      </c>
+          <t>6872535687</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>16-03-2004</t>
+          <t>23-01-2009</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>DIANA_SR16@OUTLOOK.COM</t>
+          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>17-02-2026 20:25:26</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>15-02-2026 14:10:10</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>17-02-2026 20:27:25</t>
+          <t>15-02-2026 14:11:41</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>17-02-2026 20:26:49</t>
-        </is>
-      </c>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6025,19 +6037,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26040522446490002894</t>
+          <t>26040522367230002693</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6049,12 +6061,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>345025</t>
+          <t>344705</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6064,17 +6076,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t xml:space="preserve">DIANA LAURA </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BARCENAS</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6084,12 +6096,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6675028294</t>
+          <t>6673290828</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">LA ESTANCIA </t>
+          <t>TERRAZAS</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6099,17 +6111,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>06-09-2002</t>
+          <t>16-03-2004</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>MORE312BARCENAS@GMAIL.COM</t>
+          <t>DIANA_SR16@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>03-05-2022 16:58:45</t>
+          <t>17-02-2026 20:25:26</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6120,7 +6132,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6130,27 +6142,27 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>03-02-2026 20:16:29</t>
+          <t>17-02-2026 20:27:25</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>03-02-2026 20:16:29</t>
+          <t>17-02-2026 20:26:49</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -6160,7 +6172,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26040522491060002999</t>
+          <t>26040522446490002894</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6172,24 +6184,24 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>345143</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>87308</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6199,17 +6211,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KAREM YAZMIN</t>
+          <t xml:space="preserve">KATHERINE </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAYAN </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6219,14 +6231,10 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6677974107</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>RIO MOCORITO</t>
-        </is>
-      </c>
+          <t>6671456800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6234,64 +6242,56 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>07-08-1988</t>
+          <t>05-01-2008</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>KARENY1288@HOTMAIL.COM</t>
+          <t>KAT0508SAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>19-02-2026 17:26:39</t>
+          <t>16-02-2026 15:58:58</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>19-02-2026 17:31:08</t>
+          <t>16-02-2026 16:00:45</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>19-02-2026 17:30:30</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6299,36 +6299,36 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26040522501600003040</t>
+          <t>26040522394190002754</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>345640</t>
+          <t>343906</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>87805</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6338,17 +6338,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JOSE GUILLERMO</t>
+          <t xml:space="preserve">ADRIANA REBECA </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">JACOBO </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6358,28 +6358,28 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6671911283</t>
+          <t>6674722142</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>16-02-1991</t>
+          <t>25-11-2005</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
+          <t>ADRIANAPARRA2500@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>23-02-2026 04:19:03</t>
+          <t>16-02-2026 04:24:57</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6390,22 +6390,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>23-02-2026 04:20:44</t>
+          <t>16-02-2026 04:34:04</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -6422,36 +6422,36 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26040522565240003147</t>
+          <t>26040522369090002701</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>345656</t>
+          <t>344617</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>87821</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6461,17 +6461,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ROJILY VANESSA</t>
+          <t xml:space="preserve">ALBERTO </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">ROJO </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6481,31 +6481,35 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6672345223</t>
+          <t>6671751779</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>27-03-1982</t>
+          <t>21-02-2000</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>RUCALETA2703@GMAIL.COM</t>
+          <t>ALBERTOROJO21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>23-02-2026 07:31:25</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>17-02-2026 17:34:00</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6513,22 +6517,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>23-02-2026 07:33:17</t>
+          <t>17-02-2026 17:35:27</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -6545,36 +6549,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26040522572650003159</t>
+          <t>26040522438040002865</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>345961</t>
+          <t>345655</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>88126</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6584,17 +6588,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARJORIE </t>
+          <t>ITZEL PAULINA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">X </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6604,7 +6608,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6674972190</t>
+          <t>6183256686</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6615,17 +6619,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>31-12-2004</t>
+          <t>10-10-1997</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MARJORIEV312@GMAIL.COM</t>
+          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>23-02-2026 18:08:53</t>
+          <t>23-02-2026 07:26:26</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6636,28 +6640,28 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>25-02-2026 18:17:21</t>
+          <t>23-02-2026 07:29:03</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>25-05-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -6668,44 +6672,36 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26040522662960003400</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522572610003158</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343891</t>
+          <t>344328</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6715,17 +6711,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SETH SEBASTIAN</t>
+          <t xml:space="preserve">CARLOS ALONSO </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDOVAL </t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">COTA </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6735,12 +6731,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6871298029</t>
+          <t>6721229789</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUARUTO </t>
+          <t>CAMPO BELLO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6750,17 +6746,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>04-06-2008</t>
+          <t>08-11-1995</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>SETHSEBASTIANSANDOVALFLORES@GMAIL.COM</t>
+          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>15-02-2026 19:53:47</t>
+          <t>16-02-2026 19:03:39</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6785,17 +6781,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>23-02-2026 13:01:00</t>
+          <t>16-02-2026 19:05:32</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>23-02-2026 13:00:32</t>
+          <t>16-02-2026 19:05:10</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6805,7 +6801,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6815,14 +6811,10 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26040522579910003180</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522407060002792</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
@@ -6831,24 +6823,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343909</t>
+          <t>345025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6858,17 +6850,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA GUADALUPE </t>
+          <t>MORELIA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t>BARCENAS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6878,10 +6870,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6672155907</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6675028294</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA ESTANCIA </t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6889,52 +6885,60 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>26-10-1982</t>
+          <t>06-09-2002</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>PARRAGLORIA321@GMAIL.COM</t>
+          <t>MORE312BARCENAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 04:41:54</t>
+          <t>03-05-2022 16:58:45</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-02-2026 04:45:09</t>
+          <t>03-02-2026 20:16:29</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>03-02-2026 20:16:29</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6942,36 +6946,36 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26040522369220002705</t>
+          <t>26040522491060002999</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344104</t>
+          <t>345143</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>87308</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6981,17 +6985,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA FERNANDA </t>
+          <t>KAREM YAZMIN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AMEZQUITA</t>
+          <t xml:space="preserve">PAYAN </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACHADO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7001,12 +7005,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6862342452</t>
+          <t>6677974107</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA ROCIO </t>
+          <t>RIO MOCORITO</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7016,52 +7020,52 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>27-01-1995</t>
+          <t>07-08-1988</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>FERNANDAAMEZQUITA@GAMIL.COM</t>
+          <t>KARENY1288@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>16-02-2026 14:49:21</t>
+          <t>19-02-2026 17:26:39</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>16-02-2026 14:53:31</t>
+          <t>19-02-2026 17:31:08</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>16-02-2026 14:52:00</t>
+          <t>19-02-2026 17:30:30</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7071,7 +7075,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7081,36 +7085,36 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26040522391260002745</t>
+          <t>26040522501600003040</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345655</t>
+          <t>345640</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87820</t>
+          <t>87805</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7120,17 +7124,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ITZEL PAULINA</t>
+          <t>JOSE GUILLERMO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">JACOBO </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7140,28 +7144,28 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6183256686</t>
+          <t>6671911283</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>10-10-1997</t>
+          <t>16-02-1991</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
+          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>23-02-2026 07:26:26</t>
+          <t>23-02-2026 04:19:03</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7182,7 +7186,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-02-2026 07:29:03</t>
+          <t>23-02-2026 04:20:44</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7204,7 +7208,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26040522572610003158</t>
+          <t>26040522565240003147</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7216,24 +7220,24 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>346409</t>
+          <t>345961</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>88574</t>
+          <t>88126</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7243,17 +7247,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ELIZABETH </t>
+          <t xml:space="preserve">MARJORIE </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">X </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7263,14 +7267,10 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>3141032513</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AGUARUTO </t>
-        </is>
-      </c>
+          <t>6674972190</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7278,64 +7278,52 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>24-01-2011</t>
+          <t>31-12-2004</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>GUADALUPE160509@GMAIL.COM</t>
+          <t>MARJORIEV312@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>25-02-2026 09:54:31</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>23-02-2026 18:08:53</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>25-02-2026 09:59:54</t>
+          <t>25-02-2026 18:17:21</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>25-02-2026 09:58:27</t>
-        </is>
-      </c>
+          <t>25-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7343,14 +7331,22 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26040522648990003357</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
+          <t>26040522662960003400</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7367,12 +7363,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344702</t>
+          <t>345656</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>87821</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7382,17 +7378,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLETH </t>
+          <t>ROJILY VANESSA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OROPEZA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOMINGUEZ </t>
+          <t>X</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7402,14 +7398,10 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6671444793</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
-        </is>
-      </c>
+          <t>6672345223</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7417,60 +7409,52 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>27-05-2005</t>
+          <t>27-03-1982</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>MARLETH5002@GMAIL.COM</t>
+          <t>RUCALETA2703@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>17-02-2026 20:20:03</t>
+          <t>23-02-2026 07:31:25</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>17-02-2026 20:22:39</t>
+          <t>23-02-2026 07:33:17</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>17-02-2026 20:21:36</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7478,14 +7462,14 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26040522446310002893</t>
+          <t>26040522572650003159</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7502,12 +7486,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>346066</t>
+          <t>346409</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>88231</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7517,17 +7501,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CARLOS RODRIGO</t>
+          <t xml:space="preserve">MARIA ELIZABETH </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NIEBLAS</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7537,63 +7521,79 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6673160433</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>3141032513</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUARUTO </t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>13-03-1994</t>
+          <t>24-01-2011</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>RODRIGORODRIGO1994RIVERA@GMAIL.COM</t>
+          <t>GUADALUPE160509@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>24-02-2026 06:14:38</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>25-02-2026 09:54:31</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>24-02-2026 06:16:43</t>
+          <t>25-02-2026 09:59:54</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>24-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>25-02-2026 09:58:27</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7601,24 +7601,24 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26040522610020003260</t>
+          <t>26040522648990003357</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -713,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>305321</t>
+          <t>302189</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>99687</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LESLYE LIBIER</t>
+          <t xml:space="preserve">NIDIA ADME </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MEDRANO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,14 +748,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6671399083</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>BARRANCOS</t>
-        </is>
-      </c>
+          <t>6671760805</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -763,64 +759,52 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24-01-2002</t>
+          <t>01-10-1977</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MEDRANO_LESLYE@HOTMAIL.COM</t>
+          <t>NIDIAMEDINA@LIVE.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22-07-2025 10:29:16</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>05-07-2025 06:34:10</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>24-02-2026 13:58:09</t>
+          <t>22-02-2026 14:25:33</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>24-02-2026 13:56:59</t>
-        </is>
-      </c>
+          <t>22-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -828,36 +812,40 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26040522619700003290</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26040522564200003144</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>302189</t>
+          <t>305321</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>99687</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIDIA ADME </t>
+          <t>LESLYE LIBIER</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MEDRANO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,10 +875,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6671760805</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6671399083</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BARRANCOS</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -898,52 +890,64 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>01-10-1977</t>
+          <t>24-01-2002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>NIDIAMEDINA@LIVE.COM</t>
+          <t>MEDRANO_LESLYE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>05-07-2025 06:34:10</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>22-07-2025 10:29:16</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22-02-2026 14:25:33</t>
+          <t>24-02-2026 13:58:09</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>22-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>24-02-2026 13:56:59</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -951,28 +955,24 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26040522564200003144</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26040522619700003290</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2738,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341744</t>
+          <t>340980</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2753,17 +2753,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAMACHO </t>
+          <t xml:space="preserve">PONCE </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARO </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3221713510</t>
+          <t>6673450501</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2784,17 +2784,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12-12-1974</t>
+          <t>08-10-2007</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
+          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>07-02-2026 07:59:31</t>
+          <t>04-02-2026 13:04:54</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2809,28 +2809,28 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>07-02-2026 08:01:13</t>
+          <t>04-02-2026 13:06:15</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -2841,14 +2841,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26040522155670002240</t>
+          <t>26040522074180002020</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>343530</t>
+          <t>340395</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2880,17 +2880,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MAURO EMMANUEL</t>
+          <t>SARAH FABIOLA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">BORRAZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2900,75 +2900,67 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6674640838</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CULIACANCITO </t>
-        </is>
-      </c>
+          <t>6674779002</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>04-04-2005</t>
+          <t>05-10-2004</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
+          <t>SARAHABORRAZ05@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>13-02-2026 16:28:11</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>02-02-2026 20:56:33</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>13-02-2026 16:30:21</t>
+          <t>05-02-2026 20:14:53</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>13-02-2026 16:29:54</t>
-        </is>
-      </c>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2976,36 +2968,44 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26040522324290002650</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26040522119630002171</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340395</t>
+          <t>343530</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3015,17 +3015,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SARAH FABIOLA</t>
+          <t>MAURO EMMANUEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORRAZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3035,67 +3035,75 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6674779002</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6674640838</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CULIACANCITO </t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>05-10-2004</t>
+          <t>04-04-2005</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>SARAHABORRAZ05@GMAIL.COM</t>
+          <t>MAUROEMMANUEL0404@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-02-2026 20:56:33</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>13-02-2026 16:28:11</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05-02-2026 20:14:53</t>
+          <t>13-02-2026 16:30:21</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>13-02-2026 16:29:54</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3103,44 +3111,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26040522119630002171</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522324290002650</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340980</t>
+          <t>341744</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3150,17 +3150,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">PEDRO </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">PONCE </t>
+          <t xml:space="preserve">CAMACHO </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">HARO </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6673450501</t>
+          <t>3221713510</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3181,17 +3181,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>08-10-2007</t>
+          <t>12-12-1974</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PONCEGONZALEZJUANJOSE@GMAIL.COM</t>
+          <t>PEDROCAMACHOPV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-02-2026 13:04:54</t>
+          <t>07-02-2026 07:59:31</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3206,28 +3206,28 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-02-2026 13:06:15</t>
+          <t>07-02-2026 08:01:13</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -3238,14 +3238,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26040522074180002020</t>
+          <t>26040522155670002240</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -4060,12 +4060,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342397</t>
+          <t>344702</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4075,17 +4075,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GUSTAVO</t>
+          <t xml:space="preserve">MARLETH </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEYVA </t>
+          <t>OROPEZA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t xml:space="preserve">DOMINGUEZ </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4095,67 +4095,75 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6674049839</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6671444793</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>15-10-1992</t>
+          <t>27-05-2005</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
+          <t>MARLETH5002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 18:34:08</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>17-02-2026 20:20:03</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>11-02-2026 18:23:52</t>
+          <t>17-02-2026 20:22:39</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>17-02-2026 20:21:36</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4163,27 +4171,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26040522273970002541</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Pedro Fernando  Salas RECEPCION</t>
-        </is>
-      </c>
+          <t>26040522446310002893</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4195,12 +4195,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>344702</t>
+          <t>342397</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22519</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLETH </t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OROPEZA</t>
+          <t xml:space="preserve">LEYVA </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOMINGUEZ </t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4230,75 +4230,67 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6671444793</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VILLAS DE MANANTIAL </t>
-        </is>
-      </c>
+          <t>6674049839</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27-05-2005</t>
+          <t>15-10-1992</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MARLETH5002@GMAIL.COM</t>
+          <t>GUSTAVO_LEYVAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17-02-2026 20:20:03</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>09-02-2026 18:34:08</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>17-02-2026 20:22:39</t>
+          <t>11-02-2026 18:23:52</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>17-02-2026 20:21:36</t>
-        </is>
-      </c>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4306,19 +4298,27 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26040522446310002893</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>26040522273970002541</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Pedro Fernando  Salas RECEPCION</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4846,12 +4846,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>344131</t>
+          <t>343897</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MILDERED HARUMI</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROCHA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t>OCEGUEDA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4881,79 +4881,67 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6673878560</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
-        </is>
-      </c>
+          <t>6671043288</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>01-09-1992</t>
+          <t>13-11-2000</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
+          <t>MIGUELHO13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16-02-2026 15:42:58</t>
+          <t>15-02-2026 21:36:16</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>18-02-2026 15:55:22</t>
+          <t>19-02-2026 04:36:58</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>18-02-2026 15:33:30</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4961,32 +4949,32 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26040522465030002939</t>
+          <t>26040522478480002982</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -5255,12 +5243,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343897</t>
+          <t>344131</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5270,17 +5258,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>MILDERED HARUMI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">ROCHA </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>OCEGUEDA</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5290,67 +5278,79 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6671043288</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6673878560</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C MINA GUADALUPE DE LOS REYES 1461</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13-11-2000</t>
+          <t>01-09-1992</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MIGUELHO13@GMAIL.COM</t>
+          <t>MILDREDROCHAMEZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>15-02-2026 21:36:16</t>
+          <t>16-02-2026 15:42:58</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>19-02-2026 04:36:58</t>
+          <t>18-02-2026 15:55:22</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>18-02-2026 15:33:30</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5358,44 +5358,44 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26040522478480002982</t>
+          <t>26040522465030002939</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343888</t>
+          <t>343865</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5405,19 +5405,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LIZBETH YARELI</t>
+          <t xml:space="preserve">VLADIMIR </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t xml:space="preserve">RENTERIA </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GASTELUM </t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>52</t>
@@ -5425,28 +5425,28 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6672004222</t>
+          <t>6872535687</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>22-10-2001</t>
+          <t>23-01-2009</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>LIZBETHHERNANDEZ4222@GMAIL.COM</t>
+          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>15-02-2026 18:04:14</t>
+          <t>15-02-2026 14:10:10</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5471,18 +5471,18 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>25-02-2026 13:14:17</t>
+          <t>15-02-2026 14:11:41</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -5493,19 +5493,11 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26040522652230003366</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522367230002693</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>549</t>
@@ -5525,12 +5517,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343890</t>
+          <t>343888</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21707</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5540,17 +5532,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA LUCIA </t>
+          <t>LIZBETH YARELI</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMARILLAS </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN QUI </t>
+          <t xml:space="preserve">GASTELUM </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5560,14 +5552,10 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6673938349</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AGUARUTO </t>
-        </is>
-      </c>
+          <t>6672004222</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5575,64 +5563,56 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>23-09-2008</t>
+          <t>22-10-2001</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ANAJUANQUI08@GMAIL.COM</t>
+          <t>LIZBETHHERNANDEZ4222@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>15-02-2026 19:50:41</t>
+          <t>15-02-2026 18:04:14</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>23-02-2026 12:57:58</t>
+          <t>25-02-2026 13:14:17</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>23-02-2026 12:51:21</t>
-        </is>
-      </c>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5640,7 +5620,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26040522579820003179</t>
+          <t>26040522652230003366</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5648,32 +5628,36 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343896</t>
+          <t>343890</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21713</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5683,7 +5667,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA SOFIA </t>
+          <t xml:space="preserve">ANA LUCIA </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5693,7 +5677,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JUAN QUI</t>
+          <t xml:space="preserve">JUAN QUI </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5703,12 +5687,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6677758152</t>
+          <t>6673938349</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AGUARUTO</t>
+          <t xml:space="preserve">AGUARUTO </t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5718,17 +5702,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>04-12-2010</t>
+          <t>23-09-2008</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
+          <t>ANAJUANQUI08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>15-02-2026 21:30:58</t>
+          <t>15-02-2026 19:50:41</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5753,7 +5737,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>23-02-2026 13:06:24</t>
+          <t>23-02-2026 12:57:58</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5763,7 +5747,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>23-02-2026 13:05:56</t>
+          <t>23-02-2026 12:51:21</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5783,7 +5767,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26040522580090003182</t>
+          <t>26040522579820003179</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5811,12 +5795,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343922</t>
+          <t>343896</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21713</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5826,17 +5810,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRENE </t>
+          <t xml:space="preserve">KARLA SOFIA </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAVARRO </t>
+          <t xml:space="preserve">AMARILLAS </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>JUAN QUI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5846,10 +5830,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6674077607</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6677758152</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>AGUARUTO</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5857,52 +5845,64 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>19-10-1976</t>
+          <t>04-12-2010</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
+          <t>KARLASOFIAJUANQUI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>16-02-2026 06:00:38</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>15-02-2026 21:30:58</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>16-02-2026 06:02:04</t>
+          <t>23-02-2026 13:06:24</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>23-02-2026 13:05:56</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5910,36 +5910,40 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26040522371170002712</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>26040522580090003182</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>343865</t>
+          <t>343922</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21682</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5949,17 +5953,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">VLADIMIR </t>
+          <t xml:space="preserve">IRENE </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t xml:space="preserve">NAVARRO </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5969,35 +5973,31 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6872535687</t>
+          <t>6674077607</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23-01-2009</t>
+          <t>19-10-1976</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>VLADIMIRRENTERIIAHERNANDEZ41@GMAIL.COM</t>
+          <t>LAURAIRENE.NAVARRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>15-02-2026 14:10:10</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 06:00:38</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6005,22 +6005,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>15-02-2026 14:11:41</t>
+          <t>16-02-2026 06:02:04</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -6037,19 +6037,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26040522367230002693</t>
+          <t>26040522371170002712</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6061,12 +6061,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344705</t>
+          <t>344617</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6076,17 +6076,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA LAURA </t>
+          <t xml:space="preserve">ALBERTO </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">ROJO </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ROMAN</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6096,53 +6096,53 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6673290828</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>TERRAZAS</t>
-        </is>
-      </c>
+          <t>6671751779</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>16-03-2004</t>
+          <t>21-02-2000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>DIANA_SR16@OUTLOOK.COM</t>
+          <t>ALBERTOROJO21@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>17-02-2026 20:25:26</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>17-02-2026 17:34:00</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>17-02-2026 20:27:25</t>
+          <t>17-02-2026 17:35:27</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -6150,21 +6150,13 @@
           <t>17-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>17-02-2026 20:26:49</t>
-        </is>
-      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6172,36 +6164,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26040522446490002894</t>
+          <t>26040522438040002865</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>344139</t>
+          <t>344705</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6211,17 +6203,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">KATHERINE </t>
+          <t xml:space="preserve">DIANA LAURA </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>ROMAN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6231,10 +6223,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6671456800</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6673290828</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TERRAZAS</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6242,56 +6238,60 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>05-01-2008</t>
+          <t>16-03-2004</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>KAT0508SAN@GMAIL.COM</t>
+          <t>DIANA_SR16@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>16-02-2026 15:58:58</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>17-02-2026 20:25:26</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>16-02-2026 16:00:45</t>
+          <t>17-02-2026 20:27:25</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>17-02-2026 20:26:49</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6299,19 +6299,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26040522394190002754</t>
+          <t>26040522446490002894</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6323,12 +6323,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343906</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6338,17 +6338,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADRIANA REBECA </t>
+          <t xml:space="preserve">KATHERINE </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARRA </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6674722142</t>
+          <t>6671456800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6369,20 +6369,24 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>25-11-2005</t>
+          <t>05-01-2008</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ADRIANAPARRA2500@GMAIL.COM</t>
+          <t>KAT0508SAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-02-2026 04:24:57</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>16-02-2026 15:58:58</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6390,28 +6394,28 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16-02-2026 04:34:04</t>
+          <t>16-02-2026 16:00:45</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -6422,19 +6426,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26040522369090002701</t>
+          <t>26040522394190002754</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6446,12 +6450,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344617</t>
+          <t>343906</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6461,17 +6465,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALBERTO </t>
+          <t xml:space="preserve">ADRIANA REBECA </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJO </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">PARRA </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6481,35 +6485,31 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6671751779</t>
+          <t>6674722142</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>21-02-2000</t>
+          <t>25-11-2005</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ALBERTOROJO21@HOTMAIL.COM</t>
+          <t>ADRIANAPARRA2500@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>17-02-2026 17:34:00</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>16-02-2026 04:24:57</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -6517,22 +6517,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>17-02-2026 17:35:27</t>
+          <t>16-02-2026 04:34:04</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -6549,36 +6549,36 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26040522438040002865</t>
+          <t>26040522369090002701</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>345655</t>
+          <t>344328</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>87820</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ITZEL PAULINA</t>
+          <t xml:space="preserve">CARLOS ALONSO </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">COTA </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6608,63 +6608,79 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6183256686</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6721229789</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>CAMPO BELLO</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>10-10-1997</t>
+          <t>08-11-1995</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
+          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>23-02-2026 07:26:26</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>16-02-2026 19:03:39</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>23-02-2026 07:29:03</t>
+          <t>16-02-2026 19:05:32</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>16-02-2026 19:05:10</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6672,19 +6688,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26040522572610003158</t>
+          <t>26040522407060002792</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6696,12 +6712,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344328</t>
+          <t>345025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>87190</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6711,17 +6727,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS ALONSO </t>
+          <t>MORELIA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>BARCENAS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTA </t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6731,39 +6747,35 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6721229789</t>
+          <t>6675028294</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CAMPO BELLO</t>
+          <t xml:space="preserve">LA ESTANCIA </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>08-11-1995</t>
+          <t>06-09-2002</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CARLOSMEZA0811@OUTLOOK.COM</t>
+          <t>MORE312BARCENAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 19:03:39</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>03-05-2022 16:58:45</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6781,27 +6793,27 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 19:05:32</t>
+          <t>03-02-2026 20:16:29</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>16-02-2026 19:05:10</t>
+          <t>03-02-2026 20:16:29</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6811,7 +6823,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26040522407060002792</t>
+          <t>26040522491060002999</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6823,24 +6835,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>345025</t>
+          <t>345655</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>87190</t>
+          <t>87820</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6850,17 +6862,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MORELIA</t>
+          <t>ITZEL PAULINA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BARCENAS</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6870,14 +6882,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6675028294</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA ESTANCIA </t>
-        </is>
-      </c>
+          <t>6183256686</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6885,60 +6893,52 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>06-09-2002</t>
+          <t>10-10-1997</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MORE312BARCENAS@GMAIL.COM</t>
+          <t>ITZELPAULINAGARCIAMARTINEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>03-05-2022 16:58:45</t>
+          <t>23-02-2026 07:26:26</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>03-02-2026 20:16:29</t>
+          <t>23-02-2026 07:29:03</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>03-02-2026 20:16:29</t>
-        </is>
-      </c>
+          <t>23-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6946,24 +6946,24 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26040522491060002999</t>
+          <t>26040522572610003158</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345640</t>
+          <t>345961</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87805</t>
+          <t>88126</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7124,17 +7124,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JOSE GUILLERMO</t>
+          <t xml:space="preserve">MARJORIE </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">JACOBO </t>
+          <t xml:space="preserve">X </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7144,28 +7144,28 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6671911283</t>
+          <t>6674972190</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>16-02-1991</t>
+          <t>31-12-2004</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
+          <t>MARJORIEV312@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>23-02-2026 04:19:03</t>
+          <t>23-02-2026 18:08:53</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -7176,28 +7176,28 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-02-2026 04:20:44</t>
+          <t>25-02-2026 18:17:21</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>25-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -7208,14 +7208,22 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26040522565240003147</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>26040522662960003400</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7232,12 +7240,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>345961</t>
+          <t>345640</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>88126</t>
+          <t>87805</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7247,17 +7255,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARJORIE </t>
+          <t>JOSE GUILLERMO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">X </t>
+          <t xml:space="preserve">JACOBO </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7267,28 +7275,28 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6674972190</t>
+          <t>6671911283</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>31-12-2004</t>
+          <t>16-02-1991</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>MARJORIEV312@GMAIL.COM</t>
+          <t>JOSEGUILLERMO1407@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>23-02-2026 18:08:53</t>
+          <t>23-02-2026 04:19:03</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7299,28 +7307,28 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>25-02-2026 18:17:21</t>
+          <t>23-02-2026 04:20:44</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>25-05-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -7331,22 +7339,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26040522662960003400</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>26040522565240003147</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,6 +846,260 @@
       <c r="AC3" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>348168</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>90333</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOEL </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRIQUEZ </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6671343522</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>28-05-1989</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:21:19</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:23:02</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>26040522850490003786</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>348174</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>90339</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARBELLA ISAMAR </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORENO </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6671610495</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>14-04-1991</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:24:59</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:26:44</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>26040522850760003787</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346383</t>
+          <t>77498</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88548</t>
+          <t>75300</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICAELA </t>
+          <t xml:space="preserve">SERGIO LUIS </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENICEROS </t>
+          <t xml:space="preserve">RAZO </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">SOBERANES </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6671175730</t>
+          <t>6675688155</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>MANANTIAL DE LA CIENEGA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,38 +628,42 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>19-12-1994</t>
+          <t>06-12-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MICA94HDZ@HOTMAIL.COM</t>
+          <t>SERGIOLUISRAZO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>25-02-2026 08:24:59</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>07-03-2022 19:38:42</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 10:33:39</t>
+          <t>02-03-2026 20:53:55</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -667,21 +671,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 10:31:15</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -689,44 +685,36 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26040522787820003619</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522820230003715</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>346383</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75300</t>
+          <t>88548</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERGIO LUIS </t>
+          <t xml:space="preserve">MICAELA </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAZO </t>
+          <t xml:space="preserve">CENICEROS </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOBERANES </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,12 +744,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6675688155</t>
+          <t>6671175730</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MANANTIAL DE LA CIENEGA</t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -771,42 +759,38 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>06-12-2004</t>
+          <t>19-12-1994</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SERGIOLUISRAZO@GMAIL.COM</t>
+          <t>MICA94HDZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>07-03-2022 19:38:42</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>25-02-2026 08:24:59</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 20:53:55</t>
+          <t>02-03-2026 10:33:39</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -814,13 +798,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-03-2026 10:31:15</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -828,36 +820,44 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26040522820230003715</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26040522787820003619</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>348168</t>
+          <t>347427</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90333</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOEL </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERRIQUEZ </t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6671343522</t>
+          <t>6673463596</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -898,24 +898,20 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28-05-1989</t>
+          <t>24-09-1979</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
+          <t>ITZEL_LEON17@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>03-03-2026 17:21:19</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>02-03-2026 07:38:58</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -923,28 +919,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:02</t>
+          <t>05-03-2026 08:28:53</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -955,36 +951,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26040522850490003786</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26040522910760003927</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Pedro Fernando  Salas RECEPCION</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>348174</t>
+          <t>348168</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90339</t>
+          <t>90333</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARBELLA ISAMAR </t>
+          <t xml:space="preserve">JOEL </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t xml:space="preserve">TERRIQUEZ </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,28 +1018,28 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6671610495</t>
+          <t>6671343522</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14-04-1991</t>
+          <t>28-05-1989</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
+          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-03-2026 17:24:59</t>
+          <t>03-03-2026 17:21:19</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1060,7 +1064,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 17:26:44</t>
+          <t>03-03-2026 17:23:02</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1071,7 +1075,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1082,7 +1086,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26040522850760003787</t>
+          <t>26040522850490003786</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1098,6 +1102,268 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>348174</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90339</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARBELLA ISAMAR </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORENO </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6671610495</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>14-04-1991</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:24:59</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:26:44</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>26040522850760003787</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>348683</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>90848</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEBASTIAN </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUINTERO </t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIZCARRA </t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6672298295</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>02-05-2010</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SEBASTIANQV02@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:23:33</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:28:48</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>26040522914730003936</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>346383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>75300</t>
+          <t>88548</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERGIO LUIS </t>
+          <t xml:space="preserve">MICAELA </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAZO </t>
+          <t xml:space="preserve">CENICEROS </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOBERANES </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6675688155</t>
+          <t>6671175730</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MANANTIAL DE LA CIENEGA</t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,56 +628,60 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>06-12-2004</t>
+          <t>19-12-1994</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SERGIOLUISRAZO@GMAIL.COM</t>
+          <t>MICA94HDZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>07-03-2022 19:38:42</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>25-02-2026 08:24:59</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 20:53:55</t>
+          <t>02-03-2026 10:33:39</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>02-03-2026 10:31:15</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -685,36 +689,44 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26040522820230003715</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26040522787820003619</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346383</t>
+          <t>77498</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88548</t>
+          <t>75300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICAELA </t>
+          <t xml:space="preserve">SERGIO LUIS </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENICEROS </t>
+          <t xml:space="preserve">RAZO </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">SOBERANES </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,12 +756,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6671175730</t>
+          <t>6675688155</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>MANANTIAL DE LA CIENEGA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -759,60 +771,56 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19-12-1994</t>
+          <t>06-12-2004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MICA94HDZ@HOTMAIL.COM</t>
+          <t>SERGIOLUISRAZO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>25-02-2026 08:24:59</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>07-03-2022 19:38:42</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 10:33:39</t>
+          <t>02-03-2026 20:53:55</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 10:31:15</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,44 +828,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26040522787820003619</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522820230003715</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347427</t>
+          <t>345694</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89592</t>
+          <t>87859</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">PEDRO ANTONIO </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">TIRADO </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,31 +887,35 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6673463596</t>
+          <t>6674303529</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>24-09-1979</t>
+          <t>28-02-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ITZEL_LEON17@HOTMAIL.COM</t>
+          <t>PMENDOZA354@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 07:38:58</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>23-02-2026 10:22:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -919,28 +923,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>05-03-2026 08:28:53</t>
+          <t>07-03-2026 11:43:41</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -951,7 +955,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26040522910760003927</t>
+          <t>26040522974240004056</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -961,12 +965,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Pedro Fernando  Salas RECEPCION</t>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -983,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>348168</t>
+          <t>347427</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90333</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOEL </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERRIQUEZ </t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,7 +1022,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6671343522</t>
+          <t>6673463596</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,24 +1033,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-05-1989</t>
+          <t>24-09-1979</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
+          <t>ITZEL_LEON17@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-03-2026 17:21:19</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>02-03-2026 07:38:58</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1054,28 +1054,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:02</t>
+          <t>05-03-2026 08:28:53</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1086,36 +1086,44 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26040522850490003786</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26040522910760003927</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Pedro Fernando  Salas RECEPCION</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>348174</t>
+          <t>348168</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90339</t>
+          <t>90333</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARBELLA ISAMAR </t>
+          <t xml:space="preserve">JOEL </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t xml:space="preserve">TERRIQUEZ </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,28 +1153,28 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6671610495</t>
+          <t>6671343522</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14-04-1991</t>
+          <t>28-05-1989</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
+          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 17:24:59</t>
+          <t>03-03-2026 17:21:19</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1191,18 +1199,18 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 17:26:44</t>
+          <t>03-03-2026 17:23:02</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1213,7 +1221,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26040522850760003787</t>
+          <t>26040522850490003786</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1237,12 +1245,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>348683</t>
+          <t>348174</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90848</t>
+          <t>90339</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1252,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t xml:space="preserve">MARBELLA ISAMAR </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIZCARRA </t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1272,28 +1280,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6672298295</t>
+          <t>6671610495</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>02-05-2010</t>
+          <t>14-04-1991</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>SEBASTIANQV02@GMAIL.COM</t>
+          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>05-03-2026 12:23:33</t>
+          <t>03-03-2026 17:24:59</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1318,12 +1326,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-03-2026 12:28:48</t>
+          <t>03-03-2026 17:26:44</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1340,32 +1348,282 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
+          <t>26040522850760003787</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>348683</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>90848</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEBASTIAN </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUINTERO </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIZCARRA </t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6672298295</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>02-05-2010</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>SEBASTIANQV02@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:23:33</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:28:48</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>26040522914730003936</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>349156</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>91321</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSUE  GUADALUPE </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SICAIROS </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORALES </t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6671261289</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>13-10-2009</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>JOSHSICAIROS10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:42:52</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:45:15</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>06-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26040522975800004059</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346383</t>
+          <t>77498</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88548</t>
+          <t>75300</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICAELA </t>
+          <t xml:space="preserve">SERGIO LUIS </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENICEROS </t>
+          <t xml:space="preserve">RAZO </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">SOBERANES </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6671175730</t>
+          <t>6675688155</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CENTENARIO</t>
+          <t>MANANTIAL DE LA CIENEGA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,38 +628,42 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>19-12-1994</t>
+          <t>06-12-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>MICA94HDZ@HOTMAIL.COM</t>
+          <t>SERGIOLUISRAZO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>25-02-2026 08:24:59</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>07-03-2022 19:38:42</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 10:33:39</t>
+          <t>02-03-2026 20:53:55</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -667,21 +671,13 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>02-03-2026 10:31:15</t>
-        </is>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -689,44 +685,36 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26040522787820003619</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522820230003715</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>100408</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75300</t>
+          <t>98160</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERGIO LUIS </t>
+          <t>JACKELIN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAZO </t>
+          <t>JACOBO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOBERANES </t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,39 +744,35 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6675688155</t>
+          <t>6642312712</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MANANTIAL DE LA CIENEGA</t>
+          <t>AV. MARAVILLA 2005</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>06-12-2004</t>
+          <t>25-11-2004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SERGIOLUISRAZO@GMAIL.COM</t>
+          <t>MARQUEZ.JACKALYN.637@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>07-03-2022 19:38:42</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>14-06-2022 17:39:42</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -796,22 +780,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 20:53:55</t>
+          <t>16-03-2026 13:37:21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>15-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -828,14 +812,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26040522820230003715</t>
+          <t>26040523222020004540</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -852,12 +836,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>345694</t>
+          <t>346383</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>87859</t>
+          <t>88548</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +851,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO ANTONIO </t>
+          <t xml:space="preserve">MICAELA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t xml:space="preserve">CENICEROS </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIRADO </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,67 +871,75 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6674303529</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6671175730</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CENTENARIO</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28-02-2005</t>
+          <t>19-12-1994</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PMENDOZA354@OUTLOOK.COM</t>
+          <t>MICA94HDZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>23-02-2026 10:22:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>25-02-2026 08:24:59</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>07-03-2026 11:43:41</t>
+          <t>02-03-2026 10:33:39</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 10:31:15</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,7 +947,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26040522974240004056</t>
+          <t>26040522787820003619</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -970,29 +962,29 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347427</t>
+          <t>345694</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89592</t>
+          <t>87859</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1002,17 +994,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">PEDRO ANTONIO </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">TIRADO </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1022,31 +1014,35 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6673463596</t>
+          <t>6674303529</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24-09-1979</t>
+          <t>28-02-2005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ITZEL_LEON17@HOTMAIL.COM</t>
+          <t>PMENDOZA354@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 07:38:58</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>23-02-2026 10:22:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1054,28 +1050,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>05-03-2026 08:28:53</t>
+          <t>07-03-2026 11:43:41</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1086,7 +1082,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26040522910760003927</t>
+          <t>26040522974240004056</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1096,12 +1092,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Pedro Fernando  Salas RECEPCION</t>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1118,12 +1114,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>348168</t>
+          <t>347427</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90333</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1129,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOEL </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERRIQUEZ </t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,7 +1149,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6671343522</t>
+          <t>6673463596</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,24 +1160,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-05-1989</t>
+          <t>24-09-1979</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
+          <t>ITZEL_LEON17@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 17:21:19</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>02-03-2026 07:38:58</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1189,28 +1181,28 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:02</t>
+          <t>05-03-2026 08:28:53</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1221,36 +1213,44 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26040522850490003786</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26040522910760003927</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Pedro Fernando  Salas RECEPCION</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>348174</t>
+          <t>347883</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90339</t>
+          <t>90048</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARBELLA ISAMAR </t>
+          <t xml:space="preserve">ELIZABEHT </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,10 +1280,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6671610495</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6727515698</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERSALLES </t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1291,56 +1295,64 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14-04-1991</t>
+          <t>06-05-1995</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
+          <t>ELIZABETH.HERNANDEZ13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-03-2026 17:24:59</t>
+          <t>02-03-2026 19:46:47</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 17:26:44</t>
+          <t>09-03-2026 19:15:21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:13:52</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1348,36 +1360,40 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26040522850760003787</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26040523026580004165</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348683</t>
+          <t>347880</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90848</t>
+          <t>90045</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t xml:space="preserve">MARTHA PATRICIA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t xml:space="preserve">MILLER </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIZCARRA </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1407,67 +1423,79 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6672298295</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6721195585</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>VERSALLES</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>02-05-2010</t>
+          <t>26-10-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>SEBASTIANQV02@GMAIL.COM</t>
+          <t>MARTHAMILLER2610@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>05-03-2026 12:23:33</t>
+          <t>02-03-2026 19:44:16</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>05-03-2026 12:28:48</t>
+          <t>09-03-2026 19:19:01</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:17:51</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1475,27 +1503,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26040522914730003936</t>
+          <t>26040523026880004167</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1507,12 +1531,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>349156</t>
+          <t>348174</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>91321</t>
+          <t>90339</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1522,17 +1546,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSUE  GUADALUPE </t>
+          <t xml:space="preserve">MARBELLA ISAMAR </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SICAIROS </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1542,31 +1566,35 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6671261289</t>
+          <t>6671610495</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13-10-2009</t>
+          <t>14-04-1991</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>JOSHSICAIROS10@GMAIL.COM</t>
+          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>07-03-2026 13:42:52</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>03-03-2026 17:24:59</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1574,28 +1602,28 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>07-03-2026 13:45:15</t>
+          <t>03-03-2026 17:26:44</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>06-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1606,22 +1634,2241 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26040522975800004059</t>
+          <t>26040522850760003787</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>348168</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90333</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOEL </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRIQUEZ </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6671343522</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>28-05-1989</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:21:19</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:23:02</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26040522850490003786</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348683</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90848</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEBASTIAN </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUINTERO </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIZCARRA </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6672298295</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>02-05-2010</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>SEBASTIANQV02@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:23:33</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:28:48</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26040522914730003936</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>348838</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>91003</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRAZA </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>GERARDO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6672030695</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>28-08-1986</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>MMYGUEL@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>06-03-2026 06:43:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:32:31</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26040523002070004086</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>349156</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>91321</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSUE  GUADALUPE </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SICAIROS </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORALES </t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6671261289</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13-10-2009</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>JOSHSICAIROS10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:42:52</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:45:15</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26040522975800004059</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>349734</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>91899</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA DEL CARMEN </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CELAYA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALENZUELA </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6675737880</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA ROCIO </t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>16-07-1989</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>MARIACELAYAVALENZUELA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>09-03-2026 21:16:02</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:53:56</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:53:15</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26040523106480004346</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>349726</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>91891</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSMAR </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6674970456</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MANATIAL DE IMALA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>04-03-2012</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>OSMARLOW05@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:53:34</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:59:42</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:59:01</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26040523032960004184</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>349485</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>91650</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HUMBERTO </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASTELO </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6672032728</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>19-01-2010</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>HUMBERTOLOPEZ3515@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:43:54</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>09-03-2026 15:45:23</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26040523012190004118</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>349732</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>91897</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XIMENA </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JIMENEZ </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRUZ </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6679254999</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>02-04-2012</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>XIMENITAJC@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>09-03-2026 21:09:24</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>11-03-2026 21:27:53</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26040523107180004349</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>350245</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>92409</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LEYDI DAISIRY</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROMAN </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CHAIRES</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6675841257</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>07-09-2009</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>LEYDIROMAN07@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>11-03-2026 21:00:36</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:45:18</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26040523233880004560</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Marco Antonio  Gastelum Lozoya</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>350230</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>92394</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS RAMON </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OROZCO </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>HEREDIA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5532213499</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BUGAMBILIAS</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>18-08-1990</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>RAMON.OH@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>11-03-2026 19:47:25</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:00:54</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:00:07</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26040523104400004340</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>351343</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>93507</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ASTRID ESTHEFANY</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORGEN </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBESO </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6678403986</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>14-11-1995</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ASTRIDORGEN14@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:30:28</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:31:41</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26040523233280004558</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>351602</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>93766</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE RAMON </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORTEGA </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TORRONTEGUI</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6674496909</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>24-02-1999</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CHEMON_99@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:44:52</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:46:22</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26040523262860004620</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>350437</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>92601</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>KARLOS EDMUNDO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUINTERO </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VERASTICA</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6671405121</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>24-07-2009</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>QKARLOS34@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:35:17</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:36:27</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26040523131850004399</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>351333</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>93497</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>JOSE MANUEL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OCHOA </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6672552129</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>01-05-1998</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>JM.98.OCHOA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:17:03</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:18:11</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>15-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26040523232740004557</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>350967</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>93131</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEOBEL </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LICONA </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6674209053</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRANOVA </t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>10-08-1980</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>LCD.LICONA_MTZA@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:12:08</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:41:55</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:41:07</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26040523342130004823</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>351732</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>93896</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOAQUIN SANTIAGO </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORGEN </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBESO </t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6677574799</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>06-11-2011</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>JORGEOBESO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>17-03-2026 21:20:26</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>17-03-2026 21:23:13</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>16-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26040523275520004652</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>352030</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>94194</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA ESTHER </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALENCIA </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6674626001</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>22-10-1960</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>MAESTHER@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>19-03-2026 05:46:14</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>19-03-2026 05:48:51</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26040523313310004751</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__AZAHARES CUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>100408</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>75300</t>
+          <t>98160</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERGIO LUIS </t>
+          <t>JACKELIN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAZO </t>
+          <t>JACOBO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOBERANES </t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,39 +613,35 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6675688155</t>
+          <t>6642312712</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MANANTIAL DE LA CIENEGA</t>
+          <t>AV. MARAVILLA 2005</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>06-12-2004</t>
+          <t>25-11-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SERGIOLUISRAZO@GMAIL.COM</t>
+          <t>MARQUEZ.JACKALYN.637@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>07-03-2022 19:38:42</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>14-06-2022 17:39:42</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -653,22 +649,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 20:53:55</t>
+          <t>16-03-2026 13:37:21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>15-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -685,14 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26040522820230003715</t>
+          <t>26040523222020004540</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -709,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>100408</t>
+          <t>77498</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98160</t>
+          <t>75300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>JACKELIN</t>
+          <t xml:space="preserve">SERGIO LUIS </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JACOBO</t>
+          <t xml:space="preserve">RAZO </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t xml:space="preserve">SOBERANES </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,35 +740,39 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6642312712</t>
+          <t>6675688155</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AV. MARAVILLA 2005</t>
+          <t>MANANTIAL DE LA CIENEGA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25-11-2004</t>
+          <t>06-12-2004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MARQUEZ.JACKALYN.637@GMAIL.COM</t>
+          <t>SERGIOLUISRAZO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>14-06-2022 17:39:42</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>07-03-2022 19:38:42</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -780,22 +780,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>16-03-2026 13:37:21</t>
+          <t>02-03-2026 20:53:55</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>15-06-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,14 +812,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26040523222020004540</t>
+          <t>26040522820230003715</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346383</t>
+          <t>200259</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88548</t>
+          <t>97766</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICAELA </t>
+          <t xml:space="preserve">ROSALBA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENICEROS </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -871,75 +871,63 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6671175730</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>CENTENARIO</t>
-        </is>
-      </c>
+          <t>6671779561</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19-12-1994</t>
+          <t>25-11-2002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MICA94HDZ@HOTMAIL.COM</t>
+          <t>ROSALBALOPEZIBARRA755@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25-02-2026 08:24:59</t>
+          <t>03-10-2023 16:01:36</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 10:33:39</t>
+          <t>26-03-2026 18:37:31</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 10:31:15</t>
-        </is>
-      </c>
+          <t>25-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -947,7 +935,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26040522787820003619</t>
+          <t>26040523543530005236</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -957,34 +945,34 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Henry Thomas  Carrasco Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>345694</t>
+          <t>302216</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>87859</t>
+          <t>99714</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +982,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEDRO ANTONIO </t>
+          <t>DIANA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDOZA </t>
+          <t>ESQUER</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIRADO </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,35 +1002,31 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6674303529</t>
+          <t>6673599664</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-02-2005</t>
+          <t>05-07-2025</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PMENDOZA354@OUTLOOK.COM</t>
+          <t>dianalauraesquer21@gmail.com</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>23-02-2026 10:22:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>05-07-2025 10:54:42</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1050,22 +1034,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>07-03-2026 11:43:41</t>
+          <t>24-03-2026 18:54:07</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
+          <t>23-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1082,22 +1066,18 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26040522974240004056</t>
+          <t>26040523479930005101</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1114,12 +1094,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347427</t>
+          <t>302307</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89592</t>
+          <t>99805</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,17 +1109,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">ALEXIS </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t xml:space="preserve">ROMAN </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">CARDENAS </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1149,7 +1129,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6673463596</t>
+          <t>6677974098</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,17 +1140,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24-09-1979</t>
+          <t>15-11-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ITZEL_LEON17@HOTMAIL.COM</t>
+          <t>ALEXIS.ROMAN22@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 07:38:58</t>
+          <t>06-07-2025 14:51:11</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1191,18 +1171,18 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>05-03-2026 08:28:53</t>
+          <t>24-03-2026 18:55:36</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>23-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1213,7 +1193,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26040522910760003927</t>
+          <t>26040523480110005102</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1221,11 +1201,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Pedro Fernando  Salas RECEPCION</t>
-        </is>
-      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1899</t>
@@ -1245,12 +1221,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347883</t>
+          <t>346383</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90048</t>
+          <t>88548</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1236,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABEHT </t>
+          <t xml:space="preserve">MICAELA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">CENICEROS </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,67 +1256,63 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6727515698</t>
+          <t>6671175730</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERSALLES </t>
+          <t>CENTENARIO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>06-05-1995</t>
+          <t>19-12-1994</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ELIZABETH.HERNANDEZ13@HOTMAIL.COM</t>
+          <t>MICA94HDZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:46:47</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>25-02-2026 08:24:59</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>09-03-2026 19:15:21</t>
+          <t>02-03-2026 10:33:39</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>09-03-2026 19:13:52</t>
+          <t>02-03-2026 10:31:15</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1360,40 +1332,44 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26040523026580004165</t>
+          <t>26040522787820003619</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347880</t>
+          <t>345694</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90045</t>
+          <t>87859</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1403,17 +1379,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTHA PATRICIA </t>
+          <t xml:space="preserve">PEDRO ANTONIO </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILLER </t>
+          <t xml:space="preserve">MENDOZA </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">TIRADO </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1423,14 +1399,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6721195585</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>VERSALLES</t>
-        </is>
-      </c>
+          <t>6674303529</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1438,64 +1410,56 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26-10-1994</t>
+          <t>28-02-2005</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MARTHAMILLER2610@HOTMAIL.COM</t>
+          <t>PMENDOZA354@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 19:44:16</t>
+          <t>23-02-2026 10:22:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>09-03-2026 19:19:01</t>
+          <t>07-03-2026 11:43:41</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>09-03-2026 19:17:51</t>
-        </is>
-      </c>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1503,40 +1467,44 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26040523026880004167</t>
+          <t>26040522974240004056</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348174</t>
+          <t>347427</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90339</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,17 +1514,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARBELLA ISAMAR </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1566,35 +1534,31 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6671610495</t>
+          <t>6673463596</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>14-04-1991</t>
+          <t>24-09-1979</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
+          <t>ITZEL_LEON17@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 17:24:59</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>02-03-2026 07:38:58</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1602,22 +1566,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 17:26:44</t>
+          <t>05-03-2026 08:28:53</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1634,36 +1598,44 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26040522850760003787</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26040522910760003927</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Pedro Fernando  Salas RECEPCION</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348168</t>
+          <t>347880</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90333</t>
+          <t>90045</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1673,17 +1645,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOEL </t>
+          <t xml:space="preserve">MARTHA PATRICIA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERRIQUEZ </t>
+          <t xml:space="preserve">MILLER </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1693,67 +1665,79 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6671343522</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6721195585</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>VERSALLES</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>28-05-1989</t>
+          <t>26-10-1994</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
+          <t>MARTHAMILLER2610@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 17:21:19</t>
+          <t>02-03-2026 19:44:16</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:02</t>
+          <t>09-03-2026 19:19:01</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:17:51</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1761,14 +1745,18 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26040522850490003786</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
+          <t>26040523026880004167</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1785,12 +1773,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348683</t>
+          <t>348168</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90848</t>
+          <t>90333</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1800,17 +1788,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEBASTIAN </t>
+          <t xml:space="preserve">JOEL </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t xml:space="preserve">TERRIQUEZ </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIZCARRA </t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1820,7 +1808,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6672298295</t>
+          <t>6671343522</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1831,17 +1819,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>02-05-2010</t>
+          <t>28-05-1989</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SEBASTIANQV02@GMAIL.COM</t>
+          <t>J.TERRIQUEZ2@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>05-03-2026 12:23:33</t>
+          <t>03-03-2026 17:21:19</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1866,18 +1854,18 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-03-2026 12:28:48</t>
+          <t>03-03-2026 17:23:02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1888,19 +1876,11 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26040522914730003936</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522850490003786</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1908,7 +1888,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1920,12 +1900,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348838</t>
+          <t>348174</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>91003</t>
+          <t>90339</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1935,17 +1915,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t xml:space="preserve">MARBELLA ISAMAR </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TERRAZA </t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1955,31 +1935,35 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6672030695</t>
+          <t>6671610495</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28-08-1986</t>
+          <t>14-04-1991</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MMYGUEL@HOTMAIL.COM</t>
+          <t>MARBELLA_MEDINA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>06-03-2026 06:43:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>03-03-2026 17:24:59</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -1987,28 +1971,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>09-03-2026 09:32:31</t>
+          <t>03-03-2026 17:26:44</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>08-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2019,44 +2003,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26040523002070004086</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040522850760003787</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>349156</t>
+          <t>348838</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>91321</t>
+          <t>91003</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,17 +2042,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSUE  GUADALUPE </t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SICAIROS </t>
+          <t xml:space="preserve">TERRAZA </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6671261289</t>
+          <t>6672030695</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2097,17 +2073,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13-10-2009</t>
+          <t>28-08-1986</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JOSHSICAIROS10@GMAIL.COM</t>
+          <t>MMYGUEL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>07-03-2026 13:42:52</t>
+          <t>06-03-2026 06:43:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2118,22 +2094,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>07-03-2026 13:45:15</t>
+          <t>09-03-2026 09:32:31</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>06-06-2026 23:59:59</t>
+          <t>08-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2150,36 +2126,44 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26040522975800004059</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26040523002070004086</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>349734</t>
+          <t>348683</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>91899</t>
+          <t>90848</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2189,17 +2173,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA DEL CARMEN </t>
+          <t xml:space="preserve">SEBASTIAN </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CELAYA</t>
+          <t xml:space="preserve">QUINTERO </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">VIZCARRA </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2209,47 +2193,43 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6675737880</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTA ROCIO </t>
-        </is>
-      </c>
+          <t>6672298295</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16-07-1989</t>
+          <t>02-05-2010</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MARIACELAYAVALENZUELA@GMAIL.COM</t>
+          <t>SEBASTIANQV02@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>09-03-2026 21:16:02</t>
+          <t>05-03-2026 12:23:33</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2259,29 +2239,21 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>11-03-2026 20:53:56</t>
+          <t>05-03-2026 12:28:48</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>11-03-2026 20:53:15</t>
-        </is>
-      </c>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2289,7 +2261,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26040523106480004346</t>
+          <t>26040522914730003936</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2297,7 +2269,11 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>549</t>
@@ -2305,12 +2281,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2420,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2456,12 +2432,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>349485</t>
+          <t>349156</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>91650</t>
+          <t>91321</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2471,17 +2447,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUMBERTO </t>
+          <t xml:space="preserve">JOSUE  GUADALUPE </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">SICAIROS </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELO </t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2491,7 +2467,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6672032728</t>
+          <t>6671261289</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2502,17 +2478,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19-01-2010</t>
+          <t>13-10-2009</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>HUMBERTOLOPEZ3515@GMAIL.COM</t>
+          <t>JOSHSICAIROS10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-03-2026 15:43:54</t>
+          <t>07-03-2026 13:42:52</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2533,12 +2509,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-03-2026 15:45:23</t>
+          <t>07-03-2026 13:45:15</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>08-06-2026 23:59:59</t>
+          <t>06-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2555,7 +2531,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26040523012190004118</t>
+          <t>26040522975800004059</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2710,12 +2686,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>350245</t>
+          <t>347883</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>92409</t>
+          <t>90048</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2725,17 +2701,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEYDI DAISIRY</t>
+          <t xml:space="preserve">ELIZABEHT </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMAN </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CHAIRES</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2745,10 +2721,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6675841257</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6727515698</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERSALLES </t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2756,56 +2736,64 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>07-09-2009</t>
+          <t>06-05-1995</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LEYDIROMAN07@ICLOUD.COM</t>
+          <t>ELIZABETH.HERNANDEZ13@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>11-03-2026 21:00:36</t>
+          <t>02-03-2026 19:46:47</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Culiacan pago</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>16-03-2026 19:45:18</t>
+          <t>09-03-2026 19:15:21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:13:52</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2813,44 +2801,40 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26040523233880004560</t>
+          <t>26040523026580004165</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Marco Antonio  Gastelum Lozoya</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>350230</t>
+          <t>350245</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>92394</t>
+          <t>92409</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2860,17 +2844,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS RAMON </t>
+          <t>LEYDI DAISIRY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">OROZCO </t>
+          <t xml:space="preserve">ROMAN </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HEREDIA</t>
+          <t>CHAIRES</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2880,79 +2864,67 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5532213499</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>BUGAMBILIAS</t>
-        </is>
-      </c>
+          <t>6675841257</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18-08-1990</t>
+          <t>07-09-2009</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>RAMON.OH@OUTLOOK.COM</t>
+          <t>LEYDIROMAN07@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>11-03-2026 19:47:25</t>
+          <t>11-03-2026 21:00:36</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Culiacan pago</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>11-03-2026 20:00:54</t>
+          <t>16-03-2026 19:45:18</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>11-03-2026 20:00:07</t>
-        </is>
-      </c>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2960,36 +2932,44 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26040523104400004340</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>26040523233880004560</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>351343</t>
+          <t>349734</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>93507</t>
+          <t>91899</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2999,17 +2979,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ASTRID ESTHEFANY</t>
+          <t xml:space="preserve">MARIA DEL CARMEN </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORGEN </t>
+          <t>CELAYA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBESO </t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3019,10 +2999,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6678403986</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>6675737880</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA ROCIO </t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3030,52 +3014,64 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>14-11-1995</t>
+          <t>16-07-1989</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ASTRIDORGEN14@GMAIL.COM</t>
+          <t>MARIACELAYAVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>16-03-2026 19:30:28</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>09-03-2026 21:16:02</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>16-03-2026 19:31:41</t>
+          <t>11-03-2026 20:53:56</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>15-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:53:15</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3083,36 +3079,40 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26040523233280004558</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+          <t>26040523106480004346</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Manuel Oyalit  Valenzuela Batiz</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>351602</t>
+          <t>351343</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>93766</t>
+          <t>93507</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3122,17 +3122,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE RAMON </t>
+          <t>ASTRID ESTHEFANY</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTEGA </t>
+          <t xml:space="preserve">ORGEN </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TORRONTEGUI</t>
+          <t xml:space="preserve">OBESO </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3142,35 +3142,31 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6674496909</t>
+          <t>6678403986</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>24-02-1999</t>
+          <t>14-11-1995</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CHEMON_99@HOTMAIL.COM</t>
+          <t>ASTRIDORGEN14@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>17-03-2026 17:44:52</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>16-03-2026 19:30:28</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3178,28 +3174,28 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>17-03-2026 17:46:22</t>
+          <t>16-03-2026 19:31:41</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>15-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -3210,36 +3206,36 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26040523262860004620</t>
+          <t>26040523233280004558</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>350437</t>
+          <t>349485</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>92601</t>
+          <t>91650</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3249,17 +3245,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KARLOS EDMUNDO</t>
+          <t xml:space="preserve">HUMBERTO </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUINTERO </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VERASTICA</t>
+          <t xml:space="preserve">CASTELO </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3269,35 +3265,31 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6671405121</t>
+          <t>6672032728</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>24-07-2009</t>
+          <t>19-01-2010</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>QKARLOS34@GMAIL.COM</t>
+          <t>HUMBERTOLOPEZ3515@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>12-03-2026 18:35:17</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>convenio 300</t>
-        </is>
-      </c>
+          <t>09-03-2026 15:43:54</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3305,28 +3297,28 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>12-03-2026 18:36:27</t>
+          <t>09-03-2026 15:45:23</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>08-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -3337,24 +3329,24 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26040523131850004399</t>
+          <t>26040523012190004118</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Marco Antonio  Gastelum Lozoya</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3476,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>350967</t>
+          <t>352690</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>93131</t>
+          <t>94854</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3499,17 +3491,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEOBEL </t>
+          <t xml:space="preserve">NADIA DANIELA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LICONA </t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">ROMERO </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3519,79 +3511,63 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6674209053</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TERRANOVA </t>
-        </is>
-      </c>
+          <t>6671940068</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>10-08-1980</t>
+          <t>26-05-1997</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>LCD.LICONA_MTZA@HOTMAIL.COM</t>
+          <t>NADIIAAVEGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16-03-2026 07:12:08</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Culiacan pago</t>
-        </is>
-      </c>
+          <t>23-03-2026 09:42:55</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>19-03-2026 19:41:55</t>
+          <t>23-03-2026 09:44:31</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>19-03-2026 19:41:07</t>
-        </is>
-      </c>
+          <t>22-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3599,44 +3575,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26040523342130004823</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
-        </is>
-      </c>
+          <t>26040523420680004933</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>351732</t>
+          <t>352648</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>93896</t>
+          <t>94812</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3646,17 +3614,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOAQUIN SANTIAGO </t>
+          <t>LUCINDA EMILIA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORGEN </t>
+          <t xml:space="preserve">IBARRA </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBESO </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3666,31 +3634,35 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6677574799</t>
+          <t>6673241041</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>06-11-2011</t>
+          <t>27-02-1971</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>JORGEOBESO@GMAIL.COM</t>
+          <t>LEIL71@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17-03-2026 21:20:26</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>23-03-2026 06:59:08</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3698,22 +3670,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>17-03-2026 21:23:13</t>
+          <t>23-03-2026 07:00:29</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-06-2026 23:59:59</t>
+          <t>22-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3730,36 +3702,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26040523275520004652</t>
+          <t>26040523416150004925</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Henry Thomas  Carrasco Cazares</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>352030</t>
+          <t>351732</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>94194</t>
+          <t>93896</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3769,17 +3741,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ESTHER </t>
+          <t xml:space="preserve">JOAQUIN SANTIAGO </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENCIA </t>
+          <t xml:space="preserve">ORGEN </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">OBESO </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3789,28 +3761,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6674626001</t>
+          <t>6677574799</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>22-10-1960</t>
+          <t>06-11-2011</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MAESTHER@GMAIL.COM</t>
+          <t>JORGEOBESO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19-03-2026 05:46:14</t>
+          <t>17-03-2026 21:20:26</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3831,12 +3803,12 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>19-03-2026 05:48:51</t>
+          <t>17-03-2026 21:23:13</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>18-06-2026 23:59:59</t>
+          <t>16-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3853,7 +3825,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26040523313310004751</t>
+          <t>26040523275520004652</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3865,10 +3837,1852 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
+          <t>Pedro Fernando Salas Mendoza</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>350230</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>92394</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS RAMON </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OROZCO </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HEREDIA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5532213499</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BUGAMBILIAS</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>18-08-1990</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>RAMON.OH@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11-03-2026 19:47:25</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:00:54</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:00:07</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26040523104400004340</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>353038</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>95202</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GONZALO SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELTRAN </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BUÑUELOS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6674612319</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>C SIN NOMBRE P 25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>10-01-2005</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>BELTRANB.105TM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>24-03-2026 09:13:40</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>24-03-2026 09:16:48</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>24-03-2026 09:16:30</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26040523461730005037</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Henry Thomas  Carrasco Cazares</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>352030</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>94194</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA ESTHER </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALENCIA </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6674626001</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>22-10-1960</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>MAESTHER@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>19-03-2026 05:46:14</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>19-03-2026 05:48:51</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26040523313310004751</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>353000</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>95164</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRIDA ITALIA </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ZURITA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6671030382</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>21-02-2004</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>FRIDAITALIAGARCIA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>23-03-2026 21:17:18</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>26-03-2026 21:16:29</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>25-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26040523549840005251</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>YARELI YUMEL RAMIREZ LOPEZ</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>350437</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>92601</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>KARLOS EDMUNDO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUINTERO </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VERASTICA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6671405121</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>24-07-2009</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>QKARLOS34@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:35:17</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:36:27</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26040523131850004399</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>353265</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>95429</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SELENE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VERDUGO </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHAVEZ </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6674770891</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>AEROPUERTO</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>21-08-1981</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>SELENEVCHAVEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>25-03-2026 06:48:51</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>25-03-2026 06:55:50</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>25-03-2026 06:54:43</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26040523493930005119</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Henry Thomas  Carrasco Cazares</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>353454</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>95618</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTHA ZULEMA </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOAIZA </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BELTRAN </t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6672159501</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>15-08-1995</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>ZULEMALOAIZA95@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>25-03-2026 19:36:43</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>26-03-2026 20:48:33</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26040523549130005250</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>353453</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CESAR OMAR </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARCE </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAÑUELOS </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6677956897</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUGAMBILIAS </t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>02-08-1993</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>CESAROMAR042@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>25-03-2026 19:33:31</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>26-03-2026 20:48:33</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>26-03-2026 20:47:46</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26040523549130005250</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Manuel Oyalit  Valenzuela Batiz</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>350967</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>93131</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEOBEL </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LICONA </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6674209053</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TERRANOVA </t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>10-08-1980</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>LCD.LICONA_MTZA@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:12:08</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Culiacan pago</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:41:55</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:41:07</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26040523342130004823</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA ALEJANDRA  ZAZUETA  LOPEZ </t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>351602</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>93766</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE RAMON </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORTEGA </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>TORRONTEGUI</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6674496909</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>24-02-1999</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CHEMON_99@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:44:52</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:46:22</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26040523262860004620</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>352767</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>94931</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA SOFIA </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IBARRA </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AYALA </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6676171959</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>01-07-1999</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>SOFIAIBARRAAYALA@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>23-03-2026 14:17:18</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>23-03-2026 14:19:32</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>22-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26040523427300004954</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>353137</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>95301</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN LUIS </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORENO </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>IBARRA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6674155512</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>04-06-2010</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ELVA_LUZ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>24-03-2026 16:44:00</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>24-03-2026 16:45:18</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>23-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26040523471860005073</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>353205</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>95369</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SAMANTHA MICHELLE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RICO </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>OLEA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>9818188637</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>09-06-1989</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>SAMRICOO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>24-03-2026 19:00:14</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>26-03-2026 20:04:16</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>25-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26040523547870005248</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>354043</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>96207</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AZAHARES CUL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICTORIA </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>GAMEZ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6678403815</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>26-06-2011</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>VICTORIA260606@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>29-03-2026 14:08:29</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>29-03-2026 14:10:02</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>28-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26040523607070005343</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
